--- a/.feature-dev/02-data-dictionary.xlsx
+++ b/.feature-dev/02-data-dictionary.xlsx
@@ -5157,7 +5157,11 @@
           <t>required; локальный формат ДД.ММ.ГГГГ</t>
         </is>
       </c>
-      <c r="AP37" s="14" t="inlineStr"/>
+      <c r="AP37" s="14" t="inlineStr">
+        <is>
+          <t>ОВ-11: update=Y — правится в черновике; в работе смену даты сервис блокирует (SV-10).</t>
+        </is>
+      </c>
       <c r="AQ37" s="14" t="inlineStr"/>
       <c r="AR37" s="13" t="inlineStr">
         <is>
@@ -5176,7 +5180,7 @@
       </c>
       <c r="AU37" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5429,11 @@
       <c r="AM39" s="13" t="inlineStr"/>
       <c r="AN39" s="13" t="inlineStr"/>
       <c r="AO39" s="14" t="inlineStr"/>
-      <c r="AP39" s="14" t="inlineStr"/>
+      <c r="AP39" s="14" t="inlineStr">
+        <is>
+          <t>ОВ-11: update=Y — правится в черновике; в работе смену склада сервис блокирует (приобретения уже пошли на прежний склад, SV-10).</t>
+        </is>
+      </c>
       <c r="AQ39" s="14" t="inlineStr"/>
       <c r="AR39" s="13" t="inlineStr">
         <is>
@@ -5444,7 +5452,7 @@
       </c>
       <c r="AU39" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -5687,7 +5695,7 @@
       <c r="AO41" s="14" t="inlineStr"/>
       <c r="AP41" s="14" t="inlineStr">
         <is>
-          <t>Существующая колонка закрывает «Ehtiyojning asoslanishi» бланка — отдельной колонки под причину НЕ заводим (решение заказчика 17.07.2026). В шаблон notification.html приходит под именем n.justification: имя переменной контекста рендера, не колонки.</t>
+          <t>Существующая колонка закрывает «Ehtiyojning asoslanishi» бланка — отдельной колонки под причину НЕ заводим (решение заказчика 17.07.2026). В шаблон notification.html приходит под именем n.justification: имя переменной контекста рендера, не колонки. ОВ-11: update=Y — текст правится и в черновике, и в работе (SV-10).</t>
         </is>
       </c>
       <c r="AQ41" s="14" t="inlineStr"/>
@@ -5708,7 +5716,7 @@
       </c>
       <c r="AU41" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -5809,7 +5817,7 @@
       </c>
       <c r="AP42" s="14" t="inlineStr">
         <is>
-          <t>Товары в текст абзаца НЕ дублируются — перечень рендерится из notification_items, иначе текст и таблица бланка разойдутся (см. notification.html).</t>
+          <t>Товары в текст абзаца НЕ дублируются — перечень рендерится из notification_items, иначе текст и таблица бланка разойдутся (см. notification.html). ОВ-11: update=Y — текст правится и в черновике, и в работе (SV-10).</t>
         </is>
       </c>
       <c r="AQ42" s="14" t="inlineStr"/>
@@ -5830,7 +5838,7 @@
       </c>
       <c r="AU42" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -5935,7 +5943,7 @@
       </c>
       <c r="AP43" s="14" t="inlineStr">
         <is>
-          <t>СВОБОДНЫЙ ТЕКСТ, не справочник и не FK на warehouses (решение заказчика 17.07.2026, пересмотру не подлежит). Подразделение и склад назначения — разные сущности: склад отвечает на «куда придёт товар», подразделение — «кто просит». Отдельной таблицы нет — 22 таблицы остаются 22.</t>
+          <t>СВОБОДНЫЙ ТЕКСТ, не справочник и не FK на warehouses (решение заказчика 17.07.2026, пересмотру не подлежит). Подразделение и склад назначения — разные сущности: склад отвечает на «куда придёт товар», подразделение — «кто просит». Отдельной таблицы нет — 22 таблицы остаются 22. ОВ-11: update=Y — текст правится и в черновике, и в работе (SV-10).</t>
         </is>
       </c>
       <c r="AQ43" s="14" t="inlineStr"/>
@@ -5956,7 +5964,7 @@
       </c>
       <c r="AU43" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -6603,7 +6611,11 @@
           <t>required; товар не должен повторяться в строках одного уведомления</t>
         </is>
       </c>
-      <c r="AP48" s="14" t="inlineStr"/>
+      <c r="AP48" s="14" t="inlineStr">
+        <is>
+          <t>ОВ-11: update=Y — строки правятся диффом по product_id (add/remove/смена товара). В черновике свободно; в работе удаление строки с приобретениями блокирует сервис (SV-10/SV-11).</t>
+        </is>
+      </c>
       <c r="AQ48" s="14" t="inlineStr"/>
       <c r="AR48" s="13" t="inlineStr">
         <is>
@@ -6622,7 +6634,7 @@
       </c>
       <c r="AU48" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -6723,7 +6735,7 @@
       </c>
       <c r="AP49" s="14" t="inlineStr">
         <is>
-          <t>qty_purchased и «остаток к приобретению» НЕ хранятся — считаются из acquisition_items (ТЗ §3).</t>
+          <t>qty_purchased и «остаток к приобретению» НЕ хранятся — считаются из acquisition_items (ТЗ §3). ОВ-11: update=Y — в черновике меняется свободно; в работе увеличение свободно, уменьшение ниже приобретённого блокирует сервис (SV-10).</t>
         </is>
       </c>
       <c r="AQ49" s="14" t="inlineStr"/>
@@ -6744,7 +6756,7 @@
       </c>
       <c r="AU49" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✓</t>
         </is>
       </c>
     </row>

--- a/.feature-dev/02-data-dictionary.xlsx
+++ b/.feature-dev/02-data-dictionary.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data Dictionary'!$A$4:$AU$135</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data Dictionary'!$A$4:$AU$149</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -562,7 +562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU135"/>
+  <dimension ref="A1:AU149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -11791,7 +11791,7 @@
     <row r="88">
       <c r="A88" s="13" t="inlineStr">
         <is>
-          <t>ТЗ §3 М4 requests · ADR-2 · AP-2/AP-3 · INV-2</t>
+          <t>ТЗ §3 М4 requests · ADR-2 · спека13 §2 · INV-2</t>
         </is>
       </c>
       <c r="B88" s="13" t="inlineStr"/>
@@ -11817,7 +11817,7 @@
       </c>
       <c r="J88" s="14" t="inlineStr">
         <is>
-          <t>draft | to_print | printed | issued. Статусы принадлежат ЗАЯВКЕ, не проводке (ADR-2).</t>
+          <t>draft | to_issue | issued | signed | submitted. Статусы принадлежат ЗАЯВКЕ, не проводке (ADR-2). Фича 13 §2: подпись расцеплена с выдачей.</t>
         </is>
       </c>
       <c r="K88" s="13" t="inlineStr">
@@ -11841,7 +11841,7 @@
       </c>
       <c r="R88" s="13" t="inlineStr">
         <is>
-          <t>draft | to_print | printed | issued</t>
+          <t>draft | to_issue | issued | signed | submitted</t>
         </is>
       </c>
       <c r="S88" s="13" t="inlineStr">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="U88" s="13" t="inlineStr">
         <is>
-          <t>True (partial: WHERE status = 'to_print' — AP-2/AP-3)</t>
+          <t>True (ix_requests_status — фильтр-карточки К выдаче/К подписи/Подписано/Передано, спека13 §5)</t>
         </is>
       </c>
       <c r="V88" s="13" t="inlineStr">
@@ -11867,7 +11867,7 @@
       <c r="W88" s="13" t="inlineStr"/>
       <c r="X88" s="14" t="inlineStr">
         <is>
-          <t>INV-2: CHECK ((status = 'issued') = (writeoff_id IS NOT NULL))</t>
+          <t>INV-2: CHECK ((status IN ('issued','signed','submitted')) = (writeoff_id IS NOT NULL))</t>
         </is>
       </c>
       <c r="Y88" s="13" t="inlineStr">
@@ -11879,7 +11879,7 @@
       <c r="AA88" s="13" t="inlineStr"/>
       <c r="AB88" s="13" t="inlineStr">
         <is>
-          <t>draft | to_print | printed | issued</t>
+          <t>draft | to_issue | issued | signed | submitted</t>
         </is>
       </c>
       <c r="AC88" s="13" t="inlineStr"/>
@@ -11917,7 +11917,7 @@
       <c r="AO88" s="14" t="inlineStr"/>
       <c r="AP88" s="14" t="inlineStr">
         <is>
-          <t>Переходы только через POST /confirm, /print, /issue. SV-5: issue() делает условный UPDATE ... WHERE status='printed'.</t>
+          <t>Фича 13 §2: draft→to_issue→issued→signed→submitted. Списание (writeoff) рождается на to_issue→issued (было printed→issued). Прежний частичный ix_requests_to_print снят миграцией 0002 вместе со значением to_print; четыре фильтр-карточки экрана обслуживает один ix_requests_status. Data migration 0002: to_print→to_issue, printed→to_issue. Переходы двигает сервер (статусная машина этапа 2).</t>
         </is>
       </c>
       <c r="AQ88" s="14" t="inlineStr"/>
@@ -12603,7 +12603,7 @@
     <row r="94">
       <c r="A94" s="13" t="inlineStr">
         <is>
-          <t>ТЗ §3 М4 request_items</t>
+          <t>спека13 §3</t>
         </is>
       </c>
       <c r="B94" s="13" t="inlineStr"/>
@@ -12614,22 +12614,22 @@
       </c>
       <c r="D94" s="14" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>Пачка подписи</t>
         </is>
       </c>
       <c r="E94" s="13" t="inlineStr">
         <is>
-          <t>request_items.id</t>
+          <t>requests.batch_id</t>
         </is>
       </c>
       <c r="G94" s="13" t="inlineStr">
         <is>
-          <t>bigserial</t>
+          <t>bigint FK NULL</t>
         </is>
       </c>
       <c r="J94" s="14" t="inlineStr">
         <is>
-          <t>Суррогатный первичный ключ.</t>
+          <t>Пачка печати/подписи (signature_batches). NULL до печати пачкой. Признак «напечатано» = batch_id IS NOT NULL. Печать статус НЕ меняет.</t>
         </is>
       </c>
       <c r="K94" s="13" t="inlineStr">
@@ -12641,30 +12641,26 @@
       <c r="M94" s="13" t="inlineStr"/>
       <c r="N94" s="13" t="inlineStr">
         <is>
-          <t>BigInteger</t>
-        </is>
-      </c>
-      <c r="O94" s="13" t="inlineStr">
-        <is>
-          <t>autoincrement (Identity)</t>
-        </is>
-      </c>
-      <c r="P94" s="13" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="Q94" s="13" t="inlineStr"/>
+          <t>BigInteger · ForeignKey('signature_batches.id', ondelete='RESTRICT')</t>
+        </is>
+      </c>
+      <c r="O94" s="13" t="inlineStr"/>
+      <c r="P94" s="13" t="inlineStr"/>
+      <c r="Q94" s="13" t="inlineStr">
+        <is>
+          <t>relationship SignatureBatch</t>
+        </is>
+      </c>
       <c r="R94" s="13" t="inlineStr"/>
       <c r="S94" s="13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="T94" s="13" t="inlineStr"/>
       <c r="U94" s="13" t="inlineStr">
         <is>
-          <t>True (PK)</t>
+          <t>True (FK)</t>
         </is>
       </c>
       <c r="V94" s="13" t="inlineStr">
@@ -12672,15 +12668,15 @@
           <t>False</t>
         </is>
       </c>
-      <c r="W94" s="13" t="inlineStr"/>
-      <c r="X94" s="14" t="inlineStr">
-        <is>
-          <t>PRIMARY KEY</t>
-        </is>
-      </c>
+      <c r="W94" s="13" t="inlineStr">
+        <is>
+          <t>RESTRICT</t>
+        </is>
+      </c>
+      <c r="X94" s="14" t="inlineStr"/>
       <c r="Y94" s="13" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>batch_id</t>
         </is>
       </c>
       <c r="Z94" s="13" t="inlineStr"/>
@@ -12715,7 +12711,11 @@
         </is>
       </c>
       <c r="AO94" s="14" t="inlineStr"/>
-      <c r="AP94" s="14" t="inlineStr"/>
+      <c r="AP94" s="14" t="inlineStr">
+        <is>
+          <t>Ставит сервер при пакетной печати (ЭТАП 2). RESTRICT: пачку с заявками не удалить, не отвязав заявки. Read-поле выведено (get_index/get_single): экран «К подписи» показывает признак «напечатано» = batch_id IS NOT NULL.</t>
+        </is>
+      </c>
       <c r="AQ94" s="14" t="inlineStr"/>
       <c r="AR94" s="13" t="inlineStr">
         <is>
@@ -12741,7 +12741,7 @@
     <row r="95">
       <c r="A95" s="13" t="inlineStr">
         <is>
-          <t>ТЗ §3 М4 request_items</t>
+          <t>спека13 §4</t>
         </is>
       </c>
       <c r="B95" s="13" t="inlineStr"/>
@@ -12752,22 +12752,22 @@
       </c>
       <c r="D95" s="14" t="inlineStr">
         <is>
-          <t>Заявка</t>
+          <t>Передано (дата)</t>
         </is>
       </c>
       <c r="E95" s="13" t="inlineStr">
         <is>
-          <t>request_items.request_id</t>
+          <t>requests.submitted_at</t>
         </is>
       </c>
       <c r="G95" s="13" t="inlineStr">
         <is>
-          <t>bigint FK</t>
+          <t>date NULL</t>
         </is>
       </c>
       <c r="J95" s="14" t="inlineStr">
         <is>
-          <t>Родительская заявка.</t>
+          <t>Дата передачи заявки в бухгалтерию (bulk-действие signed → submitted). NULL до передачи.</t>
         </is>
       </c>
       <c r="K95" s="13" t="inlineStr">
@@ -12779,38 +12779,30 @@
       <c r="M95" s="13" t="inlineStr"/>
       <c r="N95" s="13" t="inlineStr">
         <is>
-          <t>BigInteger · ForeignKey('requests.id', ondelete='CASCADE')</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="O95" s="13" t="inlineStr"/>
       <c r="P95" s="13" t="inlineStr"/>
-      <c r="Q95" s="13" t="inlineStr">
-        <is>
-          <t>relationship Request</t>
-        </is>
-      </c>
+      <c r="Q95" s="13" t="inlineStr"/>
       <c r="R95" s="13" t="inlineStr"/>
       <c r="S95" s="13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="T95" s="13" t="inlineStr"/>
-      <c r="U95" s="13" t="inlineStr">
-        <is>
-          <t>True (FK)</t>
-        </is>
-      </c>
-      <c r="V95" s="13" t="inlineStr"/>
-      <c r="W95" s="13" t="inlineStr">
-        <is>
-          <t>CASCADE</t>
-        </is>
-      </c>
+      <c r="U95" s="13" t="inlineStr"/>
+      <c r="V95" s="13" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="W95" s="13" t="inlineStr"/>
       <c r="X95" s="14" t="inlineStr"/>
       <c r="Y95" s="13" t="inlineStr">
         <is>
-          <t>request_id</t>
+          <t>submitted_at__range</t>
         </is>
       </c>
       <c r="Z95" s="13" t="inlineStr"/>
@@ -12830,7 +12822,7 @@
       </c>
       <c r="AK95" s="13" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>date</t>
         </is>
       </c>
       <c r="AL95" s="13" t="inlineStr">
@@ -12845,11 +12837,15 @@
         </is>
       </c>
       <c r="AO95" s="14" t="inlineStr"/>
-      <c r="AP95" s="14" t="inlineStr"/>
+      <c r="AP95" s="14" t="inlineStr">
+        <is>
+          <t>Ставит сервер (bulk «Передать в бухгалтерию», ЭТАП 2). «Передано» на экране = status='submitted'; отдельного индекса на submitted_at у requests нет — фильтр-карточки обслуживает ix_requests_status. Read-поле выведено (get_index/get_single) для карточки «Передано» и реестра передачи.</t>
+        </is>
+      </c>
       <c r="AQ95" s="14" t="inlineStr"/>
       <c r="AR95" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="AS95" s="13" t="inlineStr">
@@ -12871,7 +12867,7 @@
     <row r="96">
       <c r="A96" s="13" t="inlineStr">
         <is>
-          <t>ТЗ §3 М4 request_items</t>
+          <t>спека13 §4</t>
         </is>
       </c>
       <c r="B96" s="13" t="inlineStr"/>
@@ -12882,22 +12878,22 @@
       </c>
       <c r="D96" s="14" t="inlineStr">
         <is>
-          <t>Товар</t>
+          <t>Реестр передачи №</t>
         </is>
       </c>
       <c r="E96" s="13" t="inlineStr">
         <is>
-          <t>request_items.product_id</t>
+          <t>requests.submitted_register_no</t>
         </is>
       </c>
       <c r="G96" s="13" t="inlineStr">
         <is>
-          <t>bigint FK</t>
+          <t>varchar(32) NULL</t>
         </is>
       </c>
       <c r="J96" s="14" t="inlineStr">
         <is>
-          <t>Запрашиваемый товар.</t>
+          <t>Номер реестра передачи (один на пачку передачи). NULL до передачи. Доказательство передачи, бухгалтерия расписывается в получении (спека §4).</t>
         </is>
       </c>
       <c r="K96" s="13" t="inlineStr">
@@ -12909,46 +12905,34 @@
       <c r="M96" s="13" t="inlineStr"/>
       <c r="N96" s="13" t="inlineStr">
         <is>
-          <t>BigInteger · ForeignKey('products.id', ondelete='RESTRICT')</t>
+          <t>String(32)</t>
         </is>
       </c>
       <c r="O96" s="13" t="inlineStr"/>
       <c r="P96" s="13" t="inlineStr"/>
-      <c r="Q96" s="13" t="inlineStr">
-        <is>
-          <t>relationship Product</t>
-        </is>
-      </c>
+      <c r="Q96" s="13" t="inlineStr"/>
       <c r="R96" s="13" t="inlineStr"/>
       <c r="S96" s="13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="T96" s="13" t="inlineStr"/>
-      <c r="U96" s="13" t="inlineStr">
-        <is>
-          <t>True (FK)</t>
-        </is>
-      </c>
-      <c r="V96" s="13" t="inlineStr"/>
-      <c r="W96" s="13" t="inlineStr">
-        <is>
-          <t>RESTRICT</t>
-        </is>
-      </c>
+      <c r="U96" s="13" t="inlineStr"/>
+      <c r="V96" s="13" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="W96" s="13" t="inlineStr"/>
       <c r="X96" s="14" t="inlineStr"/>
       <c r="Y96" s="13" t="inlineStr">
         <is>
-          <t>product_id</t>
+          <t>submitted_register_no</t>
         </is>
       </c>
       <c r="Z96" s="13" t="inlineStr"/>
-      <c r="AA96" s="13" t="inlineStr">
-        <is>
-          <t>GET /stock/balances?warehouse_id={warehouse_id} (ОВ-5)</t>
-        </is>
-      </c>
+      <c r="AA96" s="13" t="inlineStr"/>
       <c r="AB96" s="13" t="inlineStr"/>
       <c r="AC96" s="13" t="inlineStr"/>
       <c r="AD96" s="13" t="inlineStr"/>
@@ -12959,27 +12943,39 @@
       <c r="AI96" s="14" t="inlineStr"/>
       <c r="AJ96" s="13" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AK96" s="13" t="inlineStr">
         <is>
-          <t>select</t>
+          <t>text</t>
         </is>
       </c>
       <c r="AL96" s="13" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AM96" s="13" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="AN96" s="13" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AM96" s="13" t="inlineStr"/>
-      <c r="AN96" s="13" t="inlineStr"/>
       <c r="AO96" s="14" t="inlineStr"/>
-      <c r="AP96" s="14" t="inlineStr"/>
+      <c r="AP96" s="14" t="inlineStr">
+        <is>
+          <t>Серверная серия, как у прочих документов (спека §7). Индекса нет: реестр печатается по требованию, не горячий путь (правило проекта — индекс под заявленный access pattern). Read-поле выведено (get_index/get_single) для реестра передачи.</t>
+        </is>
+      </c>
       <c r="AQ96" s="14" t="inlineStr"/>
       <c r="AR96" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="AS96" s="13" t="inlineStr">
@@ -12989,7 +12985,7 @@
       </c>
       <c r="AT96" s="13" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AU96" s="13" t="inlineStr">
@@ -13001,7 +12997,7 @@
     <row r="97">
       <c r="A97" s="13" t="inlineStr">
         <is>
-          <t>ТЗ §3 М4 request_items</t>
+          <t>спека13 §3 signature_batches</t>
         </is>
       </c>
       <c r="B97" s="13" t="inlineStr"/>
@@ -13012,22 +13008,22 @@
       </c>
       <c r="D97" s="14" t="inlineStr">
         <is>
-          <t>Количество</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E97" s="13" t="inlineStr">
         <is>
-          <t>request_items.qty</t>
+          <t>signature_batches.id</t>
         </is>
       </c>
       <c r="G97" s="13" t="inlineStr">
         <is>
-          <t>numeric(14,3)</t>
+          <t>bigserial</t>
         </is>
       </c>
       <c r="J97" s="14" t="inlineStr">
         <is>
-          <t>Запрошенное количество. Переносится в writeoff_items при issue().</t>
+          <t>Суррогатный первичный ключ.</t>
         </is>
       </c>
       <c r="K97" s="13" t="inlineStr">
@@ -13039,11 +13035,19 @@
       <c r="M97" s="13" t="inlineStr"/>
       <c r="N97" s="13" t="inlineStr">
         <is>
-          <t>Numeric(14, 3)</t>
-        </is>
-      </c>
-      <c r="O97" s="13" t="inlineStr"/>
-      <c r="P97" s="13" t="inlineStr"/>
+          <t>BigInteger</t>
+        </is>
+      </c>
+      <c r="O97" s="13" t="inlineStr">
+        <is>
+          <t>autoincrement (Identity)</t>
+        </is>
+      </c>
+      <c r="P97" s="13" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
       <c r="Q97" s="13" t="inlineStr"/>
       <c r="R97" s="13" t="inlineStr"/>
       <c r="S97" s="13" t="inlineStr">
@@ -13052,15 +13056,27 @@
         </is>
       </c>
       <c r="T97" s="13" t="inlineStr"/>
-      <c r="U97" s="13" t="inlineStr"/>
-      <c r="V97" s="13" t="inlineStr"/>
+      <c r="U97" s="13" t="inlineStr">
+        <is>
+          <t>True (PK)</t>
+        </is>
+      </c>
+      <c r="V97" s="13" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="W97" s="13" t="inlineStr"/>
       <c r="X97" s="14" t="inlineStr">
         <is>
-          <t>INV-6: CHECK (qty &gt; 0)</t>
-        </is>
-      </c>
-      <c r="Y97" s="13" t="inlineStr"/>
+          <t>PRIMARY KEY</t>
+        </is>
+      </c>
+      <c r="Y97" s="13" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
       <c r="Z97" s="13" t="inlineStr"/>
       <c r="AA97" s="13" t="inlineStr"/>
       <c r="AB97" s="13" t="inlineStr"/>
@@ -13073,7 +13089,7 @@
       <c r="AI97" s="14" t="inlineStr"/>
       <c r="AJ97" s="13" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AK97" s="13" t="inlineStr">
@@ -13083,25 +13099,21 @@
       </c>
       <c r="AL97" s="13" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AM97" s="13" t="inlineStr"/>
+      <c r="AN97" s="13" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AM97" s="13" t="inlineStr"/>
-      <c r="AN97" s="13" t="inlineStr"/>
-      <c r="AO97" s="14" t="inlineStr">
-        <is>
-          <t>required; &gt; 0</t>
-        </is>
-      </c>
-      <c r="AP97" s="14" t="inlineStr">
-        <is>
-          <t>Резервирования нет (§8, ADR-3): наличие проверяется только в момент issue().</t>
-        </is>
-      </c>
+      <c r="AO97" s="14" t="inlineStr"/>
+      <c r="AP97" s="14" t="inlineStr"/>
       <c r="AQ97" s="14" t="inlineStr"/>
       <c r="AR97" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="AS97" s="13" t="inlineStr">
@@ -13111,7 +13123,7 @@
       </c>
       <c r="AT97" s="13" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AU97" s="13" t="inlineStr">
@@ -13123,7 +13135,7 @@
     <row r="98">
       <c r="A98" s="13" t="inlineStr">
         <is>
-          <t>ТЗ §3 М4 writeoffs · ADR-2</t>
+          <t>спека13 §3 signature_batches · §7</t>
         </is>
       </c>
       <c r="B98" s="13" t="inlineStr"/>
@@ -13134,22 +13146,22 @@
       </c>
       <c r="D98" s="14" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>Номер пачки</t>
         </is>
       </c>
       <c r="E98" s="13" t="inlineStr">
         <is>
-          <t>writeoffs.id</t>
+          <t>signature_batches.number</t>
         </is>
       </c>
       <c r="G98" s="13" t="inlineStr">
         <is>
-          <t>bigserial</t>
+          <t>varchar(32)</t>
         </is>
       </c>
       <c r="J98" s="14" t="inlineStr">
         <is>
-          <t>Суррогатный первичный ключ.</t>
+          <t>Автономер пачки, серверная серия, как у прочих документов (спека §7).</t>
         </is>
       </c>
       <c r="K98" s="13" t="inlineStr">
@@ -13161,14 +13173,10 @@
       <c r="M98" s="13" t="inlineStr"/>
       <c r="N98" s="13" t="inlineStr">
         <is>
-          <t>BigInteger</t>
-        </is>
-      </c>
-      <c r="O98" s="13" t="inlineStr">
-        <is>
-          <t>autoincrement (Identity)</t>
-        </is>
-      </c>
+          <t>String(32)</t>
+        </is>
+      </c>
+      <c r="O98" s="13" t="inlineStr"/>
       <c r="P98" s="13" t="inlineStr">
         <is>
           <t>True</t>
@@ -13184,7 +13192,7 @@
       <c r="T98" s="13" t="inlineStr"/>
       <c r="U98" s="13" t="inlineStr">
         <is>
-          <t>True (PK)</t>
+          <t>True (UNIQUE)</t>
         </is>
       </c>
       <c r="V98" s="13" t="inlineStr">
@@ -13193,14 +13201,10 @@
         </is>
       </c>
       <c r="W98" s="13" t="inlineStr"/>
-      <c r="X98" s="14" t="inlineStr">
-        <is>
-          <t>PRIMARY KEY</t>
-        </is>
-      </c>
+      <c r="X98" s="14" t="inlineStr"/>
       <c r="Y98" s="13" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>number</t>
         </is>
       </c>
       <c r="Z98" s="13" t="inlineStr"/>
@@ -13220,7 +13224,7 @@
       </c>
       <c r="AK98" s="13" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
       <c r="AL98" s="13" t="inlineStr">
@@ -13228,23 +13232,31 @@
           <t>False</t>
         </is>
       </c>
-      <c r="AM98" s="13" t="inlineStr"/>
+      <c r="AM98" s="13" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
       <c r="AN98" s="13" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
       <c r="AO98" s="14" t="inlineStr"/>
-      <c r="AP98" s="14" t="inlineStr"/>
+      <c r="AP98" s="14" t="inlineStr">
+        <is>
+          <t>Генерируется сервером (ЭТАП 2). API-флаги и Pydantic-схемы всей таблицы — ЭТАП 2.</t>
+        </is>
+      </c>
       <c r="AQ98" s="14" t="inlineStr"/>
       <c r="AR98" s="13" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AS98" s="13" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AT98" s="13" t="inlineStr">
@@ -13261,7 +13273,7 @@
     <row r="99">
       <c r="A99" s="13" t="inlineStr">
         <is>
-          <t>ТЗ §3 М4 writeoffs · ADR-2 · ADR-2a</t>
+          <t>спека13 §3 signature_batches</t>
         </is>
       </c>
       <c r="B99" s="13" t="inlineStr"/>
@@ -13272,22 +13284,22 @@
       </c>
       <c r="D99" s="14" t="inlineStr">
         <is>
-          <t>Номер проводки</t>
+          <t>Период с</t>
         </is>
       </c>
       <c r="E99" s="13" t="inlineStr">
         <is>
-          <t>writeoffs.number</t>
+          <t>signature_batches.period_from</t>
         </is>
       </c>
       <c r="G99" s="13" t="inlineStr">
         <is>
-          <t>varchar(32)</t>
+          <t>date</t>
         </is>
       </c>
       <c r="J99" s="14" t="inlineStr">
         <is>
-          <t>СВОЯ, независимая серия — порча/брак заявки не имеют (ADR-2a).</t>
+          <t>Начало периода, за который собрана пачка выдач.</t>
         </is>
       </c>
       <c r="K99" s="13" t="inlineStr">
@@ -13299,15 +13311,11 @@
       <c r="M99" s="13" t="inlineStr"/>
       <c r="N99" s="13" t="inlineStr">
         <is>
-          <t>String(32)</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="O99" s="13" t="inlineStr"/>
-      <c r="P99" s="13" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
+      <c r="P99" s="13" t="inlineStr"/>
       <c r="Q99" s="13" t="inlineStr"/>
       <c r="R99" s="13" t="inlineStr"/>
       <c r="S99" s="13" t="inlineStr">
@@ -13316,23 +13324,15 @@
         </is>
       </c>
       <c r="T99" s="13" t="inlineStr"/>
-      <c r="U99" s="13" t="inlineStr">
-        <is>
-          <t>True (UNIQUE)</t>
-        </is>
-      </c>
-      <c r="V99" s="13" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
+      <c r="U99" s="13" t="inlineStr"/>
+      <c r="V99" s="13" t="inlineStr"/>
       <c r="W99" s="13" t="inlineStr"/>
-      <c r="X99" s="14" t="inlineStr"/>
-      <c r="Y99" s="13" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
+      <c r="X99" s="14" t="inlineStr">
+        <is>
+          <t>CHECK (period_from &lt;= period_to) — ck_signature_batches_period_order</t>
+        </is>
+      </c>
+      <c r="Y99" s="13" t="inlineStr"/>
       <c r="Z99" s="13" t="inlineStr"/>
       <c r="AA99" s="13" t="inlineStr"/>
       <c r="AB99" s="13" t="inlineStr"/>
@@ -13345,12 +13345,12 @@
       <c r="AI99" s="14" t="inlineStr"/>
       <c r="AJ99" s="13" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AK99" s="13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="AL99" s="13" t="inlineStr">
@@ -13358,31 +13358,23 @@
           <t>False</t>
         </is>
       </c>
-      <c r="AM99" s="13" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
+      <c r="AM99" s="13" t="inlineStr"/>
       <c r="AN99" s="13" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
       <c r="AO99" s="14" t="inlineStr"/>
-      <c r="AP99" s="14" t="inlineStr">
-        <is>
-          <t>Второй из двух номеров. В реестре §6.4 показываются оба, поиск по любому (ОВ-6).</t>
-        </is>
-      </c>
+      <c r="AP99" s="14" t="inlineStr"/>
       <c r="AQ99" s="14" t="inlineStr"/>
       <c r="AR99" s="13" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AS99" s="13" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AT99" s="13" t="inlineStr">
@@ -13399,7 +13391,7 @@
     <row r="100">
       <c r="A100" s="13" t="inlineStr">
         <is>
-          <t>ТЗ §3 М4 writeoffs · ADR-2</t>
+          <t>спека13 §3 signature_batches</t>
         </is>
       </c>
       <c r="B100" s="13" t="inlineStr"/>
@@ -13410,12 +13402,12 @@
       </c>
       <c r="D100" s="14" t="inlineStr">
         <is>
-          <t>Дата проводки</t>
+          <t>Период по</t>
         </is>
       </c>
       <c r="E100" s="13" t="inlineStr">
         <is>
-          <t>writeoffs.date</t>
+          <t>signature_batches.period_to</t>
         </is>
       </c>
       <c r="G100" s="13" t="inlineStr">
@@ -13425,7 +13417,7 @@
       </c>
       <c r="J100" s="14" t="inlineStr">
         <is>
-          <t>Дата списания.</t>
+          <t>Конец периода пачки.</t>
         </is>
       </c>
       <c r="K100" s="13" t="inlineStr">
@@ -13450,19 +13442,15 @@
         </is>
       </c>
       <c r="T100" s="13" t="inlineStr"/>
-      <c r="U100" s="13" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
+      <c r="U100" s="13" t="inlineStr"/>
       <c r="V100" s="13" t="inlineStr"/>
       <c r="W100" s="13" t="inlineStr"/>
-      <c r="X100" s="14" t="inlineStr"/>
-      <c r="Y100" s="13" t="inlineStr">
-        <is>
-          <t>date__range</t>
-        </is>
-      </c>
+      <c r="X100" s="14" t="inlineStr">
+        <is>
+          <t>CHECK (period_from &lt;= period_to) — ck_signature_batches_period_order</t>
+        </is>
+      </c>
+      <c r="Y100" s="13" t="inlineStr"/>
       <c r="Z100" s="13" t="inlineStr"/>
       <c r="AA100" s="13" t="inlineStr"/>
       <c r="AB100" s="13" t="inlineStr"/>
@@ -13475,7 +13463,7 @@
       <c r="AI100" s="14" t="inlineStr"/>
       <c r="AJ100" s="13" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AK100" s="13" t="inlineStr">
@@ -13485,31 +13473,31 @@
       </c>
       <c r="AL100" s="13" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AM100" s="13" t="inlineStr"/>
+      <c r="AN100" s="13" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AM100" s="13" t="inlineStr"/>
-      <c r="AN100" s="13" t="inlineStr"/>
       <c r="AO100" s="14" t="inlineStr"/>
-      <c r="AP100" s="14" t="inlineStr">
-        <is>
-          <t>При выдаче проставляется сервером = дата issue(); при порче/браке вводится админом.</t>
-        </is>
-      </c>
+      <c r="AP100" s="14" t="inlineStr"/>
       <c r="AQ100" s="14" t="inlineStr"/>
       <c r="AR100" s="13" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AS100" s="13" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AT100" s="13" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AU100" s="13" t="inlineStr">
@@ -13521,7 +13509,7 @@
     <row r="101">
       <c r="A101" s="13" t="inlineStr">
         <is>
-          <t>ТЗ §3 М4 writeoffs · ADR-2</t>
+          <t>спека13 §3 signature_batches</t>
         </is>
       </c>
       <c r="B101" s="13" t="inlineStr"/>
@@ -13532,12 +13520,12 @@
       </c>
       <c r="D101" s="14" t="inlineStr">
         <is>
-          <t>Склад списания</t>
+          <t>Автор пачки</t>
         </is>
       </c>
       <c r="E101" s="13" t="inlineStr">
         <is>
-          <t>writeoffs.warehouse_id</t>
+          <t>signature_batches.created_by</t>
         </is>
       </c>
       <c r="G101" s="13" t="inlineStr">
@@ -13547,7 +13535,7 @@
       </c>
       <c r="J101" s="14" t="inlineStr">
         <is>
-          <t>Склад, с которого списывается товар.</t>
+          <t>Кто создал пачку (админ). Из JWT.</t>
         </is>
       </c>
       <c r="K101" s="13" t="inlineStr">
@@ -13559,14 +13547,14 @@
       <c r="M101" s="13" t="inlineStr"/>
       <c r="N101" s="13" t="inlineStr">
         <is>
-          <t>BigInteger · ForeignKey('warehouses.id', ondelete='RESTRICT')</t>
+          <t>BigInteger · ForeignKey('users.id', ondelete='RESTRICT')</t>
         </is>
       </c>
       <c r="O101" s="13" t="inlineStr"/>
       <c r="P101" s="13" t="inlineStr"/>
       <c r="Q101" s="13" t="inlineStr">
         <is>
-          <t>relationship Warehouse</t>
+          <t>relationship User</t>
         </is>
       </c>
       <c r="R101" s="13" t="inlineStr"/>
@@ -13581,7 +13569,11 @@
           <t>True (FK)</t>
         </is>
       </c>
-      <c r="V101" s="13" t="inlineStr"/>
+      <c r="V101" s="13" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="W101" s="13" t="inlineStr">
         <is>
           <t>RESTRICT</t>
@@ -13590,15 +13582,11 @@
       <c r="X101" s="14" t="inlineStr"/>
       <c r="Y101" s="13" t="inlineStr">
         <is>
-          <t>warehouse_id</t>
+          <t>created_by</t>
         </is>
       </c>
       <c r="Z101" s="13" t="inlineStr"/>
-      <c r="AA101" s="13" t="inlineStr">
-        <is>
-          <t>GET /warehouses?status=active</t>
-        </is>
-      </c>
+      <c r="AA101" s="13" t="inlineStr"/>
       <c r="AB101" s="13" t="inlineStr"/>
       <c r="AC101" s="13" t="inlineStr"/>
       <c r="AD101" s="13" t="inlineStr"/>
@@ -13609,7 +13597,7 @@
       <c r="AI101" s="14" t="inlineStr"/>
       <c r="AJ101" s="13" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AK101" s="13" t="inlineStr">
@@ -13619,27 +13607,31 @@
       </c>
       <c r="AL101" s="13" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AM101" s="13" t="inlineStr"/>
+      <c r="AN101" s="13" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AM101" s="13" t="inlineStr"/>
-      <c r="AN101" s="13" t="inlineStr"/>
       <c r="AO101" s="14" t="inlineStr"/>
       <c r="AP101" s="14" t="inlineStr"/>
       <c r="AQ101" s="14" t="inlineStr"/>
       <c r="AR101" s="13" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AS101" s="13" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AT101" s="13" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AU101" s="13" t="inlineStr">
@@ -13651,7 +13643,7 @@
     <row r="102">
       <c r="A102" s="13" t="inlineStr">
         <is>
-          <t>ТЗ §3 М4 writeoffs · ADR-2 · INV-4</t>
+          <t>спека13 §3 signature_batches</t>
         </is>
       </c>
       <c r="B102" s="13" t="inlineStr"/>
@@ -13662,22 +13654,22 @@
       </c>
       <c r="D102" s="14" t="inlineStr">
         <is>
-          <t>Тип расхода товара</t>
+          <t>Напечатано</t>
         </is>
       </c>
       <c r="E102" s="13" t="inlineStr">
         <is>
-          <t>writeoffs.expense_type_id</t>
+          <t>signature_batches.printed_at</t>
         </is>
       </c>
       <c r="G102" s="13" t="inlineStr">
         <is>
-          <t>bigint FK</t>
+          <t>timestamptz NULL</t>
         </is>
       </c>
       <c r="J102" s="14" t="inlineStr">
         <is>
-          <t>Выдача сотруднику / Порча / Брак.</t>
+          <t>Момент печати пачки (генерация PDF по сотрудникам). NULL до печати.</t>
         </is>
       </c>
       <c r="K102" s="13" t="inlineStr">
@@ -13689,50 +13681,34 @@
       <c r="M102" s="13" t="inlineStr"/>
       <c r="N102" s="13" t="inlineStr">
         <is>
-          <t>BigInteger · ForeignKey('expense_types.id', ondelete='RESTRICT')</t>
+          <t>DateTime(timezone=True)</t>
         </is>
       </c>
       <c r="O102" s="13" t="inlineStr"/>
       <c r="P102" s="13" t="inlineStr"/>
-      <c r="Q102" s="13" t="inlineStr">
-        <is>
-          <t>relationship ExpenseType</t>
-        </is>
-      </c>
+      <c r="Q102" s="13" t="inlineStr"/>
       <c r="R102" s="13" t="inlineStr"/>
       <c r="S102" s="13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="T102" s="13" t="inlineStr"/>
-      <c r="U102" s="13" t="inlineStr">
-        <is>
-          <t>True (FK)</t>
-        </is>
-      </c>
-      <c r="V102" s="13" t="inlineStr"/>
-      <c r="W102" s="13" t="inlineStr">
-        <is>
-          <t>RESTRICT</t>
-        </is>
-      </c>
-      <c r="X102" s="14" t="inlineStr">
-        <is>
-          <t>INV-4: составной FK (expense_type_id, requires_employee) -&gt; expense_types(id, requires_employee) ON UPDATE CASCADE ON DELETE RESTRICT</t>
-        </is>
-      </c>
+      <c r="U102" s="13" t="inlineStr"/>
+      <c r="V102" s="13" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="W102" s="13" t="inlineStr"/>
+      <c r="X102" s="14" t="inlineStr"/>
       <c r="Y102" s="13" t="inlineStr">
         <is>
-          <t>expense_type_id</t>
+          <t>printed_at__range</t>
         </is>
       </c>
       <c r="Z102" s="13" t="inlineStr"/>
-      <c r="AA102" s="13" t="inlineStr">
-        <is>
-          <t>GET /expense-types?status=active</t>
-        </is>
-      </c>
+      <c r="AA102" s="13" t="inlineStr"/>
       <c r="AB102" s="13" t="inlineStr"/>
       <c r="AC102" s="13" t="inlineStr"/>
       <c r="AD102" s="13" t="inlineStr"/>
@@ -13743,41 +13719,41 @@
       <c r="AI102" s="14" t="inlineStr"/>
       <c r="AJ102" s="13" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AK102" s="13" t="inlineStr">
         <is>
-          <t>select</t>
+          <t>date</t>
         </is>
       </c>
       <c r="AL102" s="13" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AM102" s="13" t="inlineStr"/>
+      <c r="AN102" s="13" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AM102" s="13" t="inlineStr"/>
-      <c r="AN102" s="13" t="inlineStr"/>
-      <c r="AO102" s="14" t="inlineStr">
-        <is>
-          <t>required; при requires_employee=true форма требует сотрудника, иначе — прячет поле</t>
-        </is>
-      </c>
+      <c r="AO102" s="14" t="inlineStr"/>
       <c r="AP102" s="14" t="inlineStr"/>
       <c r="AQ102" s="14" t="inlineStr"/>
       <c r="AR102" s="13" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AS102" s="13" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AT102" s="13" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AU102" s="13" t="inlineStr">
@@ -13789,7 +13765,7 @@
     <row r="103">
       <c r="A103" s="13" t="inlineStr">
         <is>
-          <t>ТЗ §3 М4 writeoffs · ADR-2 · INV-4</t>
+          <t>спека13 §3 signature_batches</t>
         </is>
       </c>
       <c r="B103" s="13" t="inlineStr"/>
@@ -13800,22 +13776,22 @@
       </c>
       <c r="D103" s="14" t="inlineStr">
         <is>
-          <t>Требует сотрудника (копия флага)</t>
+          <t>Подписано</t>
         </is>
       </c>
       <c r="E103" s="13" t="inlineStr">
         <is>
-          <t>writeoffs.requires_employee</t>
+          <t>signature_batches.signed_at</t>
         </is>
       </c>
       <c r="G103" s="13" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>timestamptz NULL</t>
         </is>
       </c>
       <c r="J103" s="14" t="inlineStr">
         <is>
-          <t>Копия expense_types.requires_employee, синхронизируемая составным FK с ON UPDATE CASCADE. Существует ТОЛЬКО чтобы выразить межтабличный INV-4 обычным CHECK.</t>
+          <t>Момент отметки «Пачка подписана» (все заявки пачки issued → signed). NULL до подписи.</t>
         </is>
       </c>
       <c r="K103" s="13" t="inlineStr">
@@ -13827,7 +13803,7 @@
       <c r="M103" s="13" t="inlineStr"/>
       <c r="N103" s="13" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>DateTime(timezone=True)</t>
         </is>
       </c>
       <c r="O103" s="13" t="inlineStr"/>
@@ -13836,27 +13812,23 @@
       <c r="R103" s="13" t="inlineStr"/>
       <c r="S103" s="13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="T103" s="13" t="inlineStr"/>
-      <c r="U103" s="13" t="inlineStr">
-        <is>
-          <t>True (в составе композитного FK)</t>
-        </is>
-      </c>
+      <c r="U103" s="13" t="inlineStr"/>
       <c r="V103" s="13" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
       <c r="W103" s="13" t="inlineStr"/>
-      <c r="X103" s="14" t="inlineStr">
-        <is>
-          <t>INV-4: CHECK ((employee_id IS NOT NULL) = requires_employee)</t>
-        </is>
-      </c>
-      <c r="Y103" s="13" t="inlineStr"/>
+      <c r="X103" s="14" t="inlineStr"/>
+      <c r="Y103" s="13" t="inlineStr">
+        <is>
+          <t>signed_at__range</t>
+        </is>
+      </c>
       <c r="Z103" s="13" t="inlineStr"/>
       <c r="AA103" s="13" t="inlineStr"/>
       <c r="AB103" s="13" t="inlineStr"/>
@@ -13874,7 +13846,7 @@
       </c>
       <c r="AK103" s="13" t="inlineStr">
         <is>
-          <t>checkbox</t>
+          <t>date</t>
         </is>
       </c>
       <c r="AL103" s="13" t="inlineStr">
@@ -13889,11 +13861,7 @@
         </is>
       </c>
       <c r="AO103" s="14" t="inlineStr"/>
-      <c r="AP103" s="14" t="inlineStr">
-        <is>
-          <t>Вторая денормализация, вне AP: обоснование — INV-4 межтабличный, обычный CHECK его не выражает. Заполняется сервером из выбранного expense_type, клиент не присылает. Подробности и альтернатива-триггер — в 02-database.md.</t>
-        </is>
-      </c>
+      <c r="AP103" s="14" t="inlineStr"/>
       <c r="AQ103" s="14" t="inlineStr"/>
       <c r="AR103" s="13" t="inlineStr">
         <is>
@@ -13902,7 +13870,7 @@
       </c>
       <c r="AS103" s="13" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AT103" s="13" t="inlineStr">
@@ -13919,7 +13887,7 @@
     <row r="104">
       <c r="A104" s="13" t="inlineStr">
         <is>
-          <t>ТЗ §3 М4 writeoffs · ADR-2 · INV-4</t>
+          <t>спека13 §3 signature_batches</t>
         </is>
       </c>
       <c r="B104" s="13" t="inlineStr"/>
@@ -13930,22 +13898,22 @@
       </c>
       <c r="D104" s="14" t="inlineStr">
         <is>
-          <t>Сотрудник-получатель</t>
+          <t>PDF пачки</t>
         </is>
       </c>
       <c r="E104" s="13" t="inlineStr">
         <is>
-          <t>writeoffs.employee_id</t>
+          <t>signature_batches.pdf_url</t>
         </is>
       </c>
       <c r="G104" s="13" t="inlineStr">
         <is>
-          <t>bigint FK NULL</t>
+          <t>varchar(500) NULL</t>
         </is>
       </c>
       <c r="J104" s="14" t="inlineStr">
         <is>
-          <t>Получатель при «Выдаче». NULL при «Порче»/«Браке».</t>
+          <t>Ключ объекта в MinIO — один PDF, сгруппированный по сотрудникам. NULL до печати.</t>
         </is>
       </c>
       <c r="K104" s="13" t="inlineStr">
@@ -13957,16 +13925,12 @@
       <c r="M104" s="13" t="inlineStr"/>
       <c r="N104" s="13" t="inlineStr">
         <is>
-          <t>BigInteger · ForeignKey('users.id', ondelete='RESTRICT')</t>
+          <t>String(500)</t>
         </is>
       </c>
       <c r="O104" s="13" t="inlineStr"/>
       <c r="P104" s="13" t="inlineStr"/>
-      <c r="Q104" s="13" t="inlineStr">
-        <is>
-          <t>relationship User</t>
-        </is>
-      </c>
+      <c r="Q104" s="13" t="inlineStr"/>
       <c r="R104" s="13" t="inlineStr"/>
       <c r="S104" s="13" t="inlineStr">
         <is>
@@ -13974,33 +13938,17 @@
         </is>
       </c>
       <c r="T104" s="13" t="inlineStr"/>
-      <c r="U104" s="13" t="inlineStr">
-        <is>
-          <t>True (FK)</t>
-        </is>
-      </c>
-      <c r="V104" s="13" t="inlineStr"/>
-      <c r="W104" s="13" t="inlineStr">
-        <is>
-          <t>RESTRICT</t>
-        </is>
-      </c>
-      <c r="X104" s="14" t="inlineStr">
-        <is>
-          <t>INV-4: CHECK ((employee_id IS NOT NULL) = requires_employee)</t>
-        </is>
-      </c>
-      <c r="Y104" s="13" t="inlineStr">
-        <is>
-          <t>employee_id</t>
-        </is>
-      </c>
+      <c r="U104" s="13" t="inlineStr"/>
+      <c r="V104" s="13" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="W104" s="13" t="inlineStr"/>
+      <c r="X104" s="14" t="inlineStr"/>
+      <c r="Y104" s="13" t="inlineStr"/>
       <c r="Z104" s="13" t="inlineStr"/>
-      <c r="AA104" s="13" t="inlineStr">
-        <is>
-          <t>GET /users?is_active=true&amp;role__in=teacher,worker</t>
-        </is>
-      </c>
+      <c r="AA104" s="13" t="inlineStr"/>
       <c r="AB104" s="13" t="inlineStr"/>
       <c r="AC104" s="13" t="inlineStr"/>
       <c r="AD104" s="13" t="inlineStr"/>
@@ -14011,12 +13959,12 @@
       <c r="AI104" s="14" t="inlineStr"/>
       <c r="AJ104" s="13" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AK104" s="13" t="inlineStr">
         <is>
-          <t>select</t>
+          <t>text</t>
         </is>
       </c>
       <c r="AL104" s="13" t="inlineStr">
@@ -14024,32 +13972,36 @@
           <t>False</t>
         </is>
       </c>
-      <c r="AM104" s="13" t="inlineStr"/>
-      <c r="AN104" s="13" t="inlineStr"/>
-      <c r="AO104" s="14" t="inlineStr">
-        <is>
-          <t>обязателен ⟺ выбранный expense_type.requires_employee = true</t>
-        </is>
-      </c>
+      <c r="AM104" s="13" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="AN104" s="13" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AO104" s="14" t="inlineStr"/>
       <c r="AP104" s="14" t="inlineStr">
         <is>
-          <t>При issue() заполняется из requests.employee_id.</t>
+          <t>Ставит сервер при рендере. Хранится ключ объекта, не публичная ссылка (бакет приватный).</t>
         </is>
       </c>
       <c r="AQ104" s="14" t="inlineStr"/>
       <c r="AR104" s="13" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AS104" s="13" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AT104" s="13" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AU104" s="13" t="inlineStr">
@@ -14061,7 +14013,7 @@
     <row r="105">
       <c r="A105" s="13" t="inlineStr">
         <is>
-          <t>ТЗ §3 М4 writeoffs · ADR-2</t>
+          <t>спека13 §3 signature_batches</t>
         </is>
       </c>
       <c r="B105" s="13" t="inlineStr"/>
@@ -14072,22 +14024,22 @@
       </c>
       <c r="D105" s="14" t="inlineStr">
         <is>
-          <t>Автор проводки</t>
+          <t>Создана</t>
         </is>
       </c>
       <c r="E105" s="13" t="inlineStr">
         <is>
-          <t>writeoffs.author_id</t>
+          <t>signature_batches.created_at</t>
         </is>
       </c>
       <c r="G105" s="13" t="inlineStr">
         <is>
-          <t>bigint FK</t>
+          <t>timestamptz</t>
         </is>
       </c>
       <c r="J105" s="14" t="inlineStr">
         <is>
-          <t>Кто провёл списание (завскладом). Из JWT.</t>
+          <t>Момент создания пачки.</t>
         </is>
       </c>
       <c r="K105" s="13" t="inlineStr">
@@ -14099,42 +14051,38 @@
       <c r="M105" s="13" t="inlineStr"/>
       <c r="N105" s="13" t="inlineStr">
         <is>
-          <t>BigInteger · ForeignKey('users.id', ondelete='RESTRICT')</t>
-        </is>
-      </c>
-      <c r="O105" s="13" t="inlineStr"/>
+          <t>DateTime(timezone=True)</t>
+        </is>
+      </c>
+      <c r="O105" s="13" t="inlineStr">
+        <is>
+          <t>server_default=func.now()</t>
+        </is>
+      </c>
       <c r="P105" s="13" t="inlineStr"/>
-      <c r="Q105" s="13" t="inlineStr">
-        <is>
-          <t>relationship User</t>
-        </is>
-      </c>
+      <c r="Q105" s="13" t="inlineStr"/>
       <c r="R105" s="13" t="inlineStr"/>
       <c r="S105" s="13" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="T105" s="13" t="inlineStr"/>
-      <c r="U105" s="13" t="inlineStr">
-        <is>
-          <t>True (FK)</t>
-        </is>
-      </c>
+      <c r="T105" s="13" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
+      <c r="U105" s="13" t="inlineStr"/>
       <c r="V105" s="13" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="W105" s="13" t="inlineStr">
-        <is>
-          <t>RESTRICT</t>
-        </is>
-      </c>
+      <c r="W105" s="13" t="inlineStr"/>
       <c r="X105" s="14" t="inlineStr"/>
       <c r="Y105" s="13" t="inlineStr">
         <is>
-          <t>author_id</t>
+          <t>created_at__range</t>
         </is>
       </c>
       <c r="Z105" s="13" t="inlineStr"/>
@@ -14149,12 +14097,12 @@
       <c r="AI105" s="14" t="inlineStr"/>
       <c r="AJ105" s="13" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AK105" s="13" t="inlineStr">
         <is>
-          <t>select</t>
+          <t>date</t>
         </is>
       </c>
       <c r="AL105" s="13" t="inlineStr">
@@ -14169,20 +14117,16 @@
         </is>
       </c>
       <c r="AO105" s="14" t="inlineStr"/>
-      <c r="AP105" s="14" t="inlineStr">
-        <is>
-          <t>Отличается от employee_id: автор — завскладом, получатель — сотрудник.</t>
-        </is>
-      </c>
+      <c r="AP105" s="14" t="inlineStr"/>
       <c r="AQ105" s="14" t="inlineStr"/>
       <c r="AR105" s="13" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AS105" s="13" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AT105" s="13" t="inlineStr">
@@ -14199,7 +14143,7 @@
     <row r="106">
       <c r="A106" s="13" t="inlineStr">
         <is>
-          <t>ТЗ §3 М4 writeoff_items</t>
+          <t>ТЗ §3 М4 request_items</t>
         </is>
       </c>
       <c r="B106" s="13" t="inlineStr"/>
@@ -14215,7 +14159,7 @@
       </c>
       <c r="E106" s="13" t="inlineStr">
         <is>
-          <t>writeoff_items.id</t>
+          <t>request_items.id</t>
         </is>
       </c>
       <c r="G106" s="13" t="inlineStr">
@@ -14337,7 +14281,7 @@
     <row r="107">
       <c r="A107" s="13" t="inlineStr">
         <is>
-          <t>ТЗ §3 М4 writeoff_items</t>
+          <t>ТЗ §3 М4 request_items</t>
         </is>
       </c>
       <c r="B107" s="13" t="inlineStr"/>
@@ -14348,12 +14292,12 @@
       </c>
       <c r="D107" s="14" t="inlineStr">
         <is>
-          <t>Проводка</t>
+          <t>Заявка</t>
         </is>
       </c>
       <c r="E107" s="13" t="inlineStr">
         <is>
-          <t>writeoff_items.writeoff_id</t>
+          <t>request_items.request_id</t>
         </is>
       </c>
       <c r="G107" s="13" t="inlineStr">
@@ -14363,7 +14307,7 @@
       </c>
       <c r="J107" s="14" t="inlineStr">
         <is>
-          <t>Родительская проводка списания.</t>
+          <t>Родительская заявка.</t>
         </is>
       </c>
       <c r="K107" s="13" t="inlineStr">
@@ -14375,14 +14319,14 @@
       <c r="M107" s="13" t="inlineStr"/>
       <c r="N107" s="13" t="inlineStr">
         <is>
-          <t>BigInteger · ForeignKey('writeoffs.id', ondelete='CASCADE')</t>
+          <t>BigInteger · ForeignKey('requests.id', ondelete='CASCADE')</t>
         </is>
       </c>
       <c r="O107" s="13" t="inlineStr"/>
       <c r="P107" s="13" t="inlineStr"/>
       <c r="Q107" s="13" t="inlineStr">
         <is>
-          <t>relationship Writeoff</t>
+          <t>relationship Request</t>
         </is>
       </c>
       <c r="R107" s="13" t="inlineStr"/>
@@ -14406,7 +14350,7 @@
       <c r="X107" s="14" t="inlineStr"/>
       <c r="Y107" s="13" t="inlineStr">
         <is>
-          <t>writeoff_id</t>
+          <t>request_id</t>
         </is>
       </c>
       <c r="Z107" s="13" t="inlineStr"/>
@@ -14467,7 +14411,7 @@
     <row r="108">
       <c r="A108" s="13" t="inlineStr">
         <is>
-          <t>ТЗ §3 М4 writeoff_items</t>
+          <t>ТЗ §3 М4 request_items</t>
         </is>
       </c>
       <c r="B108" s="13" t="inlineStr"/>
@@ -14483,7 +14427,7 @@
       </c>
       <c r="E108" s="13" t="inlineStr">
         <is>
-          <t>writeoff_items.product_id</t>
+          <t>request_items.product_id</t>
         </is>
       </c>
       <c r="G108" s="13" t="inlineStr">
@@ -14493,7 +14437,7 @@
       </c>
       <c r="J108" s="14" t="inlineStr">
         <is>
-          <t>Списываемый товар.</t>
+          <t>Запрашиваемый товар.</t>
         </is>
       </c>
       <c r="K108" s="13" t="inlineStr">
@@ -14542,7 +14486,7 @@
       <c r="Z108" s="13" t="inlineStr"/>
       <c r="AA108" s="13" t="inlineStr">
         <is>
-          <t>GET /stock/balances?warehouse_id={warehouse_id}</t>
+          <t>GET /stock/balances?warehouse_id={warehouse_id} (ОВ-5)</t>
         </is>
       </c>
       <c r="AB108" s="13" t="inlineStr"/>
@@ -14597,7 +14541,7 @@
     <row r="109">
       <c r="A109" s="13" t="inlineStr">
         <is>
-          <t>ТЗ §3 М4 writeoff_items</t>
+          <t>ТЗ §3 М4 request_items</t>
         </is>
       </c>
       <c r="B109" s="13" t="inlineStr"/>
@@ -14613,7 +14557,7 @@
       </c>
       <c r="E109" s="13" t="inlineStr">
         <is>
-          <t>writeoff_items.qty</t>
+          <t>request_items.qty</t>
         </is>
       </c>
       <c r="G109" s="13" t="inlineStr">
@@ -14623,7 +14567,7 @@
       </c>
       <c r="J109" s="14" t="inlineStr">
         <is>
-          <t>Списываемое количество (положительное; знак ставит ledger).</t>
+          <t>Запрошенное количество. Переносится в writeoff_items при issue().</t>
         </is>
       </c>
       <c r="K109" s="13" t="inlineStr">
@@ -14686,10 +14630,14 @@
       <c r="AN109" s="13" t="inlineStr"/>
       <c r="AO109" s="14" t="inlineStr">
         <is>
-          <t>required; &gt; 0; ≤ остатка (сервер — истина)</t>
-        </is>
-      </c>
-      <c r="AP109" s="14" t="inlineStr"/>
+          <t>required; &gt; 0</t>
+        </is>
+      </c>
+      <c r="AP109" s="14" t="inlineStr">
+        <is>
+          <t>Резервирования нет (§8, ADR-3): наличие проверяется только в момент issue().</t>
+        </is>
+      </c>
       <c r="AQ109" s="14" t="inlineStr"/>
       <c r="AR109" s="13" t="inlineStr">
         <is>
@@ -14715,7 +14663,7 @@
     <row r="110">
       <c r="A110" s="13" t="inlineStr">
         <is>
-          <t>ТЗ §3 М4 writeoff_items</t>
+          <t>ТЗ §3 М4 writeoffs · ADR-2</t>
         </is>
       </c>
       <c r="B110" s="13" t="inlineStr"/>
@@ -14726,22 +14674,22 @@
       </c>
       <c r="D110" s="14" t="inlineStr">
         <is>
-          <t>Причина</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E110" s="13" t="inlineStr">
         <is>
-          <t>writeoff_items.reason</t>
+          <t>writeoffs.id</t>
         </is>
       </c>
       <c r="G110" s="13" t="inlineStr">
         <is>
-          <t>varchar(500) NULL</t>
+          <t>bigserial</t>
         </is>
       </c>
       <c r="J110" s="14" t="inlineStr">
         <is>
-          <t>Причина списания построчно (актуально для порчи/брака).</t>
+          <t>Суррогатный первичный ключ.</t>
         </is>
       </c>
       <c r="K110" s="13" t="inlineStr">
@@ -14753,24 +14701,48 @@
       <c r="M110" s="13" t="inlineStr"/>
       <c r="N110" s="13" t="inlineStr">
         <is>
-          <t>String(500)</t>
-        </is>
-      </c>
-      <c r="O110" s="13" t="inlineStr"/>
-      <c r="P110" s="13" t="inlineStr"/>
+          <t>BigInteger</t>
+        </is>
+      </c>
+      <c r="O110" s="13" t="inlineStr">
+        <is>
+          <t>autoincrement (Identity)</t>
+        </is>
+      </c>
+      <c r="P110" s="13" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
       <c r="Q110" s="13" t="inlineStr"/>
       <c r="R110" s="13" t="inlineStr"/>
       <c r="S110" s="13" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T110" s="13" t="inlineStr"/>
-      <c r="U110" s="13" t="inlineStr"/>
-      <c r="V110" s="13" t="inlineStr"/>
+      <c r="U110" s="13" t="inlineStr">
+        <is>
+          <t>True (PK)</t>
+        </is>
+      </c>
+      <c r="V110" s="13" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="W110" s="13" t="inlineStr"/>
-      <c r="X110" s="14" t="inlineStr"/>
-      <c r="Y110" s="13" t="inlineStr"/>
+      <c r="X110" s="14" t="inlineStr">
+        <is>
+          <t>PRIMARY KEY</t>
+        </is>
+      </c>
+      <c r="Y110" s="13" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
       <c r="Z110" s="13" t="inlineStr"/>
       <c r="AA110" s="13" t="inlineStr"/>
       <c r="AB110" s="13" t="inlineStr"/>
@@ -14788,7 +14760,7 @@
       </c>
       <c r="AK110" s="13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>number</t>
         </is>
       </c>
       <c r="AL110" s="13" t="inlineStr">
@@ -14796,18 +14768,18 @@
           <t>False</t>
         </is>
       </c>
-      <c r="AM110" s="13" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="AN110" s="13" t="inlineStr"/>
+      <c r="AM110" s="13" t="inlineStr"/>
+      <c r="AN110" s="13" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
       <c r="AO110" s="14" t="inlineStr"/>
       <c r="AP110" s="14" t="inlineStr"/>
       <c r="AQ110" s="14" t="inlineStr"/>
       <c r="AR110" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="AS110" s="13" t="inlineStr">
@@ -14817,7 +14789,7 @@
       </c>
       <c r="AT110" s="13" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AU110" s="13" t="inlineStr">
@@ -14829,7 +14801,7 @@
     <row r="111">
       <c r="A111" s="13" t="inlineStr">
         <is>
-          <t>ТЗ §3 М5 cash_desks · AP-9</t>
+          <t>ТЗ §3 М4 writeoffs · ADR-2 · ADR-2a</t>
         </is>
       </c>
       <c r="B111" s="13" t="inlineStr"/>
@@ -14840,22 +14812,22 @@
       </c>
       <c r="D111" s="14" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>Номер проводки</t>
         </is>
       </c>
       <c r="E111" s="13" t="inlineStr">
         <is>
-          <t>cash_desks.id</t>
+          <t>writeoffs.number</t>
         </is>
       </c>
       <c r="G111" s="13" t="inlineStr">
         <is>
-          <t>bigserial</t>
+          <t>varchar(32)</t>
         </is>
       </c>
       <c r="J111" s="14" t="inlineStr">
         <is>
-          <t>Суррогатный первичный ключ.</t>
+          <t>СВОЯ, независимая серия — порча/брак заявки не имеют (ADR-2a).</t>
         </is>
       </c>
       <c r="K111" s="13" t="inlineStr">
@@ -14867,14 +14839,10 @@
       <c r="M111" s="13" t="inlineStr"/>
       <c r="N111" s="13" t="inlineStr">
         <is>
-          <t>BigInteger</t>
-        </is>
-      </c>
-      <c r="O111" s="13" t="inlineStr">
-        <is>
-          <t>autoincrement (Identity)</t>
-        </is>
-      </c>
+          <t>String(32)</t>
+        </is>
+      </c>
+      <c r="O111" s="13" t="inlineStr"/>
       <c r="P111" s="13" t="inlineStr">
         <is>
           <t>True</t>
@@ -14890,7 +14858,7 @@
       <c r="T111" s="13" t="inlineStr"/>
       <c r="U111" s="13" t="inlineStr">
         <is>
-          <t>True (PK)</t>
+          <t>True (UNIQUE)</t>
         </is>
       </c>
       <c r="V111" s="13" t="inlineStr">
@@ -14899,14 +14867,10 @@
         </is>
       </c>
       <c r="W111" s="13" t="inlineStr"/>
-      <c r="X111" s="14" t="inlineStr">
-        <is>
-          <t>PRIMARY KEY</t>
-        </is>
-      </c>
+      <c r="X111" s="14" t="inlineStr"/>
       <c r="Y111" s="13" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>number</t>
         </is>
       </c>
       <c r="Z111" s="13" t="inlineStr"/>
@@ -14921,12 +14885,12 @@
       <c r="AI111" s="14" t="inlineStr"/>
       <c r="AJ111" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="AK111" s="13" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
       <c r="AL111" s="13" t="inlineStr">
@@ -14934,14 +14898,22 @@
           <t>False</t>
         </is>
       </c>
-      <c r="AM111" s="13" t="inlineStr"/>
+      <c r="AM111" s="13" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
       <c r="AN111" s="13" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
       <c r="AO111" s="14" t="inlineStr"/>
-      <c r="AP111" s="14" t="inlineStr"/>
+      <c r="AP111" s="14" t="inlineStr">
+        <is>
+          <t>Второй из двух номеров. В реестре §6.4 показываются оба, поиск по любому (ОВ-6).</t>
+        </is>
+      </c>
       <c r="AQ111" s="14" t="inlineStr"/>
       <c r="AR111" s="13" t="inlineStr">
         <is>
@@ -14967,7 +14939,7 @@
     <row r="112">
       <c r="A112" s="13" t="inlineStr">
         <is>
-          <t>ТЗ §3 М5 cash_desks · AP-9</t>
+          <t>ТЗ §3 М4 writeoffs · ADR-2</t>
         </is>
       </c>
       <c r="B112" s="13" t="inlineStr"/>
@@ -14978,22 +14950,22 @@
       </c>
       <c r="D112" s="14" t="inlineStr">
         <is>
-          <t>Касса</t>
+          <t>Дата проводки</t>
         </is>
       </c>
       <c r="E112" s="13" t="inlineStr">
         <is>
-          <t>cash_desks.type</t>
+          <t>writeoffs.date</t>
         </is>
       </c>
       <c r="G112" s="13" t="inlineStr">
         <is>
-          <t>enum UNIQUE</t>
+          <t>date</t>
         </is>
       </c>
       <c r="J112" s="14" t="inlineStr">
         <is>
-          <t>teacher | worker. Ровно две строки (seed). UNIQUE гарантирует, что третьей кассы не появится.</t>
+          <t>Дата списания.</t>
         </is>
       </c>
       <c r="K112" s="13" t="inlineStr">
@@ -15005,25 +14977,13 @@
       <c r="M112" s="13" t="inlineStr"/>
       <c r="N112" s="13" t="inlineStr">
         <is>
-          <t>SAEnum(CashDeskType, name='cash_desk_type')</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="O112" s="13" t="inlineStr"/>
-      <c r="P112" s="13" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="Q112" s="13" t="inlineStr">
-        <is>
-          <t>CashDeskType(str, Enum)</t>
-        </is>
-      </c>
-      <c r="R112" s="13" t="inlineStr">
-        <is>
-          <t>teacher | worker</t>
-        </is>
-      </c>
+      <c r="P112" s="13" t="inlineStr"/>
+      <c r="Q112" s="13" t="inlineStr"/>
+      <c r="R112" s="13" t="inlineStr"/>
       <c r="S112" s="13" t="inlineStr">
         <is>
           <t>False</t>
@@ -15032,7 +14992,7 @@
       <c r="T112" s="13" t="inlineStr"/>
       <c r="U112" s="13" t="inlineStr">
         <is>
-          <t>True (UNIQUE)</t>
+          <t>True</t>
         </is>
       </c>
       <c r="V112" s="13" t="inlineStr"/>
@@ -15040,16 +15000,12 @@
       <c r="X112" s="14" t="inlineStr"/>
       <c r="Y112" s="13" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>date__range</t>
         </is>
       </c>
       <c r="Z112" s="13" t="inlineStr"/>
       <c r="AA112" s="13" t="inlineStr"/>
-      <c r="AB112" s="13" t="inlineStr">
-        <is>
-          <t>teacher | worker</t>
-        </is>
-      </c>
+      <c r="AB112" s="13" t="inlineStr"/>
       <c r="AC112" s="13" t="inlineStr"/>
       <c r="AD112" s="13" t="inlineStr"/>
       <c r="AE112" s="13" t="inlineStr"/>
@@ -15064,24 +15020,20 @@
       </c>
       <c r="AK112" s="13" t="inlineStr">
         <is>
-          <t>select</t>
+          <t>date</t>
         </is>
       </c>
       <c r="AL112" s="13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AM112" s="13" t="inlineStr"/>
-      <c r="AN112" s="13" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
+      <c r="AN112" s="13" t="inlineStr"/>
       <c r="AO112" s="14" t="inlineStr"/>
       <c r="AP112" s="14" t="inlineStr">
         <is>
-          <t>SV-6: касса выводится сервером из users.category, клиент её не выбирает.</t>
+          <t>При выдаче проставляется сервером = дата issue(); при порче/браке вводится админом.</t>
         </is>
       </c>
       <c r="AQ112" s="14" t="inlineStr"/>
@@ -15097,7 +15049,7 @@
       </c>
       <c r="AT112" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="AU112" s="13" t="inlineStr">
@@ -15109,7 +15061,7 @@
     <row r="113">
       <c r="A113" s="13" t="inlineStr">
         <is>
-          <t>ТЗ §3 М5 cash_desks · AP-9 · INV-8 · ОВ-2</t>
+          <t>ТЗ §3 М4 writeoffs · ADR-2</t>
         </is>
       </c>
       <c r="B113" s="13" t="inlineStr"/>
@@ -15120,22 +15072,22 @@
       </c>
       <c r="D113" s="14" t="inlineStr">
         <is>
-          <t>Баланс кассы</t>
+          <t>Склад списания</t>
         </is>
       </c>
       <c r="E113" s="13" t="inlineStr">
         <is>
-          <t>cash_desks.balance</t>
+          <t>writeoffs.warehouse_id</t>
         </is>
       </c>
       <c r="G113" s="13" t="inlineStr">
         <is>
-          <t>numeric(18,2)</t>
+          <t>bigint FK</t>
         </is>
       </c>
       <c r="J113" s="14" t="inlineStr">
         <is>
-          <t>Текущий остаток кассы, UZS. Обновляется в TX под FOR UPDATE (AP-9).</t>
+          <t>Склад, с которого списывается товар.</t>
         </is>
       </c>
       <c r="K113" s="13" t="inlineStr">
@@ -15147,38 +15099,46 @@
       <c r="M113" s="13" t="inlineStr"/>
       <c r="N113" s="13" t="inlineStr">
         <is>
-          <t>Numeric(18, 2)</t>
+          <t>BigInteger · ForeignKey('warehouses.id', ondelete='RESTRICT')</t>
         </is>
       </c>
       <c r="O113" s="13" t="inlineStr"/>
       <c r="P113" s="13" t="inlineStr"/>
-      <c r="Q113" s="13" t="inlineStr"/>
+      <c r="Q113" s="13" t="inlineStr">
+        <is>
+          <t>relationship Warehouse</t>
+        </is>
+      </c>
       <c r="R113" s="13" t="inlineStr"/>
       <c r="S113" s="13" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="T113" s="13" t="inlineStr">
-        <is>
-          <t>0 (server_default='0')</t>
-        </is>
-      </c>
-      <c r="U113" s="13" t="inlineStr"/>
-      <c r="V113" s="13" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="W113" s="13" t="inlineStr"/>
-      <c r="X113" s="14" t="inlineStr">
-        <is>
-          <t>INV-8: CHECK (balance &gt;= 0) — по допущению ОВ-2 (жёсткая блокировка)</t>
-        </is>
-      </c>
-      <c r="Y113" s="13" t="inlineStr"/>
+      <c r="T113" s="13" t="inlineStr"/>
+      <c r="U113" s="13" t="inlineStr">
+        <is>
+          <t>True (FK)</t>
+        </is>
+      </c>
+      <c r="V113" s="13" t="inlineStr"/>
+      <c r="W113" s="13" t="inlineStr">
+        <is>
+          <t>RESTRICT</t>
+        </is>
+      </c>
+      <c r="X113" s="14" t="inlineStr"/>
+      <c r="Y113" s="13" t="inlineStr">
+        <is>
+          <t>warehouse_id</t>
+        </is>
+      </c>
       <c r="Z113" s="13" t="inlineStr"/>
-      <c r="AA113" s="13" t="inlineStr"/>
+      <c r="AA113" s="13" t="inlineStr">
+        <is>
+          <t>GET /warehouses?status=active</t>
+        </is>
+      </c>
       <c r="AB113" s="13" t="inlineStr"/>
       <c r="AC113" s="13" t="inlineStr"/>
       <c r="AD113" s="13" t="inlineStr"/>
@@ -15194,26 +15154,18 @@
       </c>
       <c r="AK113" s="13" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>select</t>
         </is>
       </c>
       <c r="AL113" s="13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AM113" s="13" t="inlineStr"/>
-      <c r="AN113" s="13" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
+      <c r="AN113" s="13" t="inlineStr"/>
       <c r="AO113" s="14" t="inlineStr"/>
-      <c r="AP113" s="14" t="inlineStr">
-        <is>
-          <t>ОВ-2 ОТКРЫТ: CHECK поставлен по принятому допущению «жёсткая блокировка». Если заказчик выберет режим предупреждения (CASH_OVERDRAFT_MODE=warn), CHECK придётся снять отдельной миграцией — единственное место, где ОВ-2 всё-таки касается схемы.</t>
-        </is>
-      </c>
+      <c r="AP113" s="14" t="inlineStr"/>
       <c r="AQ113" s="14" t="inlineStr"/>
       <c r="AR113" s="13" t="inlineStr">
         <is>
@@ -15227,7 +15179,7 @@
       </c>
       <c r="AT113" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="AU113" s="13" t="inlineStr">
@@ -15239,7 +15191,7 @@
     <row r="114">
       <c r="A114" s="13" t="inlineStr">
         <is>
-          <t>ТЗ §3 М5 money_income</t>
+          <t>ТЗ §3 М4 writeoffs · ADR-2 · INV-4</t>
         </is>
       </c>
       <c r="B114" s="13" t="inlineStr"/>
@@ -15250,22 +15202,22 @@
       </c>
       <c r="D114" s="14" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>Тип расхода товара</t>
         </is>
       </c>
       <c r="E114" s="13" t="inlineStr">
         <is>
-          <t>money_income.id</t>
+          <t>writeoffs.expense_type_id</t>
         </is>
       </c>
       <c r="G114" s="13" t="inlineStr">
         <is>
-          <t>bigserial</t>
+          <t>bigint FK</t>
         </is>
       </c>
       <c r="J114" s="14" t="inlineStr">
         <is>
-          <t>Суррогатный первичный ключ.</t>
+          <t>Выдача сотруднику / Порча / Брак.</t>
         </is>
       </c>
       <c r="K114" s="13" t="inlineStr">
@@ -15277,20 +15229,16 @@
       <c r="M114" s="13" t="inlineStr"/>
       <c r="N114" s="13" t="inlineStr">
         <is>
-          <t>BigInteger</t>
-        </is>
-      </c>
-      <c r="O114" s="13" t="inlineStr">
-        <is>
-          <t>autoincrement (Identity)</t>
-        </is>
-      </c>
-      <c r="P114" s="13" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="Q114" s="13" t="inlineStr"/>
+          <t>BigInteger · ForeignKey('expense_types.id', ondelete='RESTRICT')</t>
+        </is>
+      </c>
+      <c r="O114" s="13" t="inlineStr"/>
+      <c r="P114" s="13" t="inlineStr"/>
+      <c r="Q114" s="13" t="inlineStr">
+        <is>
+          <t>relationship ExpenseType</t>
+        </is>
+      </c>
       <c r="R114" s="13" t="inlineStr"/>
       <c r="S114" s="13" t="inlineStr">
         <is>
@@ -15300,27 +15248,31 @@
       <c r="T114" s="13" t="inlineStr"/>
       <c r="U114" s="13" t="inlineStr">
         <is>
-          <t>True (PK)</t>
-        </is>
-      </c>
-      <c r="V114" s="13" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="W114" s="13" t="inlineStr"/>
+          <t>True (FK)</t>
+        </is>
+      </c>
+      <c r="V114" s="13" t="inlineStr"/>
+      <c r="W114" s="13" t="inlineStr">
+        <is>
+          <t>RESTRICT</t>
+        </is>
+      </c>
       <c r="X114" s="14" t="inlineStr">
         <is>
-          <t>PRIMARY KEY</t>
+          <t>INV-4: составной FK (expense_type_id, requires_employee) -&gt; expense_types(id, requires_employee) ON UPDATE CASCADE ON DELETE RESTRICT</t>
         </is>
       </c>
       <c r="Y114" s="13" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>expense_type_id</t>
         </is>
       </c>
       <c r="Z114" s="13" t="inlineStr"/>
-      <c r="AA114" s="13" t="inlineStr"/>
+      <c r="AA114" s="13" t="inlineStr">
+        <is>
+          <t>GET /expense-types?status=active</t>
+        </is>
+      </c>
       <c r="AB114" s="13" t="inlineStr"/>
       <c r="AC114" s="13" t="inlineStr"/>
       <c r="AD114" s="13" t="inlineStr"/>
@@ -15331,26 +15283,26 @@
       <c r="AI114" s="14" t="inlineStr"/>
       <c r="AJ114" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="AK114" s="13" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>select</t>
         </is>
       </c>
       <c r="AL114" s="13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AM114" s="13" t="inlineStr"/>
-      <c r="AN114" s="13" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AO114" s="14" t="inlineStr"/>
+      <c r="AN114" s="13" t="inlineStr"/>
+      <c r="AO114" s="14" t="inlineStr">
+        <is>
+          <t>required; при requires_employee=true форма требует сотрудника, иначе — прячет поле</t>
+        </is>
+      </c>
       <c r="AP114" s="14" t="inlineStr"/>
       <c r="AQ114" s="14" t="inlineStr"/>
       <c r="AR114" s="13" t="inlineStr">
@@ -15365,7 +15317,7 @@
       </c>
       <c r="AT114" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="AU114" s="13" t="inlineStr">
@@ -15377,7 +15329,7 @@
     <row r="115">
       <c r="A115" s="13" t="inlineStr">
         <is>
-          <t>ТЗ §3 М5 money_income</t>
+          <t>ТЗ §3 М4 writeoffs · ADR-2 · INV-4</t>
         </is>
       </c>
       <c r="B115" s="13" t="inlineStr"/>
@@ -15388,22 +15340,22 @@
       </c>
       <c r="D115" s="14" t="inlineStr">
         <is>
-          <t>Касса</t>
+          <t>Требует сотрудника (копия флага)</t>
         </is>
       </c>
       <c r="E115" s="13" t="inlineStr">
         <is>
-          <t>money_income.cash_desk_id</t>
+          <t>writeoffs.requires_employee</t>
         </is>
       </c>
       <c r="G115" s="13" t="inlineStr">
         <is>
-          <t>bigint FK</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="J115" s="14" t="inlineStr">
         <is>
-          <t>Пополняемая касса.</t>
+          <t>Копия expense_types.requires_employee, синхронизируемая составным FK с ON UPDATE CASCADE. Существует ТОЛЬКО чтобы выразить межтабличный INV-4 обычным CHECK.</t>
         </is>
       </c>
       <c r="K115" s="13" t="inlineStr">
@@ -15415,16 +15367,12 @@
       <c r="M115" s="13" t="inlineStr"/>
       <c r="N115" s="13" t="inlineStr">
         <is>
-          <t>BigInteger · ForeignKey('cash_desks.id', ondelete='RESTRICT')</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="O115" s="13" t="inlineStr"/>
       <c r="P115" s="13" t="inlineStr"/>
-      <c r="Q115" s="13" t="inlineStr">
-        <is>
-          <t>relationship CashDesk</t>
-        </is>
-      </c>
+      <c r="Q115" s="13" t="inlineStr"/>
       <c r="R115" s="13" t="inlineStr"/>
       <c r="S115" s="13" t="inlineStr">
         <is>
@@ -15434,27 +15382,23 @@
       <c r="T115" s="13" t="inlineStr"/>
       <c r="U115" s="13" t="inlineStr">
         <is>
-          <t>True (FK)</t>
-        </is>
-      </c>
-      <c r="V115" s="13" t="inlineStr"/>
-      <c r="W115" s="13" t="inlineStr">
-        <is>
-          <t>RESTRICT</t>
-        </is>
-      </c>
-      <c r="X115" s="14" t="inlineStr"/>
-      <c r="Y115" s="13" t="inlineStr">
-        <is>
-          <t>cash_desk_id</t>
-        </is>
-      </c>
+          <t>True (в составе композитного FK)</t>
+        </is>
+      </c>
+      <c r="V115" s="13" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="W115" s="13" t="inlineStr"/>
+      <c r="X115" s="14" t="inlineStr">
+        <is>
+          <t>INV-4: CHECK ((employee_id IS NOT NULL) = requires_employee)</t>
+        </is>
+      </c>
+      <c r="Y115" s="13" t="inlineStr"/>
       <c r="Z115" s="13" t="inlineStr"/>
-      <c r="AA115" s="13" t="inlineStr">
-        <is>
-          <t>GET /cash/desks</t>
-        </is>
-      </c>
+      <c r="AA115" s="13" t="inlineStr"/>
       <c r="AB115" s="13" t="inlineStr"/>
       <c r="AC115" s="13" t="inlineStr"/>
       <c r="AD115" s="13" t="inlineStr"/>
@@ -15465,31 +15409,35 @@
       <c r="AI115" s="14" t="inlineStr"/>
       <c r="AJ115" s="13" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AK115" s="13" t="inlineStr">
         <is>
-          <t>select</t>
+          <t>checkbox</t>
         </is>
       </c>
       <c r="AL115" s="13" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AM115" s="13" t="inlineStr"/>
+      <c r="AN115" s="13" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AM115" s="13" t="inlineStr"/>
-      <c r="AN115" s="13" t="inlineStr"/>
       <c r="AO115" s="14" t="inlineStr"/>
       <c r="AP115" s="14" t="inlineStr">
         <is>
-          <t>Приход — только admin (§6 API), поэтому кассу здесь выбирают явно (в отличие от расхода, SV-6).</t>
+          <t>Вторая денормализация, вне AP: обоснование — INV-4 межтабличный, обычный CHECK его не выражает. Заполняется сервером из выбранного expense_type, клиент не присылает. Подробности и альтернатива-триггер — в 02-database.md.</t>
         </is>
       </c>
       <c r="AQ115" s="14" t="inlineStr"/>
       <c r="AR115" s="13" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AS115" s="13" t="inlineStr">
@@ -15499,7 +15447,7 @@
       </c>
       <c r="AT115" s="13" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AU115" s="13" t="inlineStr">
@@ -15511,7 +15459,7 @@
     <row r="116">
       <c r="A116" s="13" t="inlineStr">
         <is>
-          <t>ТЗ §3 М5 money_income</t>
+          <t>ТЗ §3 М4 writeoffs · ADR-2 · INV-4</t>
         </is>
       </c>
       <c r="B116" s="13" t="inlineStr"/>
@@ -15522,22 +15470,22 @@
       </c>
       <c r="D116" s="14" t="inlineStr">
         <is>
-          <t>Сумма прихода</t>
+          <t>Сотрудник-получатель</t>
         </is>
       </c>
       <c r="E116" s="13" t="inlineStr">
         <is>
-          <t>money_income.amount</t>
+          <t>writeoffs.employee_id</t>
         </is>
       </c>
       <c r="G116" s="13" t="inlineStr">
         <is>
-          <t>numeric(18,2)</t>
+          <t>bigint FK NULL</t>
         </is>
       </c>
       <c r="J116" s="14" t="inlineStr">
         <is>
-          <t>Сумма пополнения, UZS. Деньги — только NUMERIC, никогда float.</t>
+          <t>Получатель при «Выдаче». NULL при «Порче»/«Браке».</t>
         </is>
       </c>
       <c r="K116" s="13" t="inlineStr">
@@ -15549,30 +15497,50 @@
       <c r="M116" s="13" t="inlineStr"/>
       <c r="N116" s="13" t="inlineStr">
         <is>
-          <t>Numeric(18, 2)</t>
+          <t>BigInteger · ForeignKey('users.id', ondelete='RESTRICT')</t>
         </is>
       </c>
       <c r="O116" s="13" t="inlineStr"/>
       <c r="P116" s="13" t="inlineStr"/>
-      <c r="Q116" s="13" t="inlineStr"/>
+      <c r="Q116" s="13" t="inlineStr">
+        <is>
+          <t>relationship User</t>
+        </is>
+      </c>
       <c r="R116" s="13" t="inlineStr"/>
       <c r="S116" s="13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="T116" s="13" t="inlineStr"/>
-      <c r="U116" s="13" t="inlineStr"/>
+      <c r="U116" s="13" t="inlineStr">
+        <is>
+          <t>True (FK)</t>
+        </is>
+      </c>
       <c r="V116" s="13" t="inlineStr"/>
-      <c r="W116" s="13" t="inlineStr"/>
+      <c r="W116" s="13" t="inlineStr">
+        <is>
+          <t>RESTRICT</t>
+        </is>
+      </c>
       <c r="X116" s="14" t="inlineStr">
         <is>
-          <t>CHECK (amount &gt; 0)</t>
-        </is>
-      </c>
-      <c r="Y116" s="13" t="inlineStr"/>
+          <t>INV-4: CHECK ((employee_id IS NOT NULL) = requires_employee)</t>
+        </is>
+      </c>
+      <c r="Y116" s="13" t="inlineStr">
+        <is>
+          <t>employee_id</t>
+        </is>
+      </c>
       <c r="Z116" s="13" t="inlineStr"/>
-      <c r="AA116" s="13" t="inlineStr"/>
+      <c r="AA116" s="13" t="inlineStr">
+        <is>
+          <t>GET /users?is_active=true&amp;role__in=teacher,worker</t>
+        </is>
+      </c>
       <c r="AB116" s="13" t="inlineStr"/>
       <c r="AC116" s="13" t="inlineStr"/>
       <c r="AD116" s="13" t="inlineStr"/>
@@ -15588,22 +15556,26 @@
       </c>
       <c r="AK116" s="13" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>select</t>
         </is>
       </c>
       <c r="AL116" s="13" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AM116" s="13" t="inlineStr"/>
       <c r="AN116" s="13" t="inlineStr"/>
       <c r="AO116" s="14" t="inlineStr">
         <is>
-          <t>required; &gt; 0; 2 знака; UZS</t>
-        </is>
-      </c>
-      <c r="AP116" s="14" t="inlineStr"/>
+          <t>обязателен ⟺ выбранный expense_type.requires_employee = true</t>
+        </is>
+      </c>
+      <c r="AP116" s="14" t="inlineStr">
+        <is>
+          <t>При issue() заполняется из requests.employee_id.</t>
+        </is>
+      </c>
       <c r="AQ116" s="14" t="inlineStr"/>
       <c r="AR116" s="13" t="inlineStr">
         <is>
@@ -15629,7 +15601,7 @@
     <row r="117">
       <c r="A117" s="13" t="inlineStr">
         <is>
-          <t>ТЗ §3 М5 money_income</t>
+          <t>ТЗ §3 М4 writeoffs · ADR-2</t>
         </is>
       </c>
       <c r="B117" s="13" t="inlineStr"/>
@@ -15640,22 +15612,22 @@
       </c>
       <c r="D117" s="14" t="inlineStr">
         <is>
-          <t>Дата</t>
+          <t>Автор проводки</t>
         </is>
       </c>
       <c r="E117" s="13" t="inlineStr">
         <is>
-          <t>money_income.date</t>
+          <t>writeoffs.author_id</t>
         </is>
       </c>
       <c r="G117" s="13" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>bigint FK</t>
         </is>
       </c>
       <c r="J117" s="14" t="inlineStr">
         <is>
-          <t>Дата прихода.</t>
+          <t>Кто провёл списание (завскладом). Из JWT.</t>
         </is>
       </c>
       <c r="K117" s="13" t="inlineStr">
@@ -15667,12 +15639,16 @@
       <c r="M117" s="13" t="inlineStr"/>
       <c r="N117" s="13" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>BigInteger · ForeignKey('users.id', ondelete='RESTRICT')</t>
         </is>
       </c>
       <c r="O117" s="13" t="inlineStr"/>
       <c r="P117" s="13" t="inlineStr"/>
-      <c r="Q117" s="13" t="inlineStr"/>
+      <c r="Q117" s="13" t="inlineStr">
+        <is>
+          <t>relationship User</t>
+        </is>
+      </c>
       <c r="R117" s="13" t="inlineStr"/>
       <c r="S117" s="13" t="inlineStr">
         <is>
@@ -15682,15 +15658,23 @@
       <c r="T117" s="13" t="inlineStr"/>
       <c r="U117" s="13" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="V117" s="13" t="inlineStr"/>
-      <c r="W117" s="13" t="inlineStr"/>
+          <t>True (FK)</t>
+        </is>
+      </c>
+      <c r="V117" s="13" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="W117" s="13" t="inlineStr">
+        <is>
+          <t>RESTRICT</t>
+        </is>
+      </c>
       <c r="X117" s="14" t="inlineStr"/>
       <c r="Y117" s="13" t="inlineStr">
         <is>
-          <t>date__range</t>
+          <t>author_id</t>
         </is>
       </c>
       <c r="Z117" s="13" t="inlineStr"/>
@@ -15710,18 +15694,26 @@
       </c>
       <c r="AK117" s="13" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select</t>
         </is>
       </c>
       <c r="AL117" s="13" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AM117" s="13" t="inlineStr"/>
+      <c r="AN117" s="13" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AM117" s="13" t="inlineStr"/>
-      <c r="AN117" s="13" t="inlineStr"/>
       <c r="AO117" s="14" t="inlineStr"/>
-      <c r="AP117" s="14" t="inlineStr"/>
+      <c r="AP117" s="14" t="inlineStr">
+        <is>
+          <t>Отличается от employee_id: автор — завскладом, получатель — сотрудник.</t>
+        </is>
+      </c>
       <c r="AQ117" s="14" t="inlineStr"/>
       <c r="AR117" s="13" t="inlineStr">
         <is>
@@ -15735,7 +15727,7 @@
       </c>
       <c r="AT117" s="13" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AU117" s="13" t="inlineStr">
@@ -15747,7 +15739,7 @@
     <row r="118">
       <c r="A118" s="13" t="inlineStr">
         <is>
-          <t>ТЗ §3 М5 money_income</t>
+          <t>ТЗ §3 М4 writeoff_items</t>
         </is>
       </c>
       <c r="B118" s="13" t="inlineStr"/>
@@ -15758,22 +15750,22 @@
       </c>
       <c r="D118" s="14" t="inlineStr">
         <is>
-          <t>Автор</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E118" s="13" t="inlineStr">
         <is>
-          <t>money_income.author_id</t>
+          <t>writeoff_items.id</t>
         </is>
       </c>
       <c r="G118" s="13" t="inlineStr">
         <is>
-          <t>bigint FK</t>
+          <t>bigserial</t>
         </is>
       </c>
       <c r="J118" s="14" t="inlineStr">
         <is>
-          <t>Администратор, проведший приход. Из JWT.</t>
+          <t>Суррогатный первичный ключ.</t>
         </is>
       </c>
       <c r="K118" s="13" t="inlineStr">
@@ -15785,16 +15777,20 @@
       <c r="M118" s="13" t="inlineStr"/>
       <c r="N118" s="13" t="inlineStr">
         <is>
-          <t>BigInteger · ForeignKey('users.id', ondelete='RESTRICT')</t>
-        </is>
-      </c>
-      <c r="O118" s="13" t="inlineStr"/>
-      <c r="P118" s="13" t="inlineStr"/>
-      <c r="Q118" s="13" t="inlineStr">
-        <is>
-          <t>relationship User</t>
-        </is>
-      </c>
+          <t>BigInteger</t>
+        </is>
+      </c>
+      <c r="O118" s="13" t="inlineStr">
+        <is>
+          <t>autoincrement (Identity)</t>
+        </is>
+      </c>
+      <c r="P118" s="13" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Q118" s="13" t="inlineStr"/>
       <c r="R118" s="13" t="inlineStr"/>
       <c r="S118" s="13" t="inlineStr">
         <is>
@@ -15804,7 +15800,7 @@
       <c r="T118" s="13" t="inlineStr"/>
       <c r="U118" s="13" t="inlineStr">
         <is>
-          <t>True (FK)</t>
+          <t>True (PK)</t>
         </is>
       </c>
       <c r="V118" s="13" t="inlineStr">
@@ -15812,15 +15808,15 @@
           <t>False</t>
         </is>
       </c>
-      <c r="W118" s="13" t="inlineStr">
-        <is>
-          <t>RESTRICT</t>
-        </is>
-      </c>
-      <c r="X118" s="14" t="inlineStr"/>
+      <c r="W118" s="13" t="inlineStr"/>
+      <c r="X118" s="14" t="inlineStr">
+        <is>
+          <t>PRIMARY KEY</t>
+        </is>
+      </c>
       <c r="Y118" s="13" t="inlineStr">
         <is>
-          <t>author_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="Z118" s="13" t="inlineStr"/>
@@ -15835,12 +15831,12 @@
       <c r="AI118" s="14" t="inlineStr"/>
       <c r="AJ118" s="13" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AK118" s="13" t="inlineStr">
         <is>
-          <t>select</t>
+          <t>number</t>
         </is>
       </c>
       <c r="AL118" s="13" t="inlineStr">
@@ -15881,7 +15877,7 @@
     <row r="119">
       <c r="A119" s="13" t="inlineStr">
         <is>
-          <t>ТЗ §3 М5 money_income</t>
+          <t>ТЗ §3 М4 writeoff_items</t>
         </is>
       </c>
       <c r="B119" s="13" t="inlineStr"/>
@@ -15892,22 +15888,22 @@
       </c>
       <c r="D119" s="14" t="inlineStr">
         <is>
-          <t>Комментарий</t>
+          <t>Проводка</t>
         </is>
       </c>
       <c r="E119" s="13" t="inlineStr">
         <is>
-          <t>money_income.comment</t>
+          <t>writeoff_items.writeoff_id</t>
         </is>
       </c>
       <c r="G119" s="13" t="inlineStr">
         <is>
-          <t>varchar(500) NULL</t>
+          <t>bigint FK</t>
         </is>
       </c>
       <c r="J119" s="14" t="inlineStr">
         <is>
-          <t>Основание пополнения.</t>
+          <t>Родительская проводка списания.</t>
         </is>
       </c>
       <c r="K119" s="13" t="inlineStr">
@@ -15919,24 +15915,40 @@
       <c r="M119" s="13" t="inlineStr"/>
       <c r="N119" s="13" t="inlineStr">
         <is>
-          <t>String(500)</t>
+          <t>BigInteger · ForeignKey('writeoffs.id', ondelete='CASCADE')</t>
         </is>
       </c>
       <c r="O119" s="13" t="inlineStr"/>
       <c r="P119" s="13" t="inlineStr"/>
-      <c r="Q119" s="13" t="inlineStr"/>
+      <c r="Q119" s="13" t="inlineStr">
+        <is>
+          <t>relationship Writeoff</t>
+        </is>
+      </c>
       <c r="R119" s="13" t="inlineStr"/>
       <c r="S119" s="13" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T119" s="13" t="inlineStr"/>
-      <c r="U119" s="13" t="inlineStr"/>
+      <c r="U119" s="13" t="inlineStr">
+        <is>
+          <t>True (FK)</t>
+        </is>
+      </c>
       <c r="V119" s="13" t="inlineStr"/>
-      <c r="W119" s="13" t="inlineStr"/>
+      <c r="W119" s="13" t="inlineStr">
+        <is>
+          <t>CASCADE</t>
+        </is>
+      </c>
       <c r="X119" s="14" t="inlineStr"/>
-      <c r="Y119" s="13" t="inlineStr"/>
+      <c r="Y119" s="13" t="inlineStr">
+        <is>
+          <t>writeoff_id</t>
+        </is>
+      </c>
       <c r="Z119" s="13" t="inlineStr"/>
       <c r="AA119" s="13" t="inlineStr"/>
       <c r="AB119" s="13" t="inlineStr"/>
@@ -15954,7 +15966,7 @@
       </c>
       <c r="AK119" s="13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>number</t>
         </is>
       </c>
       <c r="AL119" s="13" t="inlineStr">
@@ -15962,12 +15974,12 @@
           <t>False</t>
         </is>
       </c>
-      <c r="AM119" s="13" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="AN119" s="13" t="inlineStr"/>
+      <c r="AM119" s="13" t="inlineStr"/>
+      <c r="AN119" s="13" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
       <c r="AO119" s="14" t="inlineStr"/>
       <c r="AP119" s="14" t="inlineStr"/>
       <c r="AQ119" s="14" t="inlineStr"/>
@@ -15983,7 +15995,7 @@
       </c>
       <c r="AT119" s="13" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AU119" s="13" t="inlineStr">
@@ -15995,7 +16007,7 @@
     <row r="120">
       <c r="A120" s="13" t="inlineStr">
         <is>
-          <t>ТЗ §3 М5 money_expense · AP-8</t>
+          <t>ТЗ §3 М4 writeoff_items</t>
         </is>
       </c>
       <c r="B120" s="13" t="inlineStr"/>
@@ -16006,22 +16018,22 @@
       </c>
       <c r="D120" s="14" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>Товар</t>
         </is>
       </c>
       <c r="E120" s="13" t="inlineStr">
         <is>
-          <t>money_expense.id</t>
+          <t>writeoff_items.product_id</t>
         </is>
       </c>
       <c r="G120" s="13" t="inlineStr">
         <is>
-          <t>bigserial</t>
+          <t>bigint FK</t>
         </is>
       </c>
       <c r="J120" s="14" t="inlineStr">
         <is>
-          <t>Суррогатный первичный ключ.</t>
+          <t>Списываемый товар.</t>
         </is>
       </c>
       <c r="K120" s="13" t="inlineStr">
@@ -16033,20 +16045,16 @@
       <c r="M120" s="13" t="inlineStr"/>
       <c r="N120" s="13" t="inlineStr">
         <is>
-          <t>BigInteger</t>
-        </is>
-      </c>
-      <c r="O120" s="13" t="inlineStr">
-        <is>
-          <t>autoincrement (Identity)</t>
-        </is>
-      </c>
-      <c r="P120" s="13" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="Q120" s="13" t="inlineStr"/>
+          <t>BigInteger · ForeignKey('products.id', ondelete='RESTRICT')</t>
+        </is>
+      </c>
+      <c r="O120" s="13" t="inlineStr"/>
+      <c r="P120" s="13" t="inlineStr"/>
+      <c r="Q120" s="13" t="inlineStr">
+        <is>
+          <t>relationship Product</t>
+        </is>
+      </c>
       <c r="R120" s="13" t="inlineStr"/>
       <c r="S120" s="13" t="inlineStr">
         <is>
@@ -16056,27 +16064,27 @@
       <c r="T120" s="13" t="inlineStr"/>
       <c r="U120" s="13" t="inlineStr">
         <is>
-          <t>True (PK)</t>
-        </is>
-      </c>
-      <c r="V120" s="13" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="W120" s="13" t="inlineStr"/>
-      <c r="X120" s="14" t="inlineStr">
-        <is>
-          <t>PRIMARY KEY</t>
-        </is>
-      </c>
+          <t>True (FK)</t>
+        </is>
+      </c>
+      <c r="V120" s="13" t="inlineStr"/>
+      <c r="W120" s="13" t="inlineStr">
+        <is>
+          <t>RESTRICT</t>
+        </is>
+      </c>
+      <c r="X120" s="14" t="inlineStr"/>
       <c r="Y120" s="13" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>product_id</t>
         </is>
       </c>
       <c r="Z120" s="13" t="inlineStr"/>
-      <c r="AA120" s="13" t="inlineStr"/>
+      <c r="AA120" s="13" t="inlineStr">
+        <is>
+          <t>GET /stock/balances?warehouse_id={warehouse_id}</t>
+        </is>
+      </c>
       <c r="AB120" s="13" t="inlineStr"/>
       <c r="AC120" s="13" t="inlineStr"/>
       <c r="AD120" s="13" t="inlineStr"/>
@@ -16087,31 +16095,27 @@
       <c r="AI120" s="14" t="inlineStr"/>
       <c r="AJ120" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="AK120" s="13" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>select</t>
         </is>
       </c>
       <c r="AL120" s="13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AM120" s="13" t="inlineStr"/>
-      <c r="AN120" s="13" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
+      <c r="AN120" s="13" t="inlineStr"/>
       <c r="AO120" s="14" t="inlineStr"/>
       <c r="AP120" s="14" t="inlineStr"/>
       <c r="AQ120" s="14" t="inlineStr"/>
       <c r="AR120" s="13" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AS120" s="13" t="inlineStr">
@@ -16121,7 +16125,7 @@
       </c>
       <c r="AT120" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="AU120" s="13" t="inlineStr">
@@ -16133,7 +16137,7 @@
     <row r="121">
       <c r="A121" s="13" t="inlineStr">
         <is>
-          <t>ТЗ §3 М5 money_expense · AP-8 · SV-6</t>
+          <t>ТЗ §3 М4 writeoff_items</t>
         </is>
       </c>
       <c r="B121" s="13" t="inlineStr"/>
@@ -16144,22 +16148,22 @@
       </c>
       <c r="D121" s="14" t="inlineStr">
         <is>
-          <t>Касса</t>
+          <t>Количество</t>
         </is>
       </c>
       <c r="E121" s="13" t="inlineStr">
         <is>
-          <t>money_expense.cash_desk_id</t>
+          <t>writeoff_items.qty</t>
         </is>
       </c>
       <c r="G121" s="13" t="inlineStr">
         <is>
-          <t>bigint FK</t>
+          <t>numeric(14,3)</t>
         </is>
       </c>
       <c r="J121" s="14" t="inlineStr">
         <is>
-          <t>Касса списания. ОПРЕДЕЛЯЕТСЯ СЕРВЕРОМ из users.category (SV-6).</t>
+          <t>Списываемое количество (положительное; знак ставит ledger).</t>
         </is>
       </c>
       <c r="K121" s="13" t="inlineStr">
@@ -16171,16 +16175,12 @@
       <c r="M121" s="13" t="inlineStr"/>
       <c r="N121" s="13" t="inlineStr">
         <is>
-          <t>BigInteger · ForeignKey('cash_desks.id', ondelete='RESTRICT')</t>
+          <t>Numeric(14, 3)</t>
         </is>
       </c>
       <c r="O121" s="13" t="inlineStr"/>
       <c r="P121" s="13" t="inlineStr"/>
-      <c r="Q121" s="13" t="inlineStr">
-        <is>
-          <t>relationship CashDesk</t>
-        </is>
-      </c>
+      <c r="Q121" s="13" t="inlineStr"/>
       <c r="R121" s="13" t="inlineStr"/>
       <c r="S121" s="13" t="inlineStr">
         <is>
@@ -16188,27 +16188,15 @@
         </is>
       </c>
       <c r="T121" s="13" t="inlineStr"/>
-      <c r="U121" s="13" t="inlineStr">
-        <is>
-          <t>True (composite (cash_desk_id, date DESC) — AP-8)</t>
-        </is>
-      </c>
-      <c r="V121" s="13" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="W121" s="13" t="inlineStr">
-        <is>
-          <t>RESTRICT</t>
-        </is>
-      </c>
-      <c r="X121" s="14" t="inlineStr"/>
-      <c r="Y121" s="13" t="inlineStr">
-        <is>
-          <t>cash_desk_id</t>
-        </is>
-      </c>
+      <c r="U121" s="13" t="inlineStr"/>
+      <c r="V121" s="13" t="inlineStr"/>
+      <c r="W121" s="13" t="inlineStr"/>
+      <c r="X121" s="14" t="inlineStr">
+        <is>
+          <t>INV-6: CHECK (qty &gt; 0)</t>
+        </is>
+      </c>
+      <c r="Y121" s="13" t="inlineStr"/>
       <c r="Z121" s="13" t="inlineStr"/>
       <c r="AA121" s="13" t="inlineStr"/>
       <c r="AB121" s="13" t="inlineStr"/>
@@ -16226,30 +16214,26 @@
       </c>
       <c r="AK121" s="13" t="inlineStr">
         <is>
-          <t>select</t>
+          <t>number</t>
         </is>
       </c>
       <c r="AL121" s="13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AM121" s="13" t="inlineStr"/>
-      <c r="AN121" s="13" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AO121" s="14" t="inlineStr"/>
-      <c r="AP121" s="14" t="inlineStr">
-        <is>
-          <t>SV-6: клиент кассу НЕ присылает (create=—). Иначе учитель спишет из кассы работников, подделав тело запроса. AP-9: FOR UPDATE по cash_desks при расходе.</t>
-        </is>
-      </c>
+      <c r="AN121" s="13" t="inlineStr"/>
+      <c r="AO121" s="14" t="inlineStr">
+        <is>
+          <t>required; &gt; 0; ≤ остатка (сервер — истина)</t>
+        </is>
+      </c>
+      <c r="AP121" s="14" t="inlineStr"/>
       <c r="AQ121" s="14" t="inlineStr"/>
       <c r="AR121" s="13" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AS121" s="13" t="inlineStr">
@@ -16259,7 +16243,7 @@
       </c>
       <c r="AT121" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="AU121" s="13" t="inlineStr">
@@ -16271,7 +16255,7 @@
     <row r="122">
       <c r="A122" s="13" t="inlineStr">
         <is>
-          <t>ТЗ §3 М5 money_expense · AP-8 · AP-8</t>
+          <t>ТЗ §3 М4 writeoff_items</t>
         </is>
       </c>
       <c r="B122" s="13" t="inlineStr"/>
@@ -16282,22 +16266,22 @@
       </c>
       <c r="D122" s="14" t="inlineStr">
         <is>
-          <t>Сотрудник</t>
+          <t>Причина</t>
         </is>
       </c>
       <c r="E122" s="13" t="inlineStr">
         <is>
-          <t>money_expense.employee_id</t>
+          <t>writeoff_items.reason</t>
         </is>
       </c>
       <c r="G122" s="13" t="inlineStr">
         <is>
-          <t>bigint FK</t>
+          <t>varchar(500) NULL</t>
         </is>
       </c>
       <c r="J122" s="14" t="inlineStr">
         <is>
-          <t>Кто потратил. Из JWT (сотрудник видит только свои расходы, §1.3).</t>
+          <t>Причина списания построчно (актуально для порчи/брака).</t>
         </is>
       </c>
       <c r="K122" s="13" t="inlineStr">
@@ -16309,44 +16293,24 @@
       <c r="M122" s="13" t="inlineStr"/>
       <c r="N122" s="13" t="inlineStr">
         <is>
-          <t>BigInteger · ForeignKey('users.id', ondelete='RESTRICT')</t>
+          <t>String(500)</t>
         </is>
       </c>
       <c r="O122" s="13" t="inlineStr"/>
       <c r="P122" s="13" t="inlineStr"/>
-      <c r="Q122" s="13" t="inlineStr">
-        <is>
-          <t>relationship User</t>
-        </is>
-      </c>
+      <c r="Q122" s="13" t="inlineStr"/>
       <c r="R122" s="13" t="inlineStr"/>
       <c r="S122" s="13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="T122" s="13" t="inlineStr"/>
-      <c r="U122" s="13" t="inlineStr">
-        <is>
-          <t>True (composite (employee_id, date DESC) — AP-8)</t>
-        </is>
-      </c>
-      <c r="V122" s="13" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="W122" s="13" t="inlineStr">
-        <is>
-          <t>RESTRICT</t>
-        </is>
-      </c>
+      <c r="U122" s="13" t="inlineStr"/>
+      <c r="V122" s="13" t="inlineStr"/>
+      <c r="W122" s="13" t="inlineStr"/>
       <c r="X122" s="14" t="inlineStr"/>
-      <c r="Y122" s="13" t="inlineStr">
-        <is>
-          <t>employee_id</t>
-        </is>
-      </c>
+      <c r="Y122" s="13" t="inlineStr"/>
       <c r="Z122" s="13" t="inlineStr"/>
       <c r="AA122" s="13" t="inlineStr"/>
       <c r="AB122" s="13" t="inlineStr"/>
@@ -16359,12 +16323,12 @@
       <c r="AI122" s="14" t="inlineStr"/>
       <c r="AJ122" s="13" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AK122" s="13" t="inlineStr">
         <is>
-          <t>select</t>
+          <t>text</t>
         </is>
       </c>
       <c r="AL122" s="13" t="inlineStr">
@@ -16372,18 +16336,18 @@
           <t>False</t>
         </is>
       </c>
-      <c r="AM122" s="13" t="inlineStr"/>
-      <c r="AN122" s="13" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
+      <c r="AM122" s="13" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="AN122" s="13" t="inlineStr"/>
       <c r="AO122" s="14" t="inlineStr"/>
       <c r="AP122" s="14" t="inlineStr"/>
       <c r="AQ122" s="14" t="inlineStr"/>
       <c r="AR122" s="13" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AS122" s="13" t="inlineStr">
@@ -16393,7 +16357,7 @@
       </c>
       <c r="AT122" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="AU122" s="13" t="inlineStr">
@@ -16405,7 +16369,7 @@
     <row r="123">
       <c r="A123" s="13" t="inlineStr">
         <is>
-          <t>ТЗ §3 М5 money_expense · AP-8 · AP-8</t>
+          <t>ТЗ §3 М5 cash_desks · AP-9</t>
         </is>
       </c>
       <c r="B123" s="13" t="inlineStr"/>
@@ -16416,22 +16380,22 @@
       </c>
       <c r="D123" s="14" t="inlineStr">
         <is>
-          <t>Вид расхода</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E123" s="13" t="inlineStr">
         <is>
-          <t>money_expense.expense_category_id</t>
+          <t>cash_desks.id</t>
         </is>
       </c>
       <c r="G123" s="13" t="inlineStr">
         <is>
-          <t>bigint FK</t>
+          <t>bigserial</t>
         </is>
       </c>
       <c r="J123" s="14" t="inlineStr">
         <is>
-          <t>Вид расхода денег. Обязательный фильтр отчёта ДДС (AP-8).</t>
+          <t>Суррогатный первичный ключ.</t>
         </is>
       </c>
       <c r="K123" s="13" t="inlineStr">
@@ -16443,16 +16407,20 @@
       <c r="M123" s="13" t="inlineStr"/>
       <c r="N123" s="13" t="inlineStr">
         <is>
-          <t>BigInteger · ForeignKey('expense_categories.id', ondelete='RESTRICT')</t>
-        </is>
-      </c>
-      <c r="O123" s="13" t="inlineStr"/>
-      <c r="P123" s="13" t="inlineStr"/>
-      <c r="Q123" s="13" t="inlineStr">
-        <is>
-          <t>relationship ExpenseCategory</t>
-        </is>
-      </c>
+          <t>BigInteger</t>
+        </is>
+      </c>
+      <c r="O123" s="13" t="inlineStr">
+        <is>
+          <t>autoincrement (Identity)</t>
+        </is>
+      </c>
+      <c r="P123" s="13" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Q123" s="13" t="inlineStr"/>
       <c r="R123" s="13" t="inlineStr"/>
       <c r="S123" s="13" t="inlineStr">
         <is>
@@ -16462,27 +16430,27 @@
       <c r="T123" s="13" t="inlineStr"/>
       <c r="U123" s="13" t="inlineStr">
         <is>
-          <t>True (composite (expense_category_id, date DESC) — AP-8)</t>
-        </is>
-      </c>
-      <c r="V123" s="13" t="inlineStr"/>
-      <c r="W123" s="13" t="inlineStr">
-        <is>
-          <t>RESTRICT</t>
-        </is>
-      </c>
-      <c r="X123" s="14" t="inlineStr"/>
+          <t>True (PK)</t>
+        </is>
+      </c>
+      <c r="V123" s="13" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="W123" s="13" t="inlineStr"/>
+      <c r="X123" s="14" t="inlineStr">
+        <is>
+          <t>PRIMARY KEY</t>
+        </is>
+      </c>
       <c r="Y123" s="13" t="inlineStr">
         <is>
-          <t>expense_category_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="Z123" s="13" t="inlineStr"/>
-      <c r="AA123" s="13" t="inlineStr">
-        <is>
-          <t>GET /expense-categories?status=active</t>
-        </is>
-      </c>
+      <c r="AA123" s="13" t="inlineStr"/>
       <c r="AB123" s="13" t="inlineStr"/>
       <c r="AC123" s="13" t="inlineStr"/>
       <c r="AD123" s="13" t="inlineStr"/>
@@ -16493,27 +16461,27 @@
       <c r="AI123" s="14" t="inlineStr"/>
       <c r="AJ123" s="13" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AK123" s="13" t="inlineStr">
         <is>
-          <t>select</t>
+          <t>number</t>
         </is>
       </c>
       <c r="AL123" s="13" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AM123" s="13" t="inlineStr"/>
+      <c r="AN123" s="13" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AM123" s="13" t="inlineStr"/>
-      <c r="AN123" s="13" t="inlineStr"/>
       <c r="AO123" s="14" t="inlineStr"/>
-      <c r="AP123" s="14" t="inlineStr">
-        <is>
-          <t>AP-8: «фильтр по категории обязателен» — под это отдельный composite-индекс.</t>
-        </is>
-      </c>
+      <c r="AP123" s="14" t="inlineStr"/>
       <c r="AQ123" s="14" t="inlineStr"/>
       <c r="AR123" s="13" t="inlineStr">
         <is>
@@ -16527,7 +16495,7 @@
       </c>
       <c r="AT123" s="13" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AU123" s="13" t="inlineStr">
@@ -16539,7 +16507,7 @@
     <row r="124">
       <c r="A124" s="13" t="inlineStr">
         <is>
-          <t>ТЗ §3 М5 money_expense · AP-8</t>
+          <t>ТЗ §3 М5 cash_desks · AP-9</t>
         </is>
       </c>
       <c r="B124" s="13" t="inlineStr"/>
@@ -16550,22 +16518,22 @@
       </c>
       <c r="D124" s="14" t="inlineStr">
         <is>
-          <t>Сумма расхода</t>
+          <t>Касса</t>
         </is>
       </c>
       <c r="E124" s="13" t="inlineStr">
         <is>
-          <t>money_expense.amount</t>
+          <t>cash_desks.type</t>
         </is>
       </c>
       <c r="G124" s="13" t="inlineStr">
         <is>
-          <t>numeric(18,2)</t>
+          <t>enum UNIQUE</t>
         </is>
       </c>
       <c r="J124" s="14" t="inlineStr">
         <is>
-          <t>Сумма расхода, UZS.</t>
+          <t>teacher | worker. Ровно две строки (seed). UNIQUE гарантирует, что третьей кассы не появится.</t>
         </is>
       </c>
       <c r="K124" s="13" t="inlineStr">
@@ -16577,31 +16545,51 @@
       <c r="M124" s="13" t="inlineStr"/>
       <c r="N124" s="13" t="inlineStr">
         <is>
-          <t>Numeric(18, 2)</t>
+          <t>SAEnum(CashDeskType, name='cash_desk_type')</t>
         </is>
       </c>
       <c r="O124" s="13" t="inlineStr"/>
-      <c r="P124" s="13" t="inlineStr"/>
-      <c r="Q124" s="13" t="inlineStr"/>
-      <c r="R124" s="13" t="inlineStr"/>
+      <c r="P124" s="13" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Q124" s="13" t="inlineStr">
+        <is>
+          <t>CashDeskType(str, Enum)</t>
+        </is>
+      </c>
+      <c r="R124" s="13" t="inlineStr">
+        <is>
+          <t>teacher | worker</t>
+        </is>
+      </c>
       <c r="S124" s="13" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
       <c r="T124" s="13" t="inlineStr"/>
-      <c r="U124" s="13" t="inlineStr"/>
+      <c r="U124" s="13" t="inlineStr">
+        <is>
+          <t>True (UNIQUE)</t>
+        </is>
+      </c>
       <c r="V124" s="13" t="inlineStr"/>
       <c r="W124" s="13" t="inlineStr"/>
-      <c r="X124" s="14" t="inlineStr">
-        <is>
-          <t>CHECK (amount &gt; 0)</t>
-        </is>
-      </c>
-      <c r="Y124" s="13" t="inlineStr"/>
+      <c r="X124" s="14" t="inlineStr"/>
+      <c r="Y124" s="13" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
       <c r="Z124" s="13" t="inlineStr"/>
       <c r="AA124" s="13" t="inlineStr"/>
-      <c r="AB124" s="13" t="inlineStr"/>
+      <c r="AB124" s="13" t="inlineStr">
+        <is>
+          <t>teacher | worker</t>
+        </is>
+      </c>
       <c r="AC124" s="13" t="inlineStr"/>
       <c r="AD124" s="13" t="inlineStr"/>
       <c r="AE124" s="13" t="inlineStr"/>
@@ -16616,22 +16604,26 @@
       </c>
       <c r="AK124" s="13" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>select</t>
         </is>
       </c>
       <c r="AL124" s="13" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AM124" s="13" t="inlineStr"/>
+      <c r="AN124" s="13" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AM124" s="13" t="inlineStr"/>
-      <c r="AN124" s="13" t="inlineStr"/>
-      <c r="AO124" s="14" t="inlineStr">
-        <is>
-          <t>required; &gt; 0; 2 знака; UZS; ≤ баланса кассы (сервер — истина, ОВ-2)</t>
-        </is>
-      </c>
-      <c r="AP124" s="14" t="inlineStr"/>
+      <c r="AO124" s="14" t="inlineStr"/>
+      <c r="AP124" s="14" t="inlineStr">
+        <is>
+          <t>SV-6: касса выводится сервером из users.category, клиент её не выбирает.</t>
+        </is>
+      </c>
       <c r="AQ124" s="14" t="inlineStr"/>
       <c r="AR124" s="13" t="inlineStr">
         <is>
@@ -16645,7 +16637,7 @@
       </c>
       <c r="AT124" s="13" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AU124" s="13" t="inlineStr">
@@ -16657,7 +16649,7 @@
     <row r="125">
       <c r="A125" s="13" t="inlineStr">
         <is>
-          <t>ТЗ §3 М5 money_expense · AP-8</t>
+          <t>ТЗ §3 М5 cash_desks · AP-9 · INV-8 · ОВ-2</t>
         </is>
       </c>
       <c r="B125" s="13" t="inlineStr"/>
@@ -16668,22 +16660,22 @@
       </c>
       <c r="D125" s="14" t="inlineStr">
         <is>
-          <t>Описание</t>
+          <t>Баланс кассы</t>
         </is>
       </c>
       <c r="E125" s="13" t="inlineStr">
         <is>
-          <t>money_expense.description</t>
+          <t>cash_desks.balance</t>
         </is>
       </c>
       <c r="G125" s="13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>numeric(18,2)</t>
         </is>
       </c>
       <c r="J125" s="14" t="inlineStr">
         <is>
-          <t>На что потрачены деньги.</t>
+          <t>Текущий остаток кассы, UZS. Обновляется в TX под FOR UPDATE (AP-9).</t>
         </is>
       </c>
       <c r="K125" s="13" t="inlineStr">
@@ -16695,7 +16687,7 @@
       <c r="M125" s="13" t="inlineStr"/>
       <c r="N125" s="13" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Numeric(18, 2)</t>
         </is>
       </c>
       <c r="O125" s="13" t="inlineStr"/>
@@ -16707,13 +16699,21 @@
           <t>False</t>
         </is>
       </c>
-      <c r="T125" s="13" t="inlineStr"/>
+      <c r="T125" s="13" t="inlineStr">
+        <is>
+          <t>0 (server_default='0')</t>
+        </is>
+      </c>
       <c r="U125" s="13" t="inlineStr"/>
-      <c r="V125" s="13" t="inlineStr"/>
+      <c r="V125" s="13" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="W125" s="13" t="inlineStr"/>
       <c r="X125" s="14" t="inlineStr">
         <is>
-          <t>CHECK (length(trim(description)) &gt; 0)</t>
+          <t>INV-8: CHECK (balance &gt;= 0) — по допущению ОВ-2 (жёсткая блокировка)</t>
         </is>
       </c>
       <c r="Y125" s="13" t="inlineStr"/>
@@ -16729,31 +16729,35 @@
       <c r="AI125" s="14" t="inlineStr"/>
       <c r="AJ125" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="AK125" s="13" t="inlineStr">
         <is>
-          <t>textarea</t>
+          <t>number</t>
         </is>
       </c>
       <c r="AL125" s="13" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AM125" s="13" t="inlineStr"/>
+      <c r="AN125" s="13" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AM125" s="13" t="inlineStr"/>
-      <c r="AN125" s="13" t="inlineStr"/>
-      <c r="AO125" s="14" t="inlineStr">
-        <is>
-          <t>required; непустая строка</t>
-        </is>
-      </c>
-      <c r="AP125" s="14" t="inlineStr"/>
+      <c r="AO125" s="14" t="inlineStr"/>
+      <c r="AP125" s="14" t="inlineStr">
+        <is>
+          <t>ОВ-2 ОТКРЫТ: CHECK поставлен по принятому допущению «жёсткая блокировка». Если заказчик выберет режим предупреждения (CASH_OVERDRAFT_MODE=warn), CHECK придётся снять отдельной миграцией — единственное место, где ОВ-2 всё-таки касается схемы.</t>
+        </is>
+      </c>
       <c r="AQ125" s="14" t="inlineStr"/>
       <c r="AR125" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="AS125" s="13" t="inlineStr">
@@ -16763,7 +16767,7 @@
       </c>
       <c r="AT125" s="13" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AU125" s="13" t="inlineStr">
@@ -16775,7 +16779,7 @@
     <row r="126">
       <c r="A126" s="13" t="inlineStr">
         <is>
-          <t>ТЗ §3 М5 money_expense · AP-8 · INV-7</t>
+          <t>ТЗ §3 М5 money_income</t>
         </is>
       </c>
       <c r="B126" s="13" t="inlineStr"/>
@@ -16786,22 +16790,22 @@
       </c>
       <c r="D126" s="14" t="inlineStr">
         <is>
-          <t>Чек</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E126" s="13" t="inlineStr">
         <is>
-          <t>money_expense.receipt_url</t>
+          <t>money_income.id</t>
         </is>
       </c>
       <c r="G126" s="13" t="inlineStr">
         <is>
-          <t>varchar(500)</t>
+          <t>bigserial</t>
         </is>
       </c>
       <c r="J126" s="14" t="inlineStr">
         <is>
-          <t>Ключ объекта чека в MinIO (бакет receipts). NOT NULL — чек обязателен (§7.3).</t>
+          <t>Суррогатный первичный ключ.</t>
         </is>
       </c>
       <c r="K126" s="13" t="inlineStr">
@@ -16813,11 +16817,19 @@
       <c r="M126" s="13" t="inlineStr"/>
       <c r="N126" s="13" t="inlineStr">
         <is>
-          <t>String(500)</t>
-        </is>
-      </c>
-      <c r="O126" s="13" t="inlineStr"/>
-      <c r="P126" s="13" t="inlineStr"/>
+          <t>BigInteger</t>
+        </is>
+      </c>
+      <c r="O126" s="13" t="inlineStr">
+        <is>
+          <t>autoincrement (Identity)</t>
+        </is>
+      </c>
+      <c r="P126" s="13" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
       <c r="Q126" s="13" t="inlineStr"/>
       <c r="R126" s="13" t="inlineStr"/>
       <c r="S126" s="13" t="inlineStr">
@@ -16826,15 +16838,27 @@
         </is>
       </c>
       <c r="T126" s="13" t="inlineStr"/>
-      <c r="U126" s="13" t="inlineStr"/>
-      <c r="V126" s="13" t="inlineStr"/>
+      <c r="U126" s="13" t="inlineStr">
+        <is>
+          <t>True (PK)</t>
+        </is>
+      </c>
+      <c r="V126" s="13" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="W126" s="13" t="inlineStr"/>
       <c r="X126" s="14" t="inlineStr">
         <is>
-          <t>INV-7: NOT NULL + CHECK (length(trim(receipt_url)) &gt; 0) — иначе пустая строка обойдёт NOT NULL</t>
-        </is>
-      </c>
-      <c r="Y126" s="13" t="inlineStr"/>
+          <t>PRIMARY KEY</t>
+        </is>
+      </c>
+      <c r="Y126" s="13" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
       <c r="Z126" s="13" t="inlineStr"/>
       <c r="AA126" s="13" t="inlineStr"/>
       <c r="AB126" s="13" t="inlineStr"/>
@@ -16852,34 +16876,26 @@
       </c>
       <c r="AK126" s="13" t="inlineStr">
         <is>
-          <t>file</t>
+          <t>number</t>
         </is>
       </c>
       <c r="AL126" s="13" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AM126" s="13" t="inlineStr"/>
+      <c r="AN126" s="13" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AM126" s="13" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="AN126" s="13" t="inlineStr"/>
-      <c r="AO126" s="14" t="inlineStr">
-        <is>
-          <t>required; whitelist jpg/png/pdf; ≤ 10 МБ; проверка по magic bytes (сервер)</t>
-        </is>
-      </c>
-      <c r="AP126" s="14" t="inlineStr">
-        <is>
-          <t>INV-7. Загрузка: POST /cash/expenses/{id}/receipt. Хранится ключ, наружу — presigned URL TTL 5 мин, бакет приватный.</t>
-        </is>
-      </c>
+      <c r="AO126" s="14" t="inlineStr"/>
+      <c r="AP126" s="14" t="inlineStr"/>
       <c r="AQ126" s="14" t="inlineStr"/>
       <c r="AR126" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="AS126" s="13" t="inlineStr">
@@ -16889,7 +16905,7 @@
       </c>
       <c r="AT126" s="13" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AU126" s="13" t="inlineStr">
@@ -16901,7 +16917,7 @@
     <row r="127">
       <c r="A127" s="13" t="inlineStr">
         <is>
-          <t>ТЗ §3 М5 money_expense · AP-8 · AP-8</t>
+          <t>ТЗ §3 М5 money_income</t>
         </is>
       </c>
       <c r="B127" s="13" t="inlineStr"/>
@@ -16912,22 +16928,22 @@
       </c>
       <c r="D127" s="14" t="inlineStr">
         <is>
-          <t>Дата</t>
+          <t>Касса</t>
         </is>
       </c>
       <c r="E127" s="13" t="inlineStr">
         <is>
-          <t>money_expense.date</t>
+          <t>money_income.cash_desk_id</t>
         </is>
       </c>
       <c r="G127" s="13" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>bigint FK</t>
         </is>
       </c>
       <c r="J127" s="14" t="inlineStr">
         <is>
-          <t>Дата расхода. Ключ периода в отчёте ДДС.</t>
+          <t>Пополняемая касса.</t>
         </is>
       </c>
       <c r="K127" s="13" t="inlineStr">
@@ -16939,12 +16955,16 @@
       <c r="M127" s="13" t="inlineStr"/>
       <c r="N127" s="13" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>BigInteger · ForeignKey('cash_desks.id', ondelete='RESTRICT')</t>
         </is>
       </c>
       <c r="O127" s="13" t="inlineStr"/>
       <c r="P127" s="13" t="inlineStr"/>
-      <c r="Q127" s="13" t="inlineStr"/>
+      <c r="Q127" s="13" t="inlineStr">
+        <is>
+          <t>relationship CashDesk</t>
+        </is>
+      </c>
       <c r="R127" s="13" t="inlineStr"/>
       <c r="S127" s="13" t="inlineStr">
         <is>
@@ -16954,19 +16974,27 @@
       <c r="T127" s="13" t="inlineStr"/>
       <c r="U127" s="13" t="inlineStr">
         <is>
-          <t>True (в составе composite-индексов AP-8)</t>
+          <t>True (FK)</t>
         </is>
       </c>
       <c r="V127" s="13" t="inlineStr"/>
-      <c r="W127" s="13" t="inlineStr"/>
+      <c r="W127" s="13" t="inlineStr">
+        <is>
+          <t>RESTRICT</t>
+        </is>
+      </c>
       <c r="X127" s="14" t="inlineStr"/>
       <c r="Y127" s="13" t="inlineStr">
         <is>
-          <t>date__range</t>
+          <t>cash_desk_id</t>
         </is>
       </c>
       <c r="Z127" s="13" t="inlineStr"/>
-      <c r="AA127" s="13" t="inlineStr"/>
+      <c r="AA127" s="13" t="inlineStr">
+        <is>
+          <t>GET /cash/desks</t>
+        </is>
+      </c>
       <c r="AB127" s="13" t="inlineStr"/>
       <c r="AC127" s="13" t="inlineStr"/>
       <c r="AD127" s="13" t="inlineStr"/>
@@ -16982,7 +17010,7 @@
       </c>
       <c r="AK127" s="13" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select</t>
         </is>
       </c>
       <c r="AL127" s="13" t="inlineStr">
@@ -16993,7 +17021,11 @@
       <c r="AM127" s="13" t="inlineStr"/>
       <c r="AN127" s="13" t="inlineStr"/>
       <c r="AO127" s="14" t="inlineStr"/>
-      <c r="AP127" s="14" t="inlineStr"/>
+      <c r="AP127" s="14" t="inlineStr">
+        <is>
+          <t>Приход — только admin (§6 API), поэтому кассу здесь выбирают явно (в отличие от расхода, SV-6).</t>
+        </is>
+      </c>
       <c r="AQ127" s="14" t="inlineStr"/>
       <c r="AR127" s="13" t="inlineStr">
         <is>
@@ -17019,7 +17051,7 @@
     <row r="128">
       <c r="A128" s="13" t="inlineStr">
         <is>
-          <t>ТЗ §3 М7 audit_log</t>
+          <t>ТЗ §3 М5 money_income</t>
         </is>
       </c>
       <c r="B128" s="13" t="inlineStr"/>
@@ -17030,22 +17062,22 @@
       </c>
       <c r="D128" s="14" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>Сумма прихода</t>
         </is>
       </c>
       <c r="E128" s="13" t="inlineStr">
         <is>
-          <t>audit_log.id</t>
+          <t>money_income.amount</t>
         </is>
       </c>
       <c r="G128" s="13" t="inlineStr">
         <is>
-          <t>bigserial</t>
+          <t>numeric(18,2)</t>
         </is>
       </c>
       <c r="J128" s="14" t="inlineStr">
         <is>
-          <t>Суррогатный первичный ключ.</t>
+          <t>Сумма пополнения, UZS. Деньги — только NUMERIC, никогда float.</t>
         </is>
       </c>
       <c r="K128" s="13" t="inlineStr">
@@ -17057,19 +17089,11 @@
       <c r="M128" s="13" t="inlineStr"/>
       <c r="N128" s="13" t="inlineStr">
         <is>
-          <t>BigInteger</t>
-        </is>
-      </c>
-      <c r="O128" s="13" t="inlineStr">
-        <is>
-          <t>autoincrement (Identity)</t>
-        </is>
-      </c>
-      <c r="P128" s="13" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
+          <t>Numeric(18, 2)</t>
+        </is>
+      </c>
+      <c r="O128" s="13" t="inlineStr"/>
+      <c r="P128" s="13" t="inlineStr"/>
       <c r="Q128" s="13" t="inlineStr"/>
       <c r="R128" s="13" t="inlineStr"/>
       <c r="S128" s="13" t="inlineStr">
@@ -17078,27 +17102,15 @@
         </is>
       </c>
       <c r="T128" s="13" t="inlineStr"/>
-      <c r="U128" s="13" t="inlineStr">
-        <is>
-          <t>True (PK)</t>
-        </is>
-      </c>
-      <c r="V128" s="13" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
+      <c r="U128" s="13" t="inlineStr"/>
+      <c r="V128" s="13" t="inlineStr"/>
       <c r="W128" s="13" t="inlineStr"/>
       <c r="X128" s="14" t="inlineStr">
         <is>
-          <t>PRIMARY KEY</t>
-        </is>
-      </c>
-      <c r="Y128" s="13" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
+          <t>CHECK (amount &gt; 0)</t>
+        </is>
+      </c>
+      <c r="Y128" s="13" t="inlineStr"/>
       <c r="Z128" s="13" t="inlineStr"/>
       <c r="AA128" s="13" t="inlineStr"/>
       <c r="AB128" s="13" t="inlineStr"/>
@@ -17111,7 +17123,7 @@
       <c r="AI128" s="14" t="inlineStr"/>
       <c r="AJ128" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="AK128" s="13" t="inlineStr">
@@ -17121,16 +17133,16 @@
       </c>
       <c r="AL128" s="13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AM128" s="13" t="inlineStr"/>
-      <c r="AN128" s="13" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AO128" s="14" t="inlineStr"/>
+      <c r="AN128" s="13" t="inlineStr"/>
+      <c r="AO128" s="14" t="inlineStr">
+        <is>
+          <t>required; &gt; 0; 2 знака; UZS</t>
+        </is>
+      </c>
       <c r="AP128" s="14" t="inlineStr"/>
       <c r="AQ128" s="14" t="inlineStr"/>
       <c r="AR128" s="13" t="inlineStr">
@@ -17145,7 +17157,7 @@
       </c>
       <c r="AT128" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="AU128" s="13" t="inlineStr">
@@ -17157,7 +17169,7 @@
     <row r="129">
       <c r="A129" s="13" t="inlineStr">
         <is>
-          <t>ТЗ §3 М7 audit_log</t>
+          <t>ТЗ §3 М5 money_income</t>
         </is>
       </c>
       <c r="B129" s="13" t="inlineStr"/>
@@ -17168,22 +17180,22 @@
       </c>
       <c r="D129" s="14" t="inlineStr">
         <is>
-          <t>Пользователь</t>
+          <t>Дата</t>
         </is>
       </c>
       <c r="E129" s="13" t="inlineStr">
         <is>
-          <t>audit_log.user_id</t>
+          <t>money_income.date</t>
         </is>
       </c>
       <c r="G129" s="13" t="inlineStr">
         <is>
-          <t>bigint FK</t>
+          <t>date</t>
         </is>
       </c>
       <c r="J129" s="14" t="inlineStr">
         <is>
-          <t>Кто выполнил действие.</t>
+          <t>Дата прихода.</t>
         </is>
       </c>
       <c r="K129" s="13" t="inlineStr">
@@ -17195,16 +17207,12 @@
       <c r="M129" s="13" t="inlineStr"/>
       <c r="N129" s="13" t="inlineStr">
         <is>
-          <t>BigInteger · ForeignKey('users.id', ondelete='RESTRICT')</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="O129" s="13" t="inlineStr"/>
       <c r="P129" s="13" t="inlineStr"/>
-      <c r="Q129" s="13" t="inlineStr">
-        <is>
-          <t>relationship User</t>
-        </is>
-      </c>
+      <c r="Q129" s="13" t="inlineStr"/>
       <c r="R129" s="13" t="inlineStr"/>
       <c r="S129" s="13" t="inlineStr">
         <is>
@@ -17214,23 +17222,15 @@
       <c r="T129" s="13" t="inlineStr"/>
       <c r="U129" s="13" t="inlineStr">
         <is>
-          <t>True (FK)</t>
-        </is>
-      </c>
-      <c r="V129" s="13" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="W129" s="13" t="inlineStr">
-        <is>
-          <t>RESTRICT</t>
-        </is>
-      </c>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="V129" s="13" t="inlineStr"/>
+      <c r="W129" s="13" t="inlineStr"/>
       <c r="X129" s="14" t="inlineStr"/>
       <c r="Y129" s="13" t="inlineStr">
         <is>
-          <t>user_id</t>
+          <t>date__range</t>
         </is>
       </c>
       <c r="Z129" s="13" t="inlineStr"/>
@@ -17250,26 +17250,18 @@
       </c>
       <c r="AK129" s="13" t="inlineStr">
         <is>
-          <t>select</t>
+          <t>date</t>
         </is>
       </c>
       <c r="AL129" s="13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AM129" s="13" t="inlineStr"/>
-      <c r="AN129" s="13" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
+      <c r="AN129" s="13" t="inlineStr"/>
       <c r="AO129" s="14" t="inlineStr"/>
-      <c r="AP129" s="14" t="inlineStr">
-        <is>
-          <t>Таблица append-only, пишет middleware. Чтение — только admin. API на запись нет.</t>
-        </is>
-      </c>
+      <c r="AP129" s="14" t="inlineStr"/>
       <c r="AQ129" s="14" t="inlineStr"/>
       <c r="AR129" s="13" t="inlineStr">
         <is>
@@ -17283,7 +17275,7 @@
       </c>
       <c r="AT129" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="AU129" s="13" t="inlineStr">
@@ -17295,7 +17287,7 @@
     <row r="130">
       <c r="A130" s="13" t="inlineStr">
         <is>
-          <t>ТЗ §3 М7 audit_log</t>
+          <t>ТЗ §3 М5 money_income</t>
         </is>
       </c>
       <c r="B130" s="13" t="inlineStr"/>
@@ -17306,22 +17298,22 @@
       </c>
       <c r="D130" s="14" t="inlineStr">
         <is>
-          <t>Действие</t>
+          <t>Автор</t>
         </is>
       </c>
       <c r="E130" s="13" t="inlineStr">
         <is>
-          <t>audit_log.action</t>
+          <t>money_income.author_id</t>
         </is>
       </c>
       <c r="G130" s="13" t="inlineStr">
         <is>
-          <t>varchar(50)</t>
+          <t>bigint FK</t>
         </is>
       </c>
       <c r="J130" s="14" t="inlineStr">
         <is>
-          <t>create | update | delete | issue | print и т.п.</t>
+          <t>Администратор, проведший приход. Из JWT.</t>
         </is>
       </c>
       <c r="K130" s="13" t="inlineStr">
@@ -17333,12 +17325,16 @@
       <c r="M130" s="13" t="inlineStr"/>
       <c r="N130" s="13" t="inlineStr">
         <is>
-          <t>String(50)</t>
+          <t>BigInteger · ForeignKey('users.id', ondelete='RESTRICT')</t>
         </is>
       </c>
       <c r="O130" s="13" t="inlineStr"/>
       <c r="P130" s="13" t="inlineStr"/>
-      <c r="Q130" s="13" t="inlineStr"/>
+      <c r="Q130" s="13" t="inlineStr">
+        <is>
+          <t>relationship User</t>
+        </is>
+      </c>
       <c r="R130" s="13" t="inlineStr"/>
       <c r="S130" s="13" t="inlineStr">
         <is>
@@ -17348,7 +17344,7 @@
       <c r="T130" s="13" t="inlineStr"/>
       <c r="U130" s="13" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>True (FK)</t>
         </is>
       </c>
       <c r="V130" s="13" t="inlineStr">
@@ -17356,11 +17352,15 @@
           <t>False</t>
         </is>
       </c>
-      <c r="W130" s="13" t="inlineStr"/>
+      <c r="W130" s="13" t="inlineStr">
+        <is>
+          <t>RESTRICT</t>
+        </is>
+      </c>
       <c r="X130" s="14" t="inlineStr"/>
       <c r="Y130" s="13" t="inlineStr">
         <is>
-          <t>action</t>
+          <t>author_id</t>
         </is>
       </c>
       <c r="Z130" s="13" t="inlineStr"/>
@@ -17380,7 +17380,7 @@
       </c>
       <c r="AK130" s="13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select</t>
         </is>
       </c>
       <c r="AL130" s="13" t="inlineStr">
@@ -17388,22 +17388,14 @@
           <t>False</t>
         </is>
       </c>
-      <c r="AM130" s="13" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="AM130" s="13" t="inlineStr"/>
       <c r="AN130" s="13" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
       <c r="AO130" s="14" t="inlineStr"/>
-      <c r="AP130" s="14" t="inlineStr">
-        <is>
-          <t>varchar, не enum: множество действий расширяется с каждым новым эндпоинтом, миграция типа на каждый чих не нужна.</t>
-        </is>
-      </c>
+      <c r="AP130" s="14" t="inlineStr"/>
       <c r="AQ130" s="14" t="inlineStr"/>
       <c r="AR130" s="13" t="inlineStr">
         <is>
@@ -17429,7 +17421,7 @@
     <row r="131">
       <c r="A131" s="13" t="inlineStr">
         <is>
-          <t>ТЗ §3 М7 audit_log</t>
+          <t>ТЗ §3 М5 money_income</t>
         </is>
       </c>
       <c r="B131" s="13" t="inlineStr"/>
@@ -17440,22 +17432,22 @@
       </c>
       <c r="D131" s="14" t="inlineStr">
         <is>
-          <t>Сущность</t>
+          <t>Комментарий</t>
         </is>
       </c>
       <c r="E131" s="13" t="inlineStr">
         <is>
-          <t>audit_log.entity</t>
+          <t>money_income.comment</t>
         </is>
       </c>
       <c r="G131" s="13" t="inlineStr">
         <is>
-          <t>varchar(100)</t>
+          <t>varchar(500) NULL</t>
         </is>
       </c>
       <c r="J131" s="14" t="inlineStr">
         <is>
-          <t>Имя таблицы/сущности, которую изменили.</t>
+          <t>Основание пополнения.</t>
         </is>
       </c>
       <c r="K131" s="13" t="inlineStr">
@@ -17467,7 +17459,7 @@
       <c r="M131" s="13" t="inlineStr"/>
       <c r="N131" s="13" t="inlineStr">
         <is>
-          <t>String(100)</t>
+          <t>String(500)</t>
         </is>
       </c>
       <c r="O131" s="13" t="inlineStr"/>
@@ -17476,27 +17468,15 @@
       <c r="R131" s="13" t="inlineStr"/>
       <c r="S131" s="13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="T131" s="13" t="inlineStr"/>
-      <c r="U131" s="13" t="inlineStr">
-        <is>
-          <t>True (composite (entity, entity_id))</t>
-        </is>
-      </c>
-      <c r="V131" s="13" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
+      <c r="U131" s="13" t="inlineStr"/>
+      <c r="V131" s="13" t="inlineStr"/>
       <c r="W131" s="13" t="inlineStr"/>
       <c r="X131" s="14" t="inlineStr"/>
-      <c r="Y131" s="13" t="inlineStr">
-        <is>
-          <t>entity</t>
-        </is>
-      </c>
+      <c r="Y131" s="13" t="inlineStr"/>
       <c r="Z131" s="13" t="inlineStr"/>
       <c r="AA131" s="13" t="inlineStr"/>
       <c r="AB131" s="13" t="inlineStr"/>
@@ -17509,7 +17489,7 @@
       <c r="AI131" s="14" t="inlineStr"/>
       <c r="AJ131" s="13" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AK131" s="13" t="inlineStr">
@@ -17524,20 +17504,16 @@
       </c>
       <c r="AM131" s="13" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="AN131" s="13" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="AN131" s="13" t="inlineStr"/>
       <c r="AO131" s="14" t="inlineStr"/>
       <c r="AP131" s="14" t="inlineStr"/>
       <c r="AQ131" s="14" t="inlineStr"/>
       <c r="AR131" s="13" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AS131" s="13" t="inlineStr">
@@ -17547,7 +17523,7 @@
       </c>
       <c r="AT131" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="AU131" s="13" t="inlineStr">
@@ -17559,7 +17535,7 @@
     <row r="132">
       <c r="A132" s="13" t="inlineStr">
         <is>
-          <t>ТЗ §3 М7 audit_log</t>
+          <t>ТЗ §3 М5 money_expense · AP-8</t>
         </is>
       </c>
       <c r="B132" s="13" t="inlineStr"/>
@@ -17570,22 +17546,22 @@
       </c>
       <c r="D132" s="14" t="inlineStr">
         <is>
-          <t>ID сущности</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E132" s="13" t="inlineStr">
         <is>
-          <t>audit_log.entity_id</t>
+          <t>money_expense.id</t>
         </is>
       </c>
       <c r="G132" s="13" t="inlineStr">
         <is>
-          <t>bigint NULL</t>
+          <t>bigserial</t>
         </is>
       </c>
       <c r="J132" s="14" t="inlineStr">
         <is>
-          <t>ID изменённой записи. NULL для действий без объекта (например, login).</t>
+          <t>Суррогатный первичный ключ.</t>
         </is>
       </c>
       <c r="K132" s="13" t="inlineStr">
@@ -17600,19 +17576,27 @@
           <t>BigInteger</t>
         </is>
       </c>
-      <c r="O132" s="13" t="inlineStr"/>
-      <c r="P132" s="13" t="inlineStr"/>
+      <c r="O132" s="13" t="inlineStr">
+        <is>
+          <t>autoincrement (Identity)</t>
+        </is>
+      </c>
+      <c r="P132" s="13" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
       <c r="Q132" s="13" t="inlineStr"/>
       <c r="R132" s="13" t="inlineStr"/>
       <c r="S132" s="13" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T132" s="13" t="inlineStr"/>
       <c r="U132" s="13" t="inlineStr">
         <is>
-          <t>True (composite (entity, entity_id))</t>
+          <t>True (PK)</t>
         </is>
       </c>
       <c r="V132" s="13" t="inlineStr">
@@ -17621,10 +17605,14 @@
         </is>
       </c>
       <c r="W132" s="13" t="inlineStr"/>
-      <c r="X132" s="14" t="inlineStr"/>
+      <c r="X132" s="14" t="inlineStr">
+        <is>
+          <t>PRIMARY KEY</t>
+        </is>
+      </c>
       <c r="Y132" s="13" t="inlineStr">
         <is>
-          <t>entity_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="Z132" s="13" t="inlineStr"/>
@@ -17639,7 +17627,7 @@
       <c r="AI132" s="14" t="inlineStr"/>
       <c r="AJ132" s="13" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AK132" s="13" t="inlineStr">
@@ -17685,7 +17673,7 @@
     <row r="133">
       <c r="A133" s="13" t="inlineStr">
         <is>
-          <t>ТЗ §3 М7 audit_log</t>
+          <t>ТЗ §3 М5 money_expense · AP-8 · SV-6</t>
         </is>
       </c>
       <c r="B133" s="13" t="inlineStr"/>
@@ -17696,22 +17684,22 @@
       </c>
       <c r="D133" s="14" t="inlineStr">
         <is>
-          <t>Изменения</t>
+          <t>Касса</t>
         </is>
       </c>
       <c r="E133" s="13" t="inlineStr">
         <is>
-          <t>audit_log.payload_diff</t>
+          <t>money_expense.cash_desk_id</t>
         </is>
       </c>
       <c r="G133" s="13" t="inlineStr">
         <is>
-          <t>jsonb NULL</t>
+          <t>bigint FK</t>
         </is>
       </c>
       <c r="J133" s="14" t="inlineStr">
         <is>
-          <t>Диф значений до/после.</t>
+          <t>Касса списания. ОПРЕДЕЛЯЕТСЯ СЕРВЕРОМ из users.category (SV-6).</t>
         </is>
       </c>
       <c r="K133" s="13" t="inlineStr">
@@ -17723,28 +17711,44 @@
       <c r="M133" s="13" t="inlineStr"/>
       <c r="N133" s="13" t="inlineStr">
         <is>
-          <t>JSONB</t>
+          <t>BigInteger · ForeignKey('cash_desks.id', ondelete='RESTRICT')</t>
         </is>
       </c>
       <c r="O133" s="13" t="inlineStr"/>
       <c r="P133" s="13" t="inlineStr"/>
-      <c r="Q133" s="13" t="inlineStr"/>
+      <c r="Q133" s="13" t="inlineStr">
+        <is>
+          <t>relationship CashDesk</t>
+        </is>
+      </c>
       <c r="R133" s="13" t="inlineStr"/>
       <c r="S133" s="13" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T133" s="13" t="inlineStr"/>
-      <c r="U133" s="13" t="inlineStr"/>
+      <c r="U133" s="13" t="inlineStr">
+        <is>
+          <t>True (composite (cash_desk_id, date DESC) — AP-8)</t>
+        </is>
+      </c>
       <c r="V133" s="13" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="W133" s="13" t="inlineStr"/>
+      <c r="W133" s="13" t="inlineStr">
+        <is>
+          <t>RESTRICT</t>
+        </is>
+      </c>
       <c r="X133" s="14" t="inlineStr"/>
-      <c r="Y133" s="13" t="inlineStr"/>
+      <c r="Y133" s="13" t="inlineStr">
+        <is>
+          <t>cash_desk_id</t>
+        </is>
+      </c>
       <c r="Z133" s="13" t="inlineStr"/>
       <c r="AA133" s="13" t="inlineStr"/>
       <c r="AB133" s="13" t="inlineStr"/>
@@ -17757,12 +17761,12 @@
       <c r="AI133" s="14" t="inlineStr"/>
       <c r="AJ133" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="AK133" s="13" t="inlineStr">
         <is>
-          <t>textarea</t>
+          <t>select</t>
         </is>
       </c>
       <c r="AL133" s="13" t="inlineStr">
@@ -17779,13 +17783,13 @@
       <c r="AO133" s="14" t="inlineStr"/>
       <c r="AP133" s="14" t="inlineStr">
         <is>
-          <t>Индекс GIN не создаём: поиск по телу дифа в ТЗ не заявлен (нет access pattern).</t>
+          <t>SV-6: клиент кассу НЕ присылает (create=—). Иначе учитель спишет из кассы работников, подделав тело запроса. AP-9: FOR UPDATE по cash_desks при расходе.</t>
         </is>
       </c>
       <c r="AQ133" s="14" t="inlineStr"/>
       <c r="AR133" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="AS133" s="13" t="inlineStr">
@@ -17807,7 +17811,7 @@
     <row r="134">
       <c r="A134" s="13" t="inlineStr">
         <is>
-          <t>ТЗ §3 М7 audit_log</t>
+          <t>ТЗ §3 М5 money_expense · AP-8 · AP-8</t>
         </is>
       </c>
       <c r="B134" s="13" t="inlineStr"/>
@@ -17818,22 +17822,22 @@
       </c>
       <c r="D134" s="14" t="inlineStr">
         <is>
-          <t>IP</t>
+          <t>Сотрудник</t>
         </is>
       </c>
       <c r="E134" s="13" t="inlineStr">
         <is>
-          <t>audit_log.ip</t>
+          <t>money_expense.employee_id</t>
         </is>
       </c>
       <c r="G134" s="13" t="inlineStr">
         <is>
-          <t>inet NULL</t>
+          <t>bigint FK</t>
         </is>
       </c>
       <c r="J134" s="14" t="inlineStr">
         <is>
-          <t>IP-адрес источника запроса.</t>
+          <t>Кто потратил. Из JWT (сотрудник видит только свои расходы, §1.3).</t>
         </is>
       </c>
       <c r="K134" s="13" t="inlineStr">
@@ -17845,30 +17849,42 @@
       <c r="M134" s="13" t="inlineStr"/>
       <c r="N134" s="13" t="inlineStr">
         <is>
-          <t>INET (postgresql.INET)</t>
+          <t>BigInteger · ForeignKey('users.id', ondelete='RESTRICT')</t>
         </is>
       </c>
       <c r="O134" s="13" t="inlineStr"/>
       <c r="P134" s="13" t="inlineStr"/>
-      <c r="Q134" s="13" t="inlineStr"/>
+      <c r="Q134" s="13" t="inlineStr">
+        <is>
+          <t>relationship User</t>
+        </is>
+      </c>
       <c r="R134" s="13" t="inlineStr"/>
       <c r="S134" s="13" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T134" s="13" t="inlineStr"/>
-      <c r="U134" s="13" t="inlineStr"/>
+      <c r="U134" s="13" t="inlineStr">
+        <is>
+          <t>True (composite (employee_id, date DESC) — AP-8)</t>
+        </is>
+      </c>
       <c r="V134" s="13" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="W134" s="13" t="inlineStr"/>
+      <c r="W134" s="13" t="inlineStr">
+        <is>
+          <t>RESTRICT</t>
+        </is>
+      </c>
       <c r="X134" s="14" t="inlineStr"/>
       <c r="Y134" s="13" t="inlineStr">
         <is>
-          <t>ip</t>
+          <t>employee_id</t>
         </is>
       </c>
       <c r="Z134" s="13" t="inlineStr"/>
@@ -17883,12 +17899,12 @@
       <c r="AI134" s="14" t="inlineStr"/>
       <c r="AJ134" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="AK134" s="13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select</t>
         </is>
       </c>
       <c r="AL134" s="13" t="inlineStr">
@@ -17903,15 +17919,11 @@
         </is>
       </c>
       <c r="AO134" s="14" t="inlineStr"/>
-      <c r="AP134" s="14" t="inlineStr">
-        <is>
-          <t>Нативный inet, а не varchar: корректная валидация и сравнение подсетей.</t>
-        </is>
-      </c>
+      <c r="AP134" s="14" t="inlineStr"/>
       <c r="AQ134" s="14" t="inlineStr"/>
       <c r="AR134" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="AS134" s="13" t="inlineStr">
@@ -17933,7 +17945,7 @@
     <row r="135">
       <c r="A135" s="13" t="inlineStr">
         <is>
-          <t>ТЗ §3 М7 audit_log</t>
+          <t>ТЗ §3 М5 money_expense · AP-8 · AP-8</t>
         </is>
       </c>
       <c r="B135" s="13" t="inlineStr"/>
@@ -17944,22 +17956,22 @@
       </c>
       <c r="D135" s="14" t="inlineStr">
         <is>
-          <t>Когда</t>
+          <t>Вид расхода</t>
         </is>
       </c>
       <c r="E135" s="13" t="inlineStr">
         <is>
-          <t>audit_log.created_at</t>
+          <t>money_expense.expense_category_id</t>
         </is>
       </c>
       <c r="G135" s="13" t="inlineStr">
         <is>
-          <t>timestamptz</t>
+          <t>bigint FK</t>
         </is>
       </c>
       <c r="J135" s="14" t="inlineStr">
         <is>
-          <t>Момент действия.</t>
+          <t>Вид расхода денег. Обязательный фильтр отчёта ДДС (AP-8).</t>
         </is>
       </c>
       <c r="K135" s="13" t="inlineStr">
@@ -17971,46 +17983,46 @@
       <c r="M135" s="13" t="inlineStr"/>
       <c r="N135" s="13" t="inlineStr">
         <is>
-          <t>DateTime(timezone=True)</t>
-        </is>
-      </c>
-      <c r="O135" s="13" t="inlineStr">
-        <is>
-          <t>server_default=func.now()</t>
-        </is>
-      </c>
+          <t>BigInteger · ForeignKey('expense_categories.id', ondelete='RESTRICT')</t>
+        </is>
+      </c>
+      <c r="O135" s="13" t="inlineStr"/>
       <c r="P135" s="13" t="inlineStr"/>
-      <c r="Q135" s="13" t="inlineStr"/>
+      <c r="Q135" s="13" t="inlineStr">
+        <is>
+          <t>relationship ExpenseCategory</t>
+        </is>
+      </c>
       <c r="R135" s="13" t="inlineStr"/>
       <c r="S135" s="13" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="T135" s="13" t="inlineStr">
-        <is>
-          <t>now()</t>
-        </is>
-      </c>
+      <c r="T135" s="13" t="inlineStr"/>
       <c r="U135" s="13" t="inlineStr">
         <is>
-          <t>True (created_at DESC)</t>
-        </is>
-      </c>
-      <c r="V135" s="13" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="W135" s="13" t="inlineStr"/>
+          <t>True (composite (expense_category_id, date DESC) — AP-8)</t>
+        </is>
+      </c>
+      <c r="V135" s="13" t="inlineStr"/>
+      <c r="W135" s="13" t="inlineStr">
+        <is>
+          <t>RESTRICT</t>
+        </is>
+      </c>
       <c r="X135" s="14" t="inlineStr"/>
       <c r="Y135" s="13" t="inlineStr">
         <is>
-          <t>created_at__range</t>
+          <t>expense_category_id</t>
         </is>
       </c>
       <c r="Z135" s="13" t="inlineStr"/>
-      <c r="AA135" s="13" t="inlineStr"/>
+      <c r="AA135" s="13" t="inlineStr">
+        <is>
+          <t>GET /expense-categories?status=active</t>
+        </is>
+      </c>
       <c r="AB135" s="13" t="inlineStr"/>
       <c r="AC135" s="13" t="inlineStr"/>
       <c r="AD135" s="13" t="inlineStr"/>
@@ -18026,22 +18038,22 @@
       </c>
       <c r="AK135" s="13" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select</t>
         </is>
       </c>
       <c r="AL135" s="13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AM135" s="13" t="inlineStr"/>
-      <c r="AN135" s="13" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
+      <c r="AN135" s="13" t="inlineStr"/>
       <c r="AO135" s="14" t="inlineStr"/>
-      <c r="AP135" s="14" t="inlineStr"/>
+      <c r="AP135" s="14" t="inlineStr">
+        <is>
+          <t>AP-8: «фильтр по категории обязателен» — под это отдельный composite-индекс.</t>
+        </is>
+      </c>
       <c r="AQ135" s="14" t="inlineStr"/>
       <c r="AR135" s="13" t="inlineStr">
         <is>
@@ -18055,21 +18067,1811 @@
       </c>
       <c r="AT135" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="AU135" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="13" t="inlineStr">
+        <is>
+          <t>ТЗ §3 М5 money_expense · AP-8</t>
+        </is>
+      </c>
+      <c r="B136" s="13" t="inlineStr"/>
+      <c r="C136" s="13" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="D136" s="14" t="inlineStr">
+        <is>
+          <t>Сумма расхода</t>
+        </is>
+      </c>
+      <c r="E136" s="13" t="inlineStr">
+        <is>
+          <t>money_expense.amount</t>
+        </is>
+      </c>
+      <c r="G136" s="13" t="inlineStr">
+        <is>
+          <t>numeric(18,2)</t>
+        </is>
+      </c>
+      <c r="J136" s="14" t="inlineStr">
+        <is>
+          <t>Сумма расхода, UZS.</t>
+        </is>
+      </c>
+      <c r="K136" s="13" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="L136" s="13" t="inlineStr"/>
+      <c r="M136" s="13" t="inlineStr"/>
+      <c r="N136" s="13" t="inlineStr">
+        <is>
+          <t>Numeric(18, 2)</t>
+        </is>
+      </c>
+      <c r="O136" s="13" t="inlineStr"/>
+      <c r="P136" s="13" t="inlineStr"/>
+      <c r="Q136" s="13" t="inlineStr"/>
+      <c r="R136" s="13" t="inlineStr"/>
+      <c r="S136" s="13" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="T136" s="13" t="inlineStr"/>
+      <c r="U136" s="13" t="inlineStr"/>
+      <c r="V136" s="13" t="inlineStr"/>
+      <c r="W136" s="13" t="inlineStr"/>
+      <c r="X136" s="14" t="inlineStr">
+        <is>
+          <t>CHECK (amount &gt; 0)</t>
+        </is>
+      </c>
+      <c r="Y136" s="13" t="inlineStr"/>
+      <c r="Z136" s="13" t="inlineStr"/>
+      <c r="AA136" s="13" t="inlineStr"/>
+      <c r="AB136" s="13" t="inlineStr"/>
+      <c r="AC136" s="13" t="inlineStr"/>
+      <c r="AD136" s="13" t="inlineStr"/>
+      <c r="AE136" s="13" t="inlineStr"/>
+      <c r="AF136" s="13" t="inlineStr"/>
+      <c r="AG136" s="13" t="inlineStr"/>
+      <c r="AH136" s="13" t="inlineStr"/>
+      <c r="AI136" s="14" t="inlineStr"/>
+      <c r="AJ136" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AK136" s="13" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="AL136" s="13" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AM136" s="13" t="inlineStr"/>
+      <c r="AN136" s="13" t="inlineStr"/>
+      <c r="AO136" s="14" t="inlineStr">
+        <is>
+          <t>required; &gt; 0; 2 знака; UZS; ≤ баланса кассы (сервер — истина, ОВ-2)</t>
+        </is>
+      </c>
+      <c r="AP136" s="14" t="inlineStr"/>
+      <c r="AQ136" s="14" t="inlineStr"/>
+      <c r="AR136" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS136" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AT136" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AU136" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="13" t="inlineStr">
+        <is>
+          <t>ТЗ §3 М5 money_expense · AP-8</t>
+        </is>
+      </c>
+      <c r="B137" s="13" t="inlineStr"/>
+      <c r="C137" s="13" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="D137" s="14" t="inlineStr">
+        <is>
+          <t>Описание</t>
+        </is>
+      </c>
+      <c r="E137" s="13" t="inlineStr">
+        <is>
+          <t>money_expense.description</t>
+        </is>
+      </c>
+      <c r="G137" s="13" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="J137" s="14" t="inlineStr">
+        <is>
+          <t>На что потрачены деньги.</t>
+        </is>
+      </c>
+      <c r="K137" s="13" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="L137" s="13" t="inlineStr"/>
+      <c r="M137" s="13" t="inlineStr"/>
+      <c r="N137" s="13" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="O137" s="13" t="inlineStr"/>
+      <c r="P137" s="13" t="inlineStr"/>
+      <c r="Q137" s="13" t="inlineStr"/>
+      <c r="R137" s="13" t="inlineStr"/>
+      <c r="S137" s="13" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="T137" s="13" t="inlineStr"/>
+      <c r="U137" s="13" t="inlineStr"/>
+      <c r="V137" s="13" t="inlineStr"/>
+      <c r="W137" s="13" t="inlineStr"/>
+      <c r="X137" s="14" t="inlineStr">
+        <is>
+          <t>CHECK (length(trim(description)) &gt; 0)</t>
+        </is>
+      </c>
+      <c r="Y137" s="13" t="inlineStr"/>
+      <c r="Z137" s="13" t="inlineStr"/>
+      <c r="AA137" s="13" t="inlineStr"/>
+      <c r="AB137" s="13" t="inlineStr"/>
+      <c r="AC137" s="13" t="inlineStr"/>
+      <c r="AD137" s="13" t="inlineStr"/>
+      <c r="AE137" s="13" t="inlineStr"/>
+      <c r="AF137" s="13" t="inlineStr"/>
+      <c r="AG137" s="13" t="inlineStr"/>
+      <c r="AH137" s="13" t="inlineStr"/>
+      <c r="AI137" s="14" t="inlineStr"/>
+      <c r="AJ137" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AK137" s="13" t="inlineStr">
+        <is>
+          <t>textarea</t>
+        </is>
+      </c>
+      <c r="AL137" s="13" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AM137" s="13" t="inlineStr"/>
+      <c r="AN137" s="13" t="inlineStr"/>
+      <c r="AO137" s="14" t="inlineStr">
+        <is>
+          <t>required; непустая строка</t>
+        </is>
+      </c>
+      <c r="AP137" s="14" t="inlineStr"/>
+      <c r="AQ137" s="14" t="inlineStr"/>
+      <c r="AR137" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AS137" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AT137" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AU137" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="13" t="inlineStr">
+        <is>
+          <t>ТЗ §3 М5 money_expense · AP-8 · INV-7</t>
+        </is>
+      </c>
+      <c r="B138" s="13" t="inlineStr"/>
+      <c r="C138" s="13" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="D138" s="14" t="inlineStr">
+        <is>
+          <t>Чек</t>
+        </is>
+      </c>
+      <c r="E138" s="13" t="inlineStr">
+        <is>
+          <t>money_expense.receipt_url</t>
+        </is>
+      </c>
+      <c r="G138" s="13" t="inlineStr">
+        <is>
+          <t>varchar(500)</t>
+        </is>
+      </c>
+      <c r="J138" s="14" t="inlineStr">
+        <is>
+          <t>Ключ объекта чека в MinIO (бакет receipts). NOT NULL — чек обязателен (§7.3).</t>
+        </is>
+      </c>
+      <c r="K138" s="13" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="L138" s="13" t="inlineStr"/>
+      <c r="M138" s="13" t="inlineStr"/>
+      <c r="N138" s="13" t="inlineStr">
+        <is>
+          <t>String(500)</t>
+        </is>
+      </c>
+      <c r="O138" s="13" t="inlineStr"/>
+      <c r="P138" s="13" t="inlineStr"/>
+      <c r="Q138" s="13" t="inlineStr"/>
+      <c r="R138" s="13" t="inlineStr"/>
+      <c r="S138" s="13" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="T138" s="13" t="inlineStr"/>
+      <c r="U138" s="13" t="inlineStr"/>
+      <c r="V138" s="13" t="inlineStr"/>
+      <c r="W138" s="13" t="inlineStr"/>
+      <c r="X138" s="14" t="inlineStr">
+        <is>
+          <t>INV-7: NOT NULL + CHECK (length(trim(receipt_url)) &gt; 0) — иначе пустая строка обойдёт NOT NULL</t>
+        </is>
+      </c>
+      <c r="Y138" s="13" t="inlineStr"/>
+      <c r="Z138" s="13" t="inlineStr"/>
+      <c r="AA138" s="13" t="inlineStr"/>
+      <c r="AB138" s="13" t="inlineStr"/>
+      <c r="AC138" s="13" t="inlineStr"/>
+      <c r="AD138" s="13" t="inlineStr"/>
+      <c r="AE138" s="13" t="inlineStr"/>
+      <c r="AF138" s="13" t="inlineStr"/>
+      <c r="AG138" s="13" t="inlineStr"/>
+      <c r="AH138" s="13" t="inlineStr"/>
+      <c r="AI138" s="14" t="inlineStr"/>
+      <c r="AJ138" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AK138" s="13" t="inlineStr">
+        <is>
+          <t>file</t>
+        </is>
+      </c>
+      <c r="AL138" s="13" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AM138" s="13" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="AN138" s="13" t="inlineStr"/>
+      <c r="AO138" s="14" t="inlineStr">
+        <is>
+          <t>required; whitelist jpg/png/pdf; ≤ 10 МБ; проверка по magic bytes (сервер)</t>
+        </is>
+      </c>
+      <c r="AP138" s="14" t="inlineStr">
+        <is>
+          <t>INV-7. Загрузка: POST /cash/expenses/{id}/receipt. Хранится ключ, наружу — presigned URL TTL 5 мин, бакет приватный.</t>
+        </is>
+      </c>
+      <c r="AQ138" s="14" t="inlineStr"/>
+      <c r="AR138" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AS138" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AT138" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AU138" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="13" t="inlineStr">
+        <is>
+          <t>ТЗ §3 М5 money_expense · AP-8 · AP-8</t>
+        </is>
+      </c>
+      <c r="B139" s="13" t="inlineStr"/>
+      <c r="C139" s="13" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="D139" s="14" t="inlineStr">
+        <is>
+          <t>Дата</t>
+        </is>
+      </c>
+      <c r="E139" s="13" t="inlineStr">
+        <is>
+          <t>money_expense.date</t>
+        </is>
+      </c>
+      <c r="G139" s="13" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="J139" s="14" t="inlineStr">
+        <is>
+          <t>Дата расхода. Ключ периода в отчёте ДДС.</t>
+        </is>
+      </c>
+      <c r="K139" s="13" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="L139" s="13" t="inlineStr"/>
+      <c r="M139" s="13" t="inlineStr"/>
+      <c r="N139" s="13" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="O139" s="13" t="inlineStr"/>
+      <c r="P139" s="13" t="inlineStr"/>
+      <c r="Q139" s="13" t="inlineStr"/>
+      <c r="R139" s="13" t="inlineStr"/>
+      <c r="S139" s="13" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="T139" s="13" t="inlineStr"/>
+      <c r="U139" s="13" t="inlineStr">
+        <is>
+          <t>True (в составе composite-индексов AP-8)</t>
+        </is>
+      </c>
+      <c r="V139" s="13" t="inlineStr"/>
+      <c r="W139" s="13" t="inlineStr"/>
+      <c r="X139" s="14" t="inlineStr"/>
+      <c r="Y139" s="13" t="inlineStr">
+        <is>
+          <t>date__range</t>
+        </is>
+      </c>
+      <c r="Z139" s="13" t="inlineStr"/>
+      <c r="AA139" s="13" t="inlineStr"/>
+      <c r="AB139" s="13" t="inlineStr"/>
+      <c r="AC139" s="13" t="inlineStr"/>
+      <c r="AD139" s="13" t="inlineStr"/>
+      <c r="AE139" s="13" t="inlineStr"/>
+      <c r="AF139" s="13" t="inlineStr"/>
+      <c r="AG139" s="13" t="inlineStr"/>
+      <c r="AH139" s="13" t="inlineStr"/>
+      <c r="AI139" s="14" t="inlineStr"/>
+      <c r="AJ139" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AK139" s="13" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="AL139" s="13" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AM139" s="13" t="inlineStr"/>
+      <c r="AN139" s="13" t="inlineStr"/>
+      <c r="AO139" s="14" t="inlineStr"/>
+      <c r="AP139" s="14" t="inlineStr"/>
+      <c r="AQ139" s="14" t="inlineStr"/>
+      <c r="AR139" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS139" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AT139" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AU139" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="13" t="inlineStr">
+        <is>
+          <t>спека13 §4</t>
+        </is>
+      </c>
+      <c r="B140" s="13" t="inlineStr"/>
+      <c r="C140" s="13" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="D140" s="14" t="inlineStr">
+        <is>
+          <t>Передано (дата)</t>
+        </is>
+      </c>
+      <c r="E140" s="13" t="inlineStr">
+        <is>
+          <t>money_expense.submitted_at</t>
+        </is>
+      </c>
+      <c r="G140" s="13" t="inlineStr">
+        <is>
+          <t>date NULL</t>
+        </is>
+      </c>
+      <c r="J140" s="14" t="inlineStr">
+        <is>
+          <t>Дата передачи расхода в бухгалтерию (bulk-действие). У денег НЕТ этапа подписи — чек заменяет §7.3, расход готов к передаче сразу после проведения. NULL = «Не передано».</t>
+        </is>
+      </c>
+      <c r="K140" s="13" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="L140" s="13" t="inlineStr"/>
+      <c r="M140" s="13" t="inlineStr"/>
+      <c r="N140" s="13" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="O140" s="13" t="inlineStr"/>
+      <c r="P140" s="13" t="inlineStr"/>
+      <c r="Q140" s="13" t="inlineStr"/>
+      <c r="R140" s="13" t="inlineStr"/>
+      <c r="S140" s="13" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T140" s="13" t="inlineStr"/>
+      <c r="U140" s="13" t="inlineStr"/>
+      <c r="V140" s="13" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="W140" s="13" t="inlineStr"/>
+      <c r="X140" s="14" t="inlineStr">
+        <is>
+          <t>Частичный индекс ix_money_expense_not_submitted (id) WHERE submitted_at IS NULL — фильтр «Не передано»/actionable-набор. На самой колонке btree нет (индексируется id по предикату), как в прежнем ix_requests_to_print.</t>
+        </is>
+      </c>
+      <c r="Y140" s="13" t="inlineStr">
+        <is>
+          <t>submitted_at__range</t>
+        </is>
+      </c>
+      <c r="Z140" s="13" t="inlineStr"/>
+      <c r="AA140" s="13" t="inlineStr"/>
+      <c r="AB140" s="13" t="inlineStr"/>
+      <c r="AC140" s="13" t="inlineStr"/>
+      <c r="AD140" s="13" t="inlineStr"/>
+      <c r="AE140" s="13" t="inlineStr"/>
+      <c r="AF140" s="13" t="inlineStr"/>
+      <c r="AG140" s="13" t="inlineStr"/>
+      <c r="AH140" s="13" t="inlineStr"/>
+      <c r="AI140" s="14" t="inlineStr"/>
+      <c r="AJ140" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AK140" s="13" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="AL140" s="13" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AM140" s="13" t="inlineStr"/>
+      <c r="AN140" s="13" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AO140" s="14" t="inlineStr"/>
+      <c r="AP140" s="14" t="inlineStr">
+        <is>
+          <t>Ставит сервер (bulk «Передать в бухгалтерию», ЭТАП 2). У денег нет статуса, поэтому «Передано / Не передано» различается только по этому полю; под фильтр «Не передано» заведён частичный индекс ix_money_expense_not_submitted. Read-поле выведено (get_index/get_single) для фильтра «Передано/Не передано» и реестра передачи.</t>
+        </is>
+      </c>
+      <c r="AQ140" s="14" t="inlineStr"/>
+      <c r="AR140" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS140" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AT140" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU140" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="13" t="inlineStr">
+        <is>
+          <t>спека13 §4</t>
+        </is>
+      </c>
+      <c r="B141" s="13" t="inlineStr"/>
+      <c r="C141" s="13" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="D141" s="14" t="inlineStr">
+        <is>
+          <t>Реестр передачи №</t>
+        </is>
+      </c>
+      <c r="E141" s="13" t="inlineStr">
+        <is>
+          <t>money_expense.submitted_register_no</t>
+        </is>
+      </c>
+      <c r="G141" s="13" t="inlineStr">
+        <is>
+          <t>varchar(32) NULL</t>
+        </is>
+      </c>
+      <c r="J141" s="14" t="inlineStr">
+        <is>
+          <t>Номер реестра передачи (один на пачку передачи денег). NULL до передачи.</t>
+        </is>
+      </c>
+      <c r="K141" s="13" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="L141" s="13" t="inlineStr"/>
+      <c r="M141" s="13" t="inlineStr"/>
+      <c r="N141" s="13" t="inlineStr">
+        <is>
+          <t>String(32)</t>
+        </is>
+      </c>
+      <c r="O141" s="13" t="inlineStr"/>
+      <c r="P141" s="13" t="inlineStr"/>
+      <c r="Q141" s="13" t="inlineStr"/>
+      <c r="R141" s="13" t="inlineStr"/>
+      <c r="S141" s="13" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T141" s="13" t="inlineStr"/>
+      <c r="U141" s="13" t="inlineStr"/>
+      <c r="V141" s="13" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="W141" s="13" t="inlineStr"/>
+      <c r="X141" s="14" t="inlineStr"/>
+      <c r="Y141" s="13" t="inlineStr">
+        <is>
+          <t>submitted_register_no</t>
+        </is>
+      </c>
+      <c r="Z141" s="13" t="inlineStr"/>
+      <c r="AA141" s="13" t="inlineStr"/>
+      <c r="AB141" s="13" t="inlineStr"/>
+      <c r="AC141" s="13" t="inlineStr"/>
+      <c r="AD141" s="13" t="inlineStr"/>
+      <c r="AE141" s="13" t="inlineStr"/>
+      <c r="AF141" s="13" t="inlineStr"/>
+      <c r="AG141" s="13" t="inlineStr"/>
+      <c r="AH141" s="13" t="inlineStr"/>
+      <c r="AI141" s="14" t="inlineStr"/>
+      <c r="AJ141" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AK141" s="13" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="AL141" s="13" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AM141" s="13" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="AN141" s="13" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AO141" s="14" t="inlineStr"/>
+      <c r="AP141" s="14" t="inlineStr">
+        <is>
+          <t>Серверная серия. Отдельный реестр для товара и денег (спека §4). Индекса нет: печать реестра по требованию, не горячий путь. Read-поле выведено (get_index/get_single) для реестра передачи денег.</t>
+        </is>
+      </c>
+      <c r="AQ141" s="14" t="inlineStr"/>
+      <c r="AR141" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS141" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AT141" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU141" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="13" t="inlineStr">
+        <is>
+          <t>ТЗ §3 М7 audit_log</t>
+        </is>
+      </c>
+      <c r="B142" s="13" t="inlineStr"/>
+      <c r="C142" s="13" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="D142" s="14" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="E142" s="13" t="inlineStr">
+        <is>
+          <t>audit_log.id</t>
+        </is>
+      </c>
+      <c r="G142" s="13" t="inlineStr">
+        <is>
+          <t>bigserial</t>
+        </is>
+      </c>
+      <c r="J142" s="14" t="inlineStr">
+        <is>
+          <t>Суррогатный первичный ключ.</t>
+        </is>
+      </c>
+      <c r="K142" s="13" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="L142" s="13" t="inlineStr"/>
+      <c r="M142" s="13" t="inlineStr"/>
+      <c r="N142" s="13" t="inlineStr">
+        <is>
+          <t>BigInteger</t>
+        </is>
+      </c>
+      <c r="O142" s="13" t="inlineStr">
+        <is>
+          <t>autoincrement (Identity)</t>
+        </is>
+      </c>
+      <c r="P142" s="13" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Q142" s="13" t="inlineStr"/>
+      <c r="R142" s="13" t="inlineStr"/>
+      <c r="S142" s="13" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="T142" s="13" t="inlineStr"/>
+      <c r="U142" s="13" t="inlineStr">
+        <is>
+          <t>True (PK)</t>
+        </is>
+      </c>
+      <c r="V142" s="13" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="W142" s="13" t="inlineStr"/>
+      <c r="X142" s="14" t="inlineStr">
+        <is>
+          <t>PRIMARY KEY</t>
+        </is>
+      </c>
+      <c r="Y142" s="13" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="Z142" s="13" t="inlineStr"/>
+      <c r="AA142" s="13" t="inlineStr"/>
+      <c r="AB142" s="13" t="inlineStr"/>
+      <c r="AC142" s="13" t="inlineStr"/>
+      <c r="AD142" s="13" t="inlineStr"/>
+      <c r="AE142" s="13" t="inlineStr"/>
+      <c r="AF142" s="13" t="inlineStr"/>
+      <c r="AG142" s="13" t="inlineStr"/>
+      <c r="AH142" s="13" t="inlineStr"/>
+      <c r="AI142" s="14" t="inlineStr"/>
+      <c r="AJ142" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AK142" s="13" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="AL142" s="13" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AM142" s="13" t="inlineStr"/>
+      <c r="AN142" s="13" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AO142" s="14" t="inlineStr"/>
+      <c r="AP142" s="14" t="inlineStr"/>
+      <c r="AQ142" s="14" t="inlineStr"/>
+      <c r="AR142" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS142" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AT142" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU142" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="13" t="inlineStr">
+        <is>
+          <t>ТЗ §3 М7 audit_log</t>
+        </is>
+      </c>
+      <c r="B143" s="13" t="inlineStr"/>
+      <c r="C143" s="13" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="D143" s="14" t="inlineStr">
+        <is>
+          <t>Пользователь</t>
+        </is>
+      </c>
+      <c r="E143" s="13" t="inlineStr">
+        <is>
+          <t>audit_log.user_id</t>
+        </is>
+      </c>
+      <c r="G143" s="13" t="inlineStr">
+        <is>
+          <t>bigint FK</t>
+        </is>
+      </c>
+      <c r="J143" s="14" t="inlineStr">
+        <is>
+          <t>Кто выполнил действие.</t>
+        </is>
+      </c>
+      <c r="K143" s="13" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="L143" s="13" t="inlineStr"/>
+      <c r="M143" s="13" t="inlineStr"/>
+      <c r="N143" s="13" t="inlineStr">
+        <is>
+          <t>BigInteger · ForeignKey('users.id', ondelete='RESTRICT')</t>
+        </is>
+      </c>
+      <c r="O143" s="13" t="inlineStr"/>
+      <c r="P143" s="13" t="inlineStr"/>
+      <c r="Q143" s="13" t="inlineStr">
+        <is>
+          <t>relationship User</t>
+        </is>
+      </c>
+      <c r="R143" s="13" t="inlineStr"/>
+      <c r="S143" s="13" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="T143" s="13" t="inlineStr"/>
+      <c r="U143" s="13" t="inlineStr">
+        <is>
+          <t>True (FK)</t>
+        </is>
+      </c>
+      <c r="V143" s="13" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="W143" s="13" t="inlineStr">
+        <is>
+          <t>RESTRICT</t>
+        </is>
+      </c>
+      <c r="X143" s="14" t="inlineStr"/>
+      <c r="Y143" s="13" t="inlineStr">
+        <is>
+          <t>user_id</t>
+        </is>
+      </c>
+      <c r="Z143" s="13" t="inlineStr"/>
+      <c r="AA143" s="13" t="inlineStr"/>
+      <c r="AB143" s="13" t="inlineStr"/>
+      <c r="AC143" s="13" t="inlineStr"/>
+      <c r="AD143" s="13" t="inlineStr"/>
+      <c r="AE143" s="13" t="inlineStr"/>
+      <c r="AF143" s="13" t="inlineStr"/>
+      <c r="AG143" s="13" t="inlineStr"/>
+      <c r="AH143" s="13" t="inlineStr"/>
+      <c r="AI143" s="14" t="inlineStr"/>
+      <c r="AJ143" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AK143" s="13" t="inlineStr">
+        <is>
+          <t>select</t>
+        </is>
+      </c>
+      <c r="AL143" s="13" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AM143" s="13" t="inlineStr"/>
+      <c r="AN143" s="13" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AO143" s="14" t="inlineStr"/>
+      <c r="AP143" s="14" t="inlineStr">
+        <is>
+          <t>Таблица append-only, пишет middleware. Чтение — только admin. API на запись нет.</t>
+        </is>
+      </c>
+      <c r="AQ143" s="14" t="inlineStr"/>
+      <c r="AR143" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS143" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AT143" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU143" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="13" t="inlineStr">
+        <is>
+          <t>ТЗ §3 М7 audit_log</t>
+        </is>
+      </c>
+      <c r="B144" s="13" t="inlineStr"/>
+      <c r="C144" s="13" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="D144" s="14" t="inlineStr">
+        <is>
+          <t>Действие</t>
+        </is>
+      </c>
+      <c r="E144" s="13" t="inlineStr">
+        <is>
+          <t>audit_log.action</t>
+        </is>
+      </c>
+      <c r="G144" s="13" t="inlineStr">
+        <is>
+          <t>varchar(50)</t>
+        </is>
+      </c>
+      <c r="J144" s="14" t="inlineStr">
+        <is>
+          <t>create | update | delete | issue | print и т.п.</t>
+        </is>
+      </c>
+      <c r="K144" s="13" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="L144" s="13" t="inlineStr"/>
+      <c r="M144" s="13" t="inlineStr"/>
+      <c r="N144" s="13" t="inlineStr">
+        <is>
+          <t>String(50)</t>
+        </is>
+      </c>
+      <c r="O144" s="13" t="inlineStr"/>
+      <c r="P144" s="13" t="inlineStr"/>
+      <c r="Q144" s="13" t="inlineStr"/>
+      <c r="R144" s="13" t="inlineStr"/>
+      <c r="S144" s="13" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="T144" s="13" t="inlineStr"/>
+      <c r="U144" s="13" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="V144" s="13" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="W144" s="13" t="inlineStr"/>
+      <c r="X144" s="14" t="inlineStr"/>
+      <c r="Y144" s="13" t="inlineStr">
+        <is>
+          <t>action</t>
+        </is>
+      </c>
+      <c r="Z144" s="13" t="inlineStr"/>
+      <c r="AA144" s="13" t="inlineStr"/>
+      <c r="AB144" s="13" t="inlineStr"/>
+      <c r="AC144" s="13" t="inlineStr"/>
+      <c r="AD144" s="13" t="inlineStr"/>
+      <c r="AE144" s="13" t="inlineStr"/>
+      <c r="AF144" s="13" t="inlineStr"/>
+      <c r="AG144" s="13" t="inlineStr"/>
+      <c r="AH144" s="13" t="inlineStr"/>
+      <c r="AI144" s="14" t="inlineStr"/>
+      <c r="AJ144" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AK144" s="13" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="AL144" s="13" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AM144" s="13" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="AN144" s="13" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AO144" s="14" t="inlineStr"/>
+      <c r="AP144" s="14" t="inlineStr">
+        <is>
+          <t>varchar, не enum: множество действий расширяется с каждым новым эндпоинтом, миграция типа на каждый чих не нужна.</t>
+        </is>
+      </c>
+      <c r="AQ144" s="14" t="inlineStr"/>
+      <c r="AR144" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS144" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AT144" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU144" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="13" t="inlineStr">
+        <is>
+          <t>ТЗ §3 М7 audit_log</t>
+        </is>
+      </c>
+      <c r="B145" s="13" t="inlineStr"/>
+      <c r="C145" s="13" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="D145" s="14" t="inlineStr">
+        <is>
+          <t>Сущность</t>
+        </is>
+      </c>
+      <c r="E145" s="13" t="inlineStr">
+        <is>
+          <t>audit_log.entity</t>
+        </is>
+      </c>
+      <c r="G145" s="13" t="inlineStr">
+        <is>
+          <t>varchar(100)</t>
+        </is>
+      </c>
+      <c r="J145" s="14" t="inlineStr">
+        <is>
+          <t>Имя таблицы/сущности, которую изменили.</t>
+        </is>
+      </c>
+      <c r="K145" s="13" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="L145" s="13" t="inlineStr"/>
+      <c r="M145" s="13" t="inlineStr"/>
+      <c r="N145" s="13" t="inlineStr">
+        <is>
+          <t>String(100)</t>
+        </is>
+      </c>
+      <c r="O145" s="13" t="inlineStr"/>
+      <c r="P145" s="13" t="inlineStr"/>
+      <c r="Q145" s="13" t="inlineStr"/>
+      <c r="R145" s="13" t="inlineStr"/>
+      <c r="S145" s="13" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="T145" s="13" t="inlineStr"/>
+      <c r="U145" s="13" t="inlineStr">
+        <is>
+          <t>True (composite (entity, entity_id))</t>
+        </is>
+      </c>
+      <c r="V145" s="13" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="W145" s="13" t="inlineStr"/>
+      <c r="X145" s="14" t="inlineStr"/>
+      <c r="Y145" s="13" t="inlineStr">
+        <is>
+          <t>entity</t>
+        </is>
+      </c>
+      <c r="Z145" s="13" t="inlineStr"/>
+      <c r="AA145" s="13" t="inlineStr"/>
+      <c r="AB145" s="13" t="inlineStr"/>
+      <c r="AC145" s="13" t="inlineStr"/>
+      <c r="AD145" s="13" t="inlineStr"/>
+      <c r="AE145" s="13" t="inlineStr"/>
+      <c r="AF145" s="13" t="inlineStr"/>
+      <c r="AG145" s="13" t="inlineStr"/>
+      <c r="AH145" s="13" t="inlineStr"/>
+      <c r="AI145" s="14" t="inlineStr"/>
+      <c r="AJ145" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AK145" s="13" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="AL145" s="13" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AM145" s="13" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="AN145" s="13" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AO145" s="14" t="inlineStr"/>
+      <c r="AP145" s="14" t="inlineStr"/>
+      <c r="AQ145" s="14" t="inlineStr"/>
+      <c r="AR145" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS145" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AT145" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU145" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="13" t="inlineStr">
+        <is>
+          <t>ТЗ §3 М7 audit_log</t>
+        </is>
+      </c>
+      <c r="B146" s="13" t="inlineStr"/>
+      <c r="C146" s="13" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="D146" s="14" t="inlineStr">
+        <is>
+          <t>ID сущности</t>
+        </is>
+      </c>
+      <c r="E146" s="13" t="inlineStr">
+        <is>
+          <t>audit_log.entity_id</t>
+        </is>
+      </c>
+      <c r="G146" s="13" t="inlineStr">
+        <is>
+          <t>bigint NULL</t>
+        </is>
+      </c>
+      <c r="J146" s="14" t="inlineStr">
+        <is>
+          <t>ID изменённой записи. NULL для действий без объекта (например, login).</t>
+        </is>
+      </c>
+      <c r="K146" s="13" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="L146" s="13" t="inlineStr"/>
+      <c r="M146" s="13" t="inlineStr"/>
+      <c r="N146" s="13" t="inlineStr">
+        <is>
+          <t>BigInteger</t>
+        </is>
+      </c>
+      <c r="O146" s="13" t="inlineStr"/>
+      <c r="P146" s="13" t="inlineStr"/>
+      <c r="Q146" s="13" t="inlineStr"/>
+      <c r="R146" s="13" t="inlineStr"/>
+      <c r="S146" s="13" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T146" s="13" t="inlineStr"/>
+      <c r="U146" s="13" t="inlineStr">
+        <is>
+          <t>True (composite (entity, entity_id))</t>
+        </is>
+      </c>
+      <c r="V146" s="13" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="W146" s="13" t="inlineStr"/>
+      <c r="X146" s="14" t="inlineStr"/>
+      <c r="Y146" s="13" t="inlineStr">
+        <is>
+          <t>entity_id</t>
+        </is>
+      </c>
+      <c r="Z146" s="13" t="inlineStr"/>
+      <c r="AA146" s="13" t="inlineStr"/>
+      <c r="AB146" s="13" t="inlineStr"/>
+      <c r="AC146" s="13" t="inlineStr"/>
+      <c r="AD146" s="13" t="inlineStr"/>
+      <c r="AE146" s="13" t="inlineStr"/>
+      <c r="AF146" s="13" t="inlineStr"/>
+      <c r="AG146" s="13" t="inlineStr"/>
+      <c r="AH146" s="13" t="inlineStr"/>
+      <c r="AI146" s="14" t="inlineStr"/>
+      <c r="AJ146" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AK146" s="13" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="AL146" s="13" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AM146" s="13" t="inlineStr"/>
+      <c r="AN146" s="13" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AO146" s="14" t="inlineStr"/>
+      <c r="AP146" s="14" t="inlineStr"/>
+      <c r="AQ146" s="14" t="inlineStr"/>
+      <c r="AR146" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS146" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AT146" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU146" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="13" t="inlineStr">
+        <is>
+          <t>ТЗ §3 М7 audit_log</t>
+        </is>
+      </c>
+      <c r="B147" s="13" t="inlineStr"/>
+      <c r="C147" s="13" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="D147" s="14" t="inlineStr">
+        <is>
+          <t>Изменения</t>
+        </is>
+      </c>
+      <c r="E147" s="13" t="inlineStr">
+        <is>
+          <t>audit_log.payload_diff</t>
+        </is>
+      </c>
+      <c r="G147" s="13" t="inlineStr">
+        <is>
+          <t>jsonb NULL</t>
+        </is>
+      </c>
+      <c r="J147" s="14" t="inlineStr">
+        <is>
+          <t>Диф значений до/после.</t>
+        </is>
+      </c>
+      <c r="K147" s="13" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="L147" s="13" t="inlineStr"/>
+      <c r="M147" s="13" t="inlineStr"/>
+      <c r="N147" s="13" t="inlineStr">
+        <is>
+          <t>JSONB</t>
+        </is>
+      </c>
+      <c r="O147" s="13" t="inlineStr"/>
+      <c r="P147" s="13" t="inlineStr"/>
+      <c r="Q147" s="13" t="inlineStr"/>
+      <c r="R147" s="13" t="inlineStr"/>
+      <c r="S147" s="13" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T147" s="13" t="inlineStr"/>
+      <c r="U147" s="13" t="inlineStr"/>
+      <c r="V147" s="13" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="W147" s="13" t="inlineStr"/>
+      <c r="X147" s="14" t="inlineStr"/>
+      <c r="Y147" s="13" t="inlineStr"/>
+      <c r="Z147" s="13" t="inlineStr"/>
+      <c r="AA147" s="13" t="inlineStr"/>
+      <c r="AB147" s="13" t="inlineStr"/>
+      <c r="AC147" s="13" t="inlineStr"/>
+      <c r="AD147" s="13" t="inlineStr"/>
+      <c r="AE147" s="13" t="inlineStr"/>
+      <c r="AF147" s="13" t="inlineStr"/>
+      <c r="AG147" s="13" t="inlineStr"/>
+      <c r="AH147" s="13" t="inlineStr"/>
+      <c r="AI147" s="14" t="inlineStr"/>
+      <c r="AJ147" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AK147" s="13" t="inlineStr">
+        <is>
+          <t>textarea</t>
+        </is>
+      </c>
+      <c r="AL147" s="13" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AM147" s="13" t="inlineStr"/>
+      <c r="AN147" s="13" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AO147" s="14" t="inlineStr"/>
+      <c r="AP147" s="14" t="inlineStr">
+        <is>
+          <t>Индекс GIN не создаём: поиск по телу дифа в ТЗ не заявлен (нет access pattern).</t>
+        </is>
+      </c>
+      <c r="AQ147" s="14" t="inlineStr"/>
+      <c r="AR147" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AS147" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AT147" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU147" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="13" t="inlineStr">
+        <is>
+          <t>ТЗ §3 М7 audit_log</t>
+        </is>
+      </c>
+      <c r="B148" s="13" t="inlineStr"/>
+      <c r="C148" s="13" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="D148" s="14" t="inlineStr">
+        <is>
+          <t>IP</t>
+        </is>
+      </c>
+      <c r="E148" s="13" t="inlineStr">
+        <is>
+          <t>audit_log.ip</t>
+        </is>
+      </c>
+      <c r="G148" s="13" t="inlineStr">
+        <is>
+          <t>inet NULL</t>
+        </is>
+      </c>
+      <c r="J148" s="14" t="inlineStr">
+        <is>
+          <t>IP-адрес источника запроса.</t>
+        </is>
+      </c>
+      <c r="K148" s="13" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="L148" s="13" t="inlineStr"/>
+      <c r="M148" s="13" t="inlineStr"/>
+      <c r="N148" s="13" t="inlineStr">
+        <is>
+          <t>INET (postgresql.INET)</t>
+        </is>
+      </c>
+      <c r="O148" s="13" t="inlineStr"/>
+      <c r="P148" s="13" t="inlineStr"/>
+      <c r="Q148" s="13" t="inlineStr"/>
+      <c r="R148" s="13" t="inlineStr"/>
+      <c r="S148" s="13" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T148" s="13" t="inlineStr"/>
+      <c r="U148" s="13" t="inlineStr"/>
+      <c r="V148" s="13" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="W148" s="13" t="inlineStr"/>
+      <c r="X148" s="14" t="inlineStr"/>
+      <c r="Y148" s="13" t="inlineStr">
+        <is>
+          <t>ip</t>
+        </is>
+      </c>
+      <c r="Z148" s="13" t="inlineStr"/>
+      <c r="AA148" s="13" t="inlineStr"/>
+      <c r="AB148" s="13" t="inlineStr"/>
+      <c r="AC148" s="13" t="inlineStr"/>
+      <c r="AD148" s="13" t="inlineStr"/>
+      <c r="AE148" s="13" t="inlineStr"/>
+      <c r="AF148" s="13" t="inlineStr"/>
+      <c r="AG148" s="13" t="inlineStr"/>
+      <c r="AH148" s="13" t="inlineStr"/>
+      <c r="AI148" s="14" t="inlineStr"/>
+      <c r="AJ148" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AK148" s="13" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="AL148" s="13" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AM148" s="13" t="inlineStr"/>
+      <c r="AN148" s="13" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AO148" s="14" t="inlineStr"/>
+      <c r="AP148" s="14" t="inlineStr">
+        <is>
+          <t>Нативный inet, а не varchar: корректная валидация и сравнение подсетей.</t>
+        </is>
+      </c>
+      <c r="AQ148" s="14" t="inlineStr"/>
+      <c r="AR148" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AS148" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AT148" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU148" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="13" t="inlineStr">
+        <is>
+          <t>ТЗ §3 М7 audit_log</t>
+        </is>
+      </c>
+      <c r="B149" s="13" t="inlineStr"/>
+      <c r="C149" s="13" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="D149" s="14" t="inlineStr">
+        <is>
+          <t>Когда</t>
+        </is>
+      </c>
+      <c r="E149" s="13" t="inlineStr">
+        <is>
+          <t>audit_log.created_at</t>
+        </is>
+      </c>
+      <c r="G149" s="13" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="J149" s="14" t="inlineStr">
+        <is>
+          <t>Момент действия.</t>
+        </is>
+      </c>
+      <c r="K149" s="13" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="L149" s="13" t="inlineStr"/>
+      <c r="M149" s="13" t="inlineStr"/>
+      <c r="N149" s="13" t="inlineStr">
+        <is>
+          <t>DateTime(timezone=True)</t>
+        </is>
+      </c>
+      <c r="O149" s="13" t="inlineStr">
+        <is>
+          <t>server_default=func.now()</t>
+        </is>
+      </c>
+      <c r="P149" s="13" t="inlineStr"/>
+      <c r="Q149" s="13" t="inlineStr"/>
+      <c r="R149" s="13" t="inlineStr"/>
+      <c r="S149" s="13" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="T149" s="13" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
+      <c r="U149" s="13" t="inlineStr">
+        <is>
+          <t>True (created_at DESC)</t>
+        </is>
+      </c>
+      <c r="V149" s="13" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="W149" s="13" t="inlineStr"/>
+      <c r="X149" s="14" t="inlineStr"/>
+      <c r="Y149" s="13" t="inlineStr">
+        <is>
+          <t>created_at__range</t>
+        </is>
+      </c>
+      <c r="Z149" s="13" t="inlineStr"/>
+      <c r="AA149" s="13" t="inlineStr"/>
+      <c r="AB149" s="13" t="inlineStr"/>
+      <c r="AC149" s="13" t="inlineStr"/>
+      <c r="AD149" s="13" t="inlineStr"/>
+      <c r="AE149" s="13" t="inlineStr"/>
+      <c r="AF149" s="13" t="inlineStr"/>
+      <c r="AG149" s="13" t="inlineStr"/>
+      <c r="AH149" s="13" t="inlineStr"/>
+      <c r="AI149" s="14" t="inlineStr"/>
+      <c r="AJ149" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AK149" s="13" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="AL149" s="13" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AM149" s="13" t="inlineStr"/>
+      <c r="AN149" s="13" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AO149" s="14" t="inlineStr"/>
+      <c r="AP149" s="14" t="inlineStr"/>
+      <c r="AQ149" s="14" t="inlineStr"/>
+      <c r="AR149" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS149" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AT149" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU149" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:AU135"/>
-  <mergeCells count="272">
+  <autoFilter ref="A4:AU149"/>
+  <mergeCells count="300">
     <mergeCell ref="G125:I125"/>
     <mergeCell ref="G38:I38"/>
     <mergeCell ref="G103:I103"/>
+    <mergeCell ref="E145:F145"/>
+    <mergeCell ref="E139:F139"/>
     <mergeCell ref="G112:I112"/>
     <mergeCell ref="G13:I13"/>
     <mergeCell ref="E62:F62"/>
@@ -18082,6 +19884,7 @@
     <mergeCell ref="E23:F23"/>
     <mergeCell ref="G87:I87"/>
     <mergeCell ref="G127:I127"/>
+    <mergeCell ref="E142:F142"/>
     <mergeCell ref="E8:F8"/>
     <mergeCell ref="G15:I15"/>
     <mergeCell ref="E64:F64"/>
@@ -18100,6 +19903,7 @@
     <mergeCell ref="E128:F128"/>
     <mergeCell ref="G73:I73"/>
     <mergeCell ref="G88:I88"/>
+    <mergeCell ref="E137:F137"/>
     <mergeCell ref="G26:I26"/>
     <mergeCell ref="E65:F65"/>
     <mergeCell ref="G63:I63"/>
@@ -18107,6 +19911,7 @@
     <mergeCell ref="G129:I129"/>
     <mergeCell ref="G16:I16"/>
     <mergeCell ref="E105:F105"/>
+    <mergeCell ref="E148:F148"/>
     <mergeCell ref="G50:I50"/>
     <mergeCell ref="E99:F99"/>
     <mergeCell ref="G90:I90"/>
@@ -18127,15 +19932,18 @@
     <mergeCell ref="E85:F85"/>
     <mergeCell ref="E100:F100"/>
     <mergeCell ref="G107:I107"/>
+    <mergeCell ref="E136:F136"/>
     <mergeCell ref="E75:F75"/>
     <mergeCell ref="E22:F22"/>
     <mergeCell ref="E53:F53"/>
     <mergeCell ref="E93:F93"/>
     <mergeCell ref="E115:F115"/>
+    <mergeCell ref="E146:F146"/>
     <mergeCell ref="E102:F102"/>
     <mergeCell ref="G122:I122"/>
     <mergeCell ref="E12:F12"/>
     <mergeCell ref="G101:I101"/>
+    <mergeCell ref="G141:I141"/>
     <mergeCell ref="G28:I28"/>
     <mergeCell ref="E117:F117"/>
     <mergeCell ref="G6:I6"/>
@@ -18156,6 +19964,8 @@
     <mergeCell ref="G133:I133"/>
     <mergeCell ref="E38:F38"/>
     <mergeCell ref="G14:I14"/>
+    <mergeCell ref="G142:I142"/>
+    <mergeCell ref="E147:F147"/>
     <mergeCell ref="G80:I80"/>
     <mergeCell ref="E133:F133"/>
     <mergeCell ref="G55:I55"/>
@@ -18165,6 +19975,7 @@
     <mergeCell ref="G135:I135"/>
     <mergeCell ref="E40:F40"/>
     <mergeCell ref="G51:I51"/>
+    <mergeCell ref="G144:I144"/>
     <mergeCell ref="G54:I54"/>
     <mergeCell ref="G119:I119"/>
     <mergeCell ref="G32:I32"/>
@@ -18184,6 +19995,7 @@
     <mergeCell ref="G71:I71"/>
     <mergeCell ref="E120:F120"/>
     <mergeCell ref="E16:F16"/>
+    <mergeCell ref="G145:I145"/>
     <mergeCell ref="G27:I27"/>
     <mergeCell ref="E76:F76"/>
     <mergeCell ref="E25:F25"/>
@@ -18196,14 +20008,17 @@
     <mergeCell ref="E58:F58"/>
     <mergeCell ref="Z2:AO2"/>
     <mergeCell ref="G82:I82"/>
+    <mergeCell ref="G147:I147"/>
     <mergeCell ref="E50:F50"/>
     <mergeCell ref="E121:F121"/>
     <mergeCell ref="G10:I10"/>
     <mergeCell ref="G66:I66"/>
     <mergeCell ref="E130:F130"/>
+    <mergeCell ref="G137:I137"/>
     <mergeCell ref="G19:I19"/>
     <mergeCell ref="E68:F68"/>
     <mergeCell ref="G53:I53"/>
+    <mergeCell ref="G146:I146"/>
     <mergeCell ref="G93:I93"/>
     <mergeCell ref="G34:I34"/>
     <mergeCell ref="E52:F52"/>
@@ -18218,12 +20033,14 @@
     <mergeCell ref="G108:I108"/>
     <mergeCell ref="E123:F123"/>
     <mergeCell ref="E132:F132"/>
+    <mergeCell ref="G139:I139"/>
     <mergeCell ref="G58:I58"/>
     <mergeCell ref="E20:F20"/>
     <mergeCell ref="E107:F107"/>
     <mergeCell ref="E29:F29"/>
     <mergeCell ref="G5:I5"/>
     <mergeCell ref="G123:I123"/>
+    <mergeCell ref="E143:F143"/>
     <mergeCell ref="G45:I45"/>
     <mergeCell ref="E94:F94"/>
     <mergeCell ref="E103:F103"/>
@@ -18243,6 +20060,7 @@
     <mergeCell ref="E114:F114"/>
     <mergeCell ref="G47:I47"/>
     <mergeCell ref="E59:F59"/>
+    <mergeCell ref="E149:F149"/>
     <mergeCell ref="E6:F6"/>
     <mergeCell ref="E77:F77"/>
     <mergeCell ref="G44:I44"/>
@@ -18265,6 +20083,7 @@
     <mergeCell ref="G21:I21"/>
     <mergeCell ref="E70:F70"/>
     <mergeCell ref="G86:I86"/>
+    <mergeCell ref="E144:F144"/>
     <mergeCell ref="E57:F57"/>
     <mergeCell ref="E54:F54"/>
     <mergeCell ref="E32:F32"/>
@@ -18277,11 +20096,13 @@
     <mergeCell ref="E81:F81"/>
     <mergeCell ref="E112:F112"/>
     <mergeCell ref="E134:F134"/>
+    <mergeCell ref="G136:I136"/>
     <mergeCell ref="G97:I97"/>
     <mergeCell ref="G7:I7"/>
     <mergeCell ref="E56:F56"/>
     <mergeCell ref="E96:F96"/>
     <mergeCell ref="E43:F43"/>
+    <mergeCell ref="E141:F141"/>
     <mergeCell ref="E24:F24"/>
     <mergeCell ref="G57:I57"/>
     <mergeCell ref="E106:F106"/>
@@ -18299,8 +20120,11 @@
     <mergeCell ref="E126:F126"/>
     <mergeCell ref="G33:I33"/>
     <mergeCell ref="E82:F82"/>
+    <mergeCell ref="E140:F140"/>
     <mergeCell ref="E35:F35"/>
+    <mergeCell ref="G148:I148"/>
     <mergeCell ref="E10:F10"/>
+    <mergeCell ref="E138:F138"/>
     <mergeCell ref="G114:I114"/>
     <mergeCell ref="E19:F19"/>
     <mergeCell ref="Y3"/>
@@ -18311,16 +20135,20 @@
     <mergeCell ref="E60:F60"/>
     <mergeCell ref="E9:F9"/>
     <mergeCell ref="E74:F74"/>
+    <mergeCell ref="G138:I138"/>
     <mergeCell ref="G76:I76"/>
     <mergeCell ref="G91:I91"/>
     <mergeCell ref="G25:I25"/>
     <mergeCell ref="G85:I85"/>
+    <mergeCell ref="G143:I143"/>
     <mergeCell ref="G99:I99"/>
     <mergeCell ref="E30:F30"/>
     <mergeCell ref="G60:I60"/>
     <mergeCell ref="E11:F11"/>
     <mergeCell ref="G75:I75"/>
+    <mergeCell ref="G140:I140"/>
     <mergeCell ref="E45:F45"/>
+    <mergeCell ref="G149:I149"/>
     <mergeCell ref="G59:I59"/>
     <mergeCell ref="G130:I130"/>
     <mergeCell ref="G77:I77"/>
